--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -637,16 +637,16 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -18195,7 +18195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -18320,29 +18320,29 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>0a833edel1lpsxz42k49hmmuqhxvciws</t>
+          <t>0a835aeel1lkinjudbqkx66gewwuzmq6</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>经贸学院路保利·樾广场站点C</t>
+          <t>高新-高校-金科南门B</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -18351,7 +18351,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -18369,18 +18369,14 @@
       <c r="M3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N3" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="N3" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="8" t="inlineStr">
-        <is>
-          <t>5☂</t>
-        </is>
+      <c r="P3" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q3" s="7" t="n">
         <v>0</v>
@@ -18392,29 +18388,29 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lycifn494eenmgjrt9tew5</t>
+          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>湖东路41号龙眠大道站商贸中心站点</t>
+          <t>龙眠大道海丰小视科技中心(建设中)站点</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -18441,18 +18437,14 @@
       <c r="M4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="N4" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="P4" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q4" s="7" t="n">
         <v>0</v>
@@ -18464,12 +18456,12 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>897071617543372800</t>
+          <t>0a83a414l1l7iaxy7ybfmcgce27jr5vm</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道龙湖新壹城站点I</t>
+          <t>修文路保利·梧桐语站点Z18</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -18479,14 +18471,14 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -18495,7 +18487,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -18513,18 +18505,14 @@
       <c r="M5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>22☂</t>
-        </is>
+      <c r="N5" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="8" t="inlineStr">
-        <is>
-          <t>37☂</t>
-        </is>
+      <c r="P5" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q5" s="7" t="n">
         <v>0</v>
@@ -18536,17 +18524,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0a83e3a1l1lvhijhmcquysadw8bfa5wf</t>
+          <t>893749047382581248</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>日晖路南京工程学院(江宁校区)站点K</t>
+          <t>玉堂巷2-1号小里新寓站点A</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -18561,22 +18549,22 @@
         <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -18591,8 +18579,8 @@
       <c r="O6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="9" t="n">
-        <v>12</v>
+      <c r="P6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="7" t="n">
         <v>0</v>
@@ -18604,12 +18592,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1lhbvcb74ktgp2ndxews5ds</t>
+          <t>893715809572151296</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>鼓山路31号万达公馆站点</t>
+          <t>土山路华意泰富花苑站点A</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -18619,27 +18607,27 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -18653,21 +18641,17 @@
       <c r="M7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="N7" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="8" t="inlineStr">
-        <is>
-          <t>1☂</t>
-        </is>
-      </c>
-      <c r="Q7" s="10" t="n">
-        <v>1</v>
+      <c r="P7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R7" s="7" t="n">
         <v>0</v>
@@ -18676,12 +18660,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>889807458993676288</t>
+          <t>0a83a414l1lyxfkh7vjgmkyih6st4gkb</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>江宁区龙眠大道224号</t>
+          <t>经贸学院路保利·樾广场站点A</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -18691,52 +18675,48 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>12☂</t>
-        </is>
+      <c r="M8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>36☂</t>
-        </is>
+      <c r="P8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>0</v>
@@ -18748,12 +18728,12 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>0a836834l1l3da2h7tzr2f862acja42j</t>
+          <t>0a83f181l1l6rkzb44xcdctf7rrdynbs</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>凤鸣路江宁大学城商业广场站点A</t>
+          <t>南京医科大学门口右</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -18763,32 +18743,32 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L9" s="7" t="n">
@@ -18797,21 +18777,17 @@
       <c r="M9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="N9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="8" t="inlineStr">
-        <is>
-          <t>5☂</t>
-        </is>
-      </c>
-      <c r="Q9" s="9" t="n">
-        <v>12</v>
+      <c r="P9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R9" s="7" t="n">
         <v>0</v>
@@ -18820,42 +18796,42 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l5gghy5e8paunuv4b52xec</t>
+          <t>897028622557294592</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>东山地铁站3号口南京科技银行南京市发展和改革委员会站点</t>
+          <t>丽泽路南京工程学院江宁校区站点D</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -18869,65 +18845,61 @@
       <c r="M10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>1☂</t>
-        </is>
+      <c r="N10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="8" t="inlineStr">
-        <is>
-          <t>1☂</t>
-        </is>
-      </c>
-      <c r="Q10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="10" t="n">
-        <v>1</v>
+      <c r="P10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a831714l1lheej2es9p3zdcf66mz8iv</t>
+          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>上元大街458号东域城站点</t>
+          <t>竹山路地铁1号口</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -18941,65 +18913,61 @@
       <c r="M11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="N11" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t>1☂</t>
-        </is>
-      </c>
-      <c r="Q11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" s="10" t="n">
-        <v>1</v>
+      <c r="P11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a898873l1lhrvzgk4fxegmuu4yx8ttj</t>
+          <t>0a83f7a2l1l2993ab6ytviysu39x2a23</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>竹山路5号志宁花园站点</t>
+          <t>天景山路天景山公寓站点A</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -19013,35 +18981,31 @@
       <c r="M12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="N12" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>1☂</t>
-        </is>
-      </c>
-      <c r="Q12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" s="10" t="n">
-        <v>2</v>
+      <c r="P12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lc8358c5v83a5jbqvkpkxv</t>
+          <t>889833971314581504</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>知行路祥云·悦广场站点I</t>
+          <t>江宁区天景山锦绣苑</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -19051,55 +19015,51 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Q13" s="9" t="n">
-        <v>11</v>
+      <c r="P13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R13" s="7" t="n">
         <v>0</v>
@@ -19108,47 +19068,47 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0a83fd33l1lahbv3p94qs2r8968jt4fp</t>
+          <t>0a83879dl1l7wim598gqfxfejud8ahhy</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道金轮·津桥华府站点P</t>
+          <t>海事学院北门左侧</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="L14" s="7" t="n">
@@ -19157,40 +19117,36 @@
       <c r="M14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>11☂</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="n">
+      <c r="N14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="R14" s="9" t="n">
-        <v>11</v>
+      <c r="P14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1222113693250682880</t>
+          <t>0a836834l1l3da2h7tzr2f862acja42j</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺3</t>
+          <t>凤鸣路江宁大学城商业广场站点A</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -19199,23 +19155,23 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -19223,90 +19179,88 @@
           <t>14%</t>
         </is>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="L15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="R15" s="9" t="n">
-        <v>32</v>
+      <c r="R15" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>0a83fd33l1lkftqhupwfzyizsz3mzrxg</t>
+          <t>0a8398f6l1lgcmyt8mtjtxnw4bwhwj4b</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道保利·樾广场站点I</t>
+          <t>高新-地铁-交院地铁站2号口a</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>373</v>
+        <v>130</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>91☂</t>
-        </is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>114</v>
-      </c>
-      <c r="P16" s="7" t="n">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>49</v>
       </c>
       <c r="Q16" s="7" t="n">
         <v>0</v>
@@ -19318,12 +19272,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1158030571808550912</t>
+          <t>1222113693250682880</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>1号门</t>
+          <t>灵谷寺3</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -19333,14 +19287,14 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>3</v>
@@ -19353,66 +19307,62 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>0</v>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>11☂</t>
-        </is>
-      </c>
-      <c r="O17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Q17" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="R17" s="10" t="n">
-        <v>10</v>
+      <c r="N17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="R17" s="9" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>891406556039413760</t>
+          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>江宁区善鉴路51号</t>
+          <t>土山路东域城站点A</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>3</v>
@@ -19421,53 +19371,49 @@
         <v>3</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="M18" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t>12☂</t>
-        </is>
+      <c r="M18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="n">
-        <v>0</v>
+      <c r="P18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="R18" s="9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>889466722646794240</t>
+          <t>893750907107000320</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>胜太东路江宁供销商厦站点</t>
+          <t>新医路27-2号小里新寓站点</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -19477,14 +19423,14 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>3</v>
@@ -19493,123 +19439,117 @@
         <v>3</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="n">
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="P19" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="R19" s="9" t="n">
-        <v>11</v>
+      <c r="R19" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0a83fd33l1l2puh6hcfgjnnxq4rgg2ve</t>
+          <t>889466722646794240</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道保利·樾广场站点L</t>
+          <t>胜太东路江宁供销商厦站点</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>287</v>
+        <v>35</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="M20" s="9" t="n">
-        <v>73</v>
-      </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t>34☂</t>
-        </is>
-      </c>
-      <c r="O20" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="P20" s="9" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="R20" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>0a83e9a8l1l5gi7n8g39kdamy6h6xzfc</t>
+          <t>0a8398f6l1lxqartiapyxea3wiq2natv</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路城市之光大厦站点</t>
+          <t>经贸地铁站2号口停车场</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -19619,55 +19559,51 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>80</v>
+        <v>335</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="M21" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="O21" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>10☂</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="n">
-        <v>0</v>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q21" s="9" t="n">
+        <v>191</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>24</v>
@@ -19676,12 +19612,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>0a83f070l1l3nefxhf3epn6wjp3gniq2</t>
+          <t>897042860272709632</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道龙湖·新壹城站点S</t>
+          <t>鹏山路中粮悦天地(建设中)站点B</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -19691,14 +19627,14 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>4</v>
@@ -19707,58 +19643,54 @@
         <v>4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>394</v>
+        <v>68</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="L22" s="9" t="n">
-        <v>101</v>
-      </c>
-      <c r="M22" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t>22☂</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>36☂</t>
-        </is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="P22" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="R22" s="9" t="n">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="R22" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
+          <t>1158030571808550912</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>格致路金陵科技学院(江宁校区)站点Z50</t>
+          <t>1号门</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -19767,54 +19699,54 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>23</v>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>33☂</t>
-        </is>
-      </c>
-      <c r="O23" s="7" t="n">
-        <v>0</v>
+          <t>11☂</t>
+        </is>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="P23" s="8" t="inlineStr">
         <is>
-          <t>11☂</t>
+          <t>0☂</t>
         </is>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="R23" s="9" t="n">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="R23" s="10" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -19835,14 +19767,14 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>5</v>
@@ -19855,12 +19787,12 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
@@ -19869,10 +19801,8 @@
       <c r="M24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N24" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="N24" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O24" s="10" t="n">
         <v>10</v>
@@ -19890,87 +19820,85 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
+          <t>0a898873l1l2z5yttrk27pq8kwxsxux8</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>平泰街太平花苑站点</t>
+          <t>高新-小区-瑾家珑熹台（南1门）</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>5</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="n">
-        <v>0</v>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t>10☂</t>
-        </is>
-      </c>
-      <c r="O25" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="P25" s="9" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="R25" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>1158030574945890304</t>
+          <t>897053191954571264</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺2</t>
+          <t>知行路中粮悦天地(建设中)站点F</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -19979,66 +19907,66 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="N26" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" s="10" t="n">
+      <c r="O26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q26" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="Q26" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="R26" s="10" t="n">
+      <c r="R26" s="9" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lcxaqiruqqydidbajabwk5</t>
+          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>日晖路南京工程学院(江宁校区)站点O</t>
+          <t>鹏山路东方·龙湖湾站点Z2</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -20053,132 +19981,128 @@
         <v>7</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>360</v>
+        <v>66</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="M27" s="9" t="n">
-        <v>72</v>
-      </c>
-      <c r="N27" s="9" t="n">
-        <v>36</v>
+        <v>11</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="R27" s="7" t="n">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="R27" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>889665664809402368</t>
+          <t>1158030574945890304</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>江宁区弘景大道90号</t>
+          <t>灵谷寺2</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="n">
-        <v>25</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="N28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="O28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="P28" s="8" t="inlineStr">
-        <is>
-          <t>48☂</t>
-        </is>
-      </c>
       <c r="Q28" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="R28" s="9" t="n">
-        <v>36</v>
+        <v>11</v>
+      </c>
+      <c r="R28" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lvbbtuc6ix87f3uds958yn</t>
+          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>知行路中国银行江苏省分行培训中心站点C</t>
+          <t>平泰街太平花苑站点</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -20187,205 +20111,197 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>219</v>
+        <v>109</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>29%</t>
-        </is>
-      </c>
-      <c r="L29" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="M29" s="10" t="n">
-        <v>12</v>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="O29" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q29" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="R29" s="9" t="n">
         <v>11</v>
-      </c>
-      <c r="P29" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q29" s="9" t="n">
-        <v>89</v>
-      </c>
-      <c r="R29" s="9" t="n">
-        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
+          <t>889797845067956224</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>胜太西路45号汇金新天地广场站点</t>
+          <t>经贸学院北门右手</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>5</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>242</v>
+        <v>137</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="M30" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="N30" s="8" t="inlineStr">
-        <is>
-          <t>20☂</t>
-        </is>
-      </c>
-      <c r="O30" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="P30" s="8" t="inlineStr">
-        <is>
-          <t>45☂</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="O30" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P30" s="9" t="n">
+        <v>24</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="R30" s="9" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1l766y62mwt6n4tcfjp3swe</t>
+          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>日晖路南京工程学院(江宁校区)站点W</t>
+          <t>吉印大道融信·铂岸中心站点</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>697</v>
+        <v>241</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>72</v>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t>12☂</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>116</v>
-      </c>
-      <c r="P31" s="8" t="inlineStr">
-        <is>
-          <t>222☂</t>
-        </is>
+        <v>38</v>
+      </c>
+      <c r="P31" s="9" t="n">
+        <v>36</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="R31" s="9" t="n">
-        <v>120</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>897020632785661952</t>
+          <t>889665664809402368</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>知行路南京晓庄学院方山校区站点C</t>
+          <t>高新-高校-金科南门C</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -20395,69 +20311,65 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>575</v>
+        <v>155</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>144</v>
+        <v>25</v>
       </c>
       <c r="M32" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="P32" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t>30☂</t>
-        </is>
-      </c>
-      <c r="O32" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="P32" s="8" t="inlineStr">
-        <is>
-          <t>35☂</t>
-        </is>
-      </c>
       <c r="Q32" s="9" t="n">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>144</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>897019876399329280</t>
+          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>知行路中国银行江苏省分行培训中心站点</t>
+          <t>高新-小区-瑾家珑熹台（南2门）</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -20467,58 +20379,54 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>751</v>
+        <v>96</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>105</v>
+        <v>12</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>204</v>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t>121☂</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="P33" s="8" t="inlineStr">
-        <is>
-          <t>179☂</t>
-        </is>
+        <v>36</v>
+      </c>
+      <c r="P33" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="R33" s="9" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
@@ -20596,12 +20504,12 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>0a838de0l1lnurtzrb4hnycbdpmcz7tn</t>
+          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>吉印大道东南大学(九龙湖校区)站点H</t>
+          <t>胜太西路太平花苑北苑站点C</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -20611,23 +20519,23 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>820</v>
+        <v>95</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -20636,70 +20544,66 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>192</v>
+        <v>11</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>92</v>
-      </c>
-      <c r="N35" s="8" t="inlineStr">
-        <is>
-          <t>141☂</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="N35" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>108</v>
-      </c>
-      <c r="P35" s="8" t="inlineStr">
-        <is>
-          <t>120☂</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="P35" s="9" t="n">
+        <v>16</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>0a896d49l1lbbwz747pcy5i4di8mdtrt</t>
+          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道站点E</t>
+          <t>胜太西路47号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>152</v>
+        <v>257</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -20712,40 +20616,36 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="M36" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="M36" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="N36" s="8" t="inlineStr">
-        <is>
-          <t>11☂</t>
-        </is>
+      <c r="N36" s="9" t="n">
+        <v>19</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="P36" s="8" t="inlineStr">
-        <is>
-          <t>22☂</t>
-        </is>
+        <v>55</v>
+      </c>
+      <c r="P36" s="9" t="n">
+        <v>33</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
+          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
+          <t>胜太西路45号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -20755,23 +20655,23 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>120</v>
+        <v>242</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -20784,29 +20684,25 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="N37" s="8" t="inlineStr">
-        <is>
-          <t>24☂</t>
-        </is>
+        <v>43</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="P37" s="8" t="inlineStr">
-        <is>
-          <t>12☂</t>
-        </is>
+        <v>43</v>
+      </c>
+      <c r="P37" s="9" t="n">
+        <v>45</v>
       </c>
       <c r="Q37" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R37" s="9" t="n">
         <v>23</v>
-      </c>
-      <c r="R37" s="9" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="38">
@@ -20827,20 +20723,20 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>210</v>
@@ -20861,10 +20757,8 @@
       <c r="M38" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="N38" s="8" t="inlineStr">
-        <is>
-          <t>17☂</t>
-        </is>
+      <c r="N38" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="O38" s="9" t="n">
         <v>22</v>
@@ -20882,12 +20776,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
+          <t>0a838de0l1lnurtzrb4hnycbdpmcz7tn</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>吉印大道东南大学(九龙湖校区)站点H</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -20910,10 +20804,10 @@
         <v>7</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>95</v>
+        <v>820</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -20922,40 +20816,40 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>11</v>
+        <v>192</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="N39" s="10" t="n">
-        <v>10</v>
+        <v>92</v>
+      </c>
+      <c r="N39" s="9" t="n">
+        <v>141</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="P39" s="9" t="n">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
+          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>吉印大道融信·铂岸中心站点</t>
+          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -20965,23 +20859,23 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>241</v>
+        <v>120</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -20994,38 +20888,36 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="N40" s="9" t="n">
+        <v>24</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P40" s="9" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R40" s="9" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
+          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>胜太西路47号汇金新天地广场站点</t>
+          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -21051,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -21064,41 +20956,41 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>33</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="R41" s="9" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1l8wxq7ggvbwv6ueqbp4nwi</t>
+          <t>1158030570667700224</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>日晖路南京工程学院(江宁校区)站点N</t>
+          <t>美龄宫</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -21107,7 +20999,7 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>7</v>
@@ -21119,7 +21011,7 @@
         <v>7</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>463</v>
+        <v>4139</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -21132,41 +21024,41 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>12</v>
+        <v>550</v>
       </c>
       <c r="M42" s="9" t="n">
-        <v>24</v>
+        <v>506</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>24</v>
+        <v>346</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>23</v>
+        <v>658</v>
       </c>
       <c r="P42" s="9" t="n">
-        <v>44</v>
+        <v>539</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>84</v>
+        <v>769</v>
       </c>
       <c r="R42" s="9" t="n">
-        <v>252</v>
+        <v>771</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1ltpjvhpxzdrj37x2e9tbjg</t>
+          <t>1158030572869709824</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>燕语堂休闲娱乐祥云·悦广场站点A</t>
+          <t>东沟停车场</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -21175,7 +21067,7 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>7</v>
@@ -21187,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>156</v>
+        <v>1843</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -21200,36 +21092,36 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>33</v>
+        <v>328</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>45</v>
+        <v>301</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>11</v>
+        <v>221</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="P43" s="9" t="n">
-        <v>22</v>
+        <v>407</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="R43" s="9" t="n">
-        <v>11</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>1158030570667700224</t>
+          <t>1158025287508230144</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>美龄宫</t>
+          <t>3号门</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -21243,7 +21135,7 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>7</v>
@@ -21255,7 +21147,7 @@
         <v>7</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>4139</v>
+        <v>994</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -21268,36 +21160,36 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>550</v>
+        <v>121</v>
       </c>
       <c r="M44" s="9" t="n">
-        <v>506</v>
+        <v>132</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>346</v>
+        <v>52</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>658</v>
+        <v>171</v>
       </c>
       <c r="P44" s="9" t="n">
-        <v>539</v>
+        <v>121</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>769</v>
+        <v>199</v>
       </c>
       <c r="R44" s="9" t="n">
-        <v>771</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>1158030572869709824</t>
+          <t>1158030569614929920</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>东沟停车场</t>
+          <t>海底世界站台</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -21311,7 +21203,7 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>7</v>
@@ -21323,7 +21215,7 @@
         <v>7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1843</v>
+        <v>1063</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -21336,36 +21228,36 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>328</v>
+        <v>196</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>301</v>
+        <v>132</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>221</v>
+        <v>64</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="P45" s="9" t="n">
-        <v>407</v>
+        <v>143</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>287</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>1158025287508230144</t>
+          <t>1158030573943451648</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>3号门</t>
+          <t>中山陵7号门</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -21379,7 +21271,7 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>7</v>
@@ -21391,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>994</v>
+        <v>840</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -21404,36 +21296,36 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M46" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="N46" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="O46" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="P46" s="9" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q46" s="9" t="n">
         <v>132</v>
       </c>
-      <c r="N46" s="9" t="n">
-        <v>52</v>
-      </c>
-      <c r="O46" s="9" t="n">
-        <v>171</v>
-      </c>
-      <c r="P46" s="9" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q46" s="9" t="n">
-        <v>199</v>
-      </c>
       <c r="R46" s="9" t="n">
-        <v>198</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>1158030569614929920</t>
+          <t>1158030568570548224</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>海底世界站台</t>
+          <t>海底世界</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -21447,7 +21339,7 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>7</v>
@@ -21459,7 +21351,7 @@
         <v>7</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>1063</v>
+        <v>456</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -21472,36 +21364,36 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>176</v>
+        <v>55</v>
       </c>
       <c r="P47" s="9" t="n">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>198</v>
+        <v>55</v>
       </c>
       <c r="R47" s="9" t="n">
-        <v>154</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>1158030573943451648</t>
+          <t>1158030563076009984</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>中山陵7号门</t>
+          <t>灵谷寺公园1</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -21527,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>840</v>
+        <v>428</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -21540,229 +21432,25 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="M48" s="9" t="n">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="P48" s="9" t="n">
-        <v>176</v>
+        <v>91</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="R48" s="9" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>1158030568570548224</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>海底世界</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>刘永振</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>全天点位</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>456</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L49" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="M49" s="9" t="n">
-        <v>88</v>
-      </c>
-      <c r="N49" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="O49" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="P49" s="9" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q49" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="R49" s="9" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>1158030563076009984</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>灵谷寺公园1</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>刘永振</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>全天点位</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>428</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L50" s="9" t="n">
-        <v>94</v>
-      </c>
-      <c r="M50" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="N50" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="O50" s="9" t="n">
-        <v>54</v>
-      </c>
-      <c r="P50" s="9" t="n">
-        <v>91</v>
-      </c>
-      <c r="Q50" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="R50" s="9" t="n">
         <v>57</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>刘博文</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>全天点位</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L51" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="M51" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="N51" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="O51" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="P51" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q51" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="R51" s="9" t="n">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -21776,7 +21464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -21871,29 +21559,29 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
+          <t>0a835aeel1lkinjudbqkx66gewwuzmq6</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>严南路金辉禹洲金陵铭著站点A</t>
+          <t>高新-高校-金科南门B</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -21902,7 +21590,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -21914,40 +21602,36 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
-        <is>
-          <t>18☂</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>10☂</t>
-        </is>
+      <c r="L3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lc8358c5v83a5jbqvkpkxv</t>
+          <t>0a898873l1l2z5yttrk27pq8kwxsxux8</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>知行路祥云·悦广场站点I</t>
+          <t>高新-小区-瑾家珑熹台（南1门）</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>2</v>
@@ -21981,29 +21665,29 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>1158025287508230144</t>
+          <t>0a8398f6l1lgcmyt8mtjtxnw4bwhwj4b</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>3号门</t>
+          <t>高新-地铁-交院地铁站2号口a</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -22012,7 +21696,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -22024,31 +21708,27 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>220☂</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>154☂</t>
-        </is>
+      <c r="L5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0a8339f4l1lh4xmtqcvwzga6zi8snxmx</t>
+          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺4</t>
+          <t>龙眠大道海丰小视科技中心(建设中)站点</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -22057,7 +21737,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>2</v>
@@ -22091,17 +21771,17 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1158030564174917632</t>
+          <t>0a83a414l1l7iaxy7ybfmcgce27jr5vm</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>东山头</t>
+          <t>修文路保利·梧桐语站点Z18</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -22110,7 +21790,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>2</v>
@@ -22144,26 +21824,26 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>0a83975dl1lvajc5ev6ycaq4s68uymbk</t>
+          <t>893749047382581248</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>知行路金陵科技学院(江宁校区)站点Z</t>
+          <t>玉堂巷2-1号小里新寓站点A</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>2</v>
@@ -22197,29 +21877,29 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
+          <t>893750907107000320</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>平泰街太平花苑站点</t>
+          <t>新医路27-2号小里新寓站点</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -22228,7 +21908,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -22240,40 +21920,36 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>10☂</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>30☂</t>
-        </is>
+      <c r="L9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>0a896d49l1l6x2efdb3k9ed82ci7t7ek</t>
+          <t>893715809572151296</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道站点D</t>
+          <t>土山路华意泰富花苑站点A</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>2</v>
@@ -22307,17 +21983,17 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a83352el1lkzv3q9puxrvbtrzwss2pm</t>
+          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>知行路金陵科技学院(江宁校区)站点R</t>
+          <t>竹山路地铁1号口</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -22326,7 +22002,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>2</v>
@@ -22360,17 +22036,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a83f181l1leg5h4gu2x95z56js3khdp</t>
+          <t>0a83a414l1lyxfkh7vjgmkyih6st4gkb</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>凤溪东路龙湖·新壹城站点A</t>
+          <t>经贸学院路保利·樾广场站点A</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -22379,7 +22055,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>2</v>
@@ -22413,123 +22089,127 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
+          <t>1158025287508230144</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>胜太西路太平花苑北苑站点C</t>
+          <t>3号门</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M13" s="9" t="n">
-        <v>11</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>220☂</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>154☂</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
+          <t>0a8339f4l1lh4xmtqcvwzga6zi8snxmx</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>胜太西路天琪雅居站点</t>
+          <t>灵谷寺4</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L14" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M14" s="9" t="n">
-        <v>26</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1ltpjvhpxzdrj37x2e9tbjg</t>
+          <t>1158030564174917632</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>燕语堂休闲娱乐祥云·悦广场站点A</t>
+          <t>东山头</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -22538,46 +22218,46 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>22</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>889717813217533952</t>
+          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>江宁区龙眠大道628号</t>
+          <t>鹏山路东方·龙湖湾站点Z2</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -22587,50 +22267,50 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="M16" s="10" t="n">
-        <v>11</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
+          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>格致路金陵科技学院(江宁校区)站点Z50</t>
+          <t>高新-小区-瑾家珑熹台（南2门）</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -22640,27 +22320,27 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -22669,31 +22349,31 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="M17" s="10" t="n">
-        <v>11</v>
+        <v>35</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
+          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>胜太西路47号汇金新天地广场站点</t>
+          <t>土山路东域城站点A</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
@@ -22703,40 +22383,40 @@
         <v>2</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="n">
-        <v>22</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
+          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>胜太西路45号汇金新天地广场站点</t>
+          <t>严南路金辉禹洲金陵铭著站点A</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -22746,7 +22426,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
@@ -22759,10 +22439,10 @@
         <v>2</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -22771,30 +22451,30 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="M19" s="9" t="n">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1158030570667700224</t>
+          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>美龄宫</t>
+          <t>胜太西路太平花苑北苑站点C</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -22803,7 +22483,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>2</v>
@@ -22812,10 +22492,10 @@
         <v>2</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>832</v>
+        <v>21</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -22824,30 +22504,30 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="n">
-        <v>436</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>396</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1158030572869709824</t>
+          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>东沟停车场</t>
+          <t>胜太西路天琪雅居站点</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -22856,7 +22536,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>2</v>
@@ -22865,10 +22545,10 @@
         <v>2</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>759</v>
+        <v>36</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -22877,30 +22557,30 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>341</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>418</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1158030569614929920</t>
+          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>海底世界站台</t>
+          <t>平泰街太平花苑站点</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -22909,7 +22589,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>2</v>
@@ -22918,10 +22598,10 @@
         <v>2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>342</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -22930,30 +22610,30 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L22" s="9" t="n">
-        <v>143</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>199</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>1158030573943451648</t>
+          <t>889665664809402368</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>中山陵7号门</t>
+          <t>高新-高校-金科南门C</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -22962,7 +22642,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>2</v>
@@ -22971,10 +22651,10 @@
         <v>2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>264</v>
+        <v>45</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -22983,30 +22663,30 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>132</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>132</v>
+        <v>35</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>1158030568570548224</t>
+          <t>889466722646794240</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>海底世界</t>
+          <t>胜太东路江宁供销商厦站点</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -23015,7 +22695,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>2</v>
@@ -23024,10 +22704,10 @@
         <v>2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>131</v>
+        <v>13</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -23036,30 +22716,30 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>65</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1158030571808550912</t>
+          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>1号门</t>
+          <t>胜太西路47号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -23068,7 +22748,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>2</v>
@@ -23080,7 +22760,7 @@
         <v>2</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -23093,26 +22773,26 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>1158025279480332288</t>
+          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2号门</t>
+          <t>胜太西路45号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -23121,7 +22801,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>2</v>
@@ -23133,7 +22813,7 @@
         <v>2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -23146,10 +22826,10 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -23170,7 +22850,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -23208,26 +22888,26 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>0a83fd33l1l5bh27pufaui5wq3zvj2hk</t>
+          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道金轮·津桥华府站点Z7</t>
+          <t>吉印大道融信·铂岸中心站点</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>2</v>
@@ -23239,7 +22919,7 @@
         <v>2</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -23252,21 +22932,21 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
+          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>吉印大道融信·铂岸中心站点</t>
+          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -23292,7 +22972,7 @@
         <v>2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -23305,35 +22985,35 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>897071617543372800</t>
+          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道龙湖新壹城站点I</t>
+          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>2</v>
@@ -23345,7 +23025,7 @@
         <v>2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -23358,31 +23038,31 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
+          <t>897042860272709632</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
+          <t>鹏山路中粮悦天地(建设中)站点B</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
@@ -23398,7 +23078,7 @@
         <v>2</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -23411,26 +23091,26 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
+          <t>897053191954571264</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
+          <t>知行路中粮悦天地(建设中)站点F</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -23451,7 +23131,7 @@
         <v>2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -23464,10 +23144,381 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M32" s="9" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>1158030570667700224</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>美龄宫</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>刘永振</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>全天点位</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>832</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>436</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>1158030572869709824</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>东沟停车场</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>刘永振</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>全天点位</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>759</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>341</v>
+      </c>
+      <c r="M34" s="9" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>1158030569614929920</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>海底世界站台</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>刘永振</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>全天点位</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>342</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>143</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>1158030573943451648</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>中山陵7号门</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>刘永振</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>全天点位</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>132</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>1158030568570548224</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>海底世界</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>刘永振</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>全天点位</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>1158030571808550912</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>1号门</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>刘永振</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>全天点位</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="n">
         <v>11</v>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>1158025279480332288</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>2号门</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>刘永振</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>全天点位</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -24261,22 +24312,22 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>87.1%</t>
         </is>
       </c>
     </row>
@@ -24316,25 +24367,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -24345,25 +24396,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -24377,22 +24428,22 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
     </row>
@@ -24407,7 +24458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -24473,14 +24524,14 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
@@ -24488,7 +24539,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -24528,10 +24579,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>8</v>
@@ -24541,12 +24592,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -24563,19 +24614,48 @@
         <v>4</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>赵龙浩</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>20.0%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -616,12 +616,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -14277,7 +14277,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>06c3ed6b54e6438faf952d2bdbebd0c5</t>
+          <t>1174535134415278080</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -18482,17 +18482,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>893749047382581248</t>
+          <t>0a83f181l1l6rkzb44xcdctf7rrdynbs</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>玉堂巷2-1号小里新寓站点A</t>
+          <t>南京医科大学门口右</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -18553,12 +18553,12 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>0a83f181l1l6rkzb44xcdctf7rrdynbs</t>
+          <t>889833971314581504</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>南京医科大学门口右</t>
+          <t>江宁区天景山锦绣苑</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -18624,17 +18624,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>889833971314581504</t>
+          <t>0a835aeel1lkinjudbqkx66gewwuzmq6</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>江宁区天景山锦绣苑</t>
+          <t>高新-高校-金科南门B</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -18649,22 +18649,22 @@
         <v>8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -18688,19 +18688,19 @@
       <c r="R6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="7" t="n">
-        <v>0</v>
+      <c r="S6" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0a835aeel1lkinjudbqkx66gewwuzmq6</t>
+          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科南门B</t>
+          <t>龙眠大道海丰小视科技中心(建设中)站点</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -18726,7 +18726,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -18760,23 +18760,23 @@
         <v>0</v>
       </c>
       <c r="S7" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
+          <t>893715809572151296</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道海丰小视科技中心(建设中)站点</t>
+          <t>土山路华意泰富花苑站点A</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -18797,7 +18797,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -18831,23 +18831,23 @@
         <v>0</v>
       </c>
       <c r="S8" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>893715809572151296</t>
+          <t>0a83a414l1lyxfkh7vjgmkyih6st4gkb</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>土山路华意泰富花苑站点A</t>
+          <t>经贸学院路保利·樾广场站点A</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -18908,12 +18908,12 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lyxfkh7vjgmkyih6st4gkb</t>
+          <t>0a83879dl1l7wim598gqfxfejud8ahhy</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>经贸学院路保利·樾广场站点A</t>
+          <t>海事学院北门左侧</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -18939,7 +18939,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -18960,8 +18960,8 @@
       <c r="N10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="7" t="n">
-        <v>0</v>
+      <c r="O10" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="P10" s="7" t="n">
         <v>0</v>
@@ -18972,19 +18972,19 @@
       <c r="R10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="10" t="n">
-        <v>12</v>
+      <c r="S10" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a83879dl1l7wim598gqfxfejud8ahhy</t>
+          <t>897028622557294592</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>海事学院北门左侧</t>
+          <t>丽泽路南京工程学院江宁校区站点D</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -19010,7 +19010,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -19031,8 +19031,8 @@
       <c r="N11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="10" t="n">
-        <v>11</v>
+      <c r="O11" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="P11" s="7" t="n">
         <v>0</v>
@@ -19043,19 +19043,19 @@
       <c r="R11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="7" t="n">
-        <v>0</v>
+      <c r="S11" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>897028622557294592</t>
+          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>丽泽路南京工程学院江宁校区站点D</t>
+          <t>竹山路地铁1号口</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -19121,12 +19121,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
+          <t>0a83f7a2l1l2993ab6ytviysu39x2a23</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>竹山路地铁1号口</t>
+          <t>天景山路天景山公寓站点A</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -19192,17 +19192,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0a83f7a2l1l2993ab6ytviysu39x2a23</t>
+          <t>0a8398f6l1lgcmyt8mtjtxnw4bwhwj4b</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>天景山路天景山公寓站点A</t>
+          <t>高新-地铁-交院地铁站2号口a</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -19217,22 +19217,22 @@
         <v>8</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L14" s="7" t="n">
@@ -19244,11 +19244,11 @@
       <c r="N14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="7" t="n">
-        <v>0</v>
+      <c r="O14" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="P14" s="10" t="n">
+        <v>49</v>
       </c>
       <c r="Q14" s="7" t="n">
         <v>0</v>
@@ -19256,24 +19256,24 @@
       <c r="R14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="10" t="n">
-        <v>12</v>
+      <c r="S14" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>0a8398f6l1lgcmyt8mtjtxnw4bwhwj4b</t>
+          <t>0a836834l1l3da2h7tzr2f862acja42j</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>高新-地铁-交院地铁站2号口a</t>
+          <t>凤鸣路江宁大学城商业广场站点A</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -19288,24 +19288,24 @@
         <v>8</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
       <c r="L15" s="7" t="n">
         <v>0</v>
       </c>
@@ -19315,31 +19315,31 @@
       <c r="N15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="10" t="n">
-        <v>81</v>
-      </c>
-      <c r="P15" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q15" s="7" t="n">
-        <v>0</v>
+      <c r="O15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="R15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="7" t="n">
-        <v>0</v>
+      <c r="S15" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>0a836834l1l3da2h7tzr2f862acja42j</t>
+          <t>0a8398f6l1lxqartiapyxea3wiq2natv</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>凤鸣路江宁大学城商业广场站点A</t>
+          <t>经贸地铁站2号口停车场</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -19362,10 +19362,10 @@
         <v>3</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>29</v>
+        <v>335</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="L16" s="7" t="n">
@@ -19389,33 +19389,33 @@
       <c r="O16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="9" t="n">
-        <v>5</v>
+      <c r="P16" s="10" t="n">
+        <v>120</v>
       </c>
       <c r="Q16" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="R16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="10" t="n">
-        <v>12</v>
+        <v>191</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>0a8398f6l1lxqartiapyxea3wiq2natv</t>
+          <t>1222113693250682880</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>经贸地铁站2号口停车场</t>
+          <t>灵谷寺3</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -19424,32 +19424,32 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>335</v>
+        <v>77</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>0</v>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>0</v>
@@ -19460,33 +19460,33 @@
       <c r="O17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="10" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q17" s="10" t="n">
-        <v>191</v>
+      <c r="P17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="R17" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="S17" s="7" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="S17" s="10" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1222113693250682880</t>
+          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺3</t>
+          <t>土山路东域城站点A</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -19495,7 +19495,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>8</v>
@@ -19504,10 +19504,10 @@
         <v>4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -19516,10 +19516,10 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="n">
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="n">
         <v>12</v>
       </c>
       <c r="M18" s="7" t="n">
@@ -19534,25 +19534,25 @@
       <c r="P18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="9" t="n">
-        <v>11</v>
+      <c r="Q18" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="R18" s="10" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="S18" s="10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
+          <t>893749163098365952</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>土山路东域城站点A</t>
+          <t>玉堂巷2-1号小里新寓站点A</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -19590,17 +19590,17 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="L19" s="10" t="n">
+      <c r="L19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10" t="n">
         <v>12</v>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="P19" s="7" t="n">
         <v>0</v>
@@ -22053,7 +22053,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>893749047382581248</t>
+          <t>893749163098365952</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -24660,19 +24660,19 @@
         <v>40</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>42.5%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -591,12 +591,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>38.3%</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>62.4%</t>
         </is>
       </c>
     </row>
@@ -654,14 +654,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20260701 ~ 20260710</t>
+          <t>数据范围: 20260701 ~ 20260711</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 8天, 周末: 2天</t>
+          <t>工作日: 8天, 周末: 3天</t>
         </is>
       </c>
     </row>
@@ -13163,7 +13163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13179,6 +13179,7 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13254,33 +13255,38 @@
           <t>07-05(日)</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>07-11(六)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>732956182771253248</t>
+          <t>1104749676559319040</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>25-全天-商超-金茂汇渗透</t>
+          <t>集庆门大街南京万达广场万达中心建邺渗透</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -13305,23 +13311,26 @@
         <v>0</v>
       </c>
       <c r="M3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
+          <t>0a836146l1lb75b2rkfyy7vkvm675giz</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>九家圩路世茂外滩新城投放点A</t>
+          <t>南京建邺吾悦广场(3号门)吾悦广场(南京建邺店)投放点</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -13333,7 +13342,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -13358,23 +13367,26 @@
         <v>0</v>
       </c>
       <c r="M4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lbekztkg9bb795bdwjee85</t>
+          <t>0a836587l1luwpb8icj8s7h27qzgfz6h</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>天润城地铁站2号口天润城十一街区投放点A</t>
+          <t>新安江街河西CBD投放点</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -13383,10 +13395,10 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -13411,23 +13423,26 @@
         <v>0</v>
       </c>
       <c r="M5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1104749676559319040</t>
+          <t>1153706292829134848</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>集庆门大街南京万达广场万达中心建邺渗透</t>
+          <t>广志路投放点A</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -13436,10 +13451,10 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -13464,23 +13479,26 @@
         <v>0</v>
       </c>
       <c r="M6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1lb75b2rkfyy7vkvm675giz</t>
+          <t>0a836146l1lyjs7c5zcucbu58t8qkunu</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>南京建邺吾悦广场(3号门)吾悦广场(南京建邺店)投放点</t>
+          <t>茂民路御湖仕家投放点</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -13489,10 +13507,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -13517,23 +13535,26 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1luwpb8icj8s7h27qzgfz6h</t>
+          <t>5331e3a58a50481dbc8e7273561f4e25</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>新安江街河西CBD投放点</t>
+          <t>工作日-全天-地铁站-夫子庙2号口-10</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -13542,10 +13563,10 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -13570,23 +13591,26 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>684268350256898048</t>
+          <t>1110455764291215360</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-学则路</t>
+          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -13595,10 +13619,10 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -13623,23 +13647,26 @@
         <v>0</v>
       </c>
       <c r="M9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1153706292829134848</t>
+          <t>1110456076207075328</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>广志路投放点A</t>
+          <t>南京市秦淮区双塘街道升州路夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -13648,10 +13675,10 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -13676,23 +13703,26 @@
         <v>0</v>
       </c>
       <c r="M10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1lyjs7c5zcucbu58t8qkunu</t>
+          <t>0a89a0cdl1luijmqd4buxi8s686ps96i</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>茂民路御湖仕家投放点</t>
+          <t>鱼嘴湿地公园江豚广场南京鱼嘴湿地公园投放点</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -13701,10 +13731,10 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -13729,23 +13759,26 @@
         <v>0</v>
       </c>
       <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
+          <t>0a83e80al1ldxqqv34qytix6br5r7zzh</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
+          <t>江提路投放点</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -13754,10 +13787,10 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -13782,75 +13815,77 @@
         <v>0</v>
       </c>
       <c r="M12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>778851422965239808</t>
+          <t>0a836587l1lbekztkg9bb795bdwjee85</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-仙林新村</t>
+          <t>天润城地铁站2号口天润城十一街区投放点A</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>23☂</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>24☂</t>
-        </is>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>684268350256898048</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>25-全天-地铁-学则路</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -13860,54 +13895,53 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>11☂</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="L14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>788321551519383552</t>
+          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>玄武区鹤鸣路37号</t>
+          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -13917,54 +13951,53 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t>20☂</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t>16☂</t>
-        </is>
+      <c r="L15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1176842717252255744</t>
+          <t>1150704239247155200</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>三元巷6号三元公寓投放点渗透</t>
+          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带A</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -13981,43 +14014,46 @@
         <v>20</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="L16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>813294194703020032</t>
+          <t>1174535930061524992</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>打钉巷金鼎湾国际投放点</t>
+          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -14027,267 +14063,282 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="L17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1174627346911133696</t>
+          <t>754365148238000128</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道户部街长发银座</t>
+          <t>玄武区四牌楼63号</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="L18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>732955142450266112</t>
+          <t>0a836587l1l2ehxa2pgziwbi3i3kp6ct</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
+          <t>红山路辅路常发广场投放点B</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="L19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1150704239247155200</t>
+          <t>0a836146l1lyau4xnzsbvbjunbxguey8</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带A</t>
+          <t>浦珠南路南京工业大学江浦校区投放点A</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="L20" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1174622729575776256</t>
+          <t>1153706318256898048</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区常府街地铁站3号口</t>
+          <t>浦口大道投放点渗透</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="L21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N21" s="9" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1174535134415278080</t>
+          <t>0a8331f1l1ld9wgam59z73ha4yn6qxdr</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道箍桶巷夫子庙秦淮风光带</t>
+          <t>镇南河路东方万汇城投放点E</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -14296,51 +14347,54 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="L22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N22" s="9" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>5331e3a58a50481dbc8e7273561f4e25</t>
+          <t>0a83d1c7l1lae4s7r5hq76dmaivv9ibv</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-地铁站-夫子庙2号口-10</t>
+          <t>迎江路玖印府(建设中)投放点</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -14349,51 +14403,54 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="L23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N23" s="9" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>1174535134415278080</t>
+          <t>732956182771253248</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道箍桶巷夫子庙秦淮风光带</t>
+          <t>25-全天-商超-金茂汇渗透</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -14402,28 +14459,28 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
@@ -14431,22 +14488,25 @@
       </c>
       <c r="M24" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1110455764291215360</t>
+          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
+          <t>九家圩路世茂外滩新城投放点A</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -14455,28 +14515,28 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L25" s="7" t="n">
@@ -14484,17 +14544,20 @@
       </c>
       <c r="M25" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1lm5w7r6duyverna8nzapss</t>
+          <t>1176842717252255744</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>中山东路南京航空航天大学(明故宫校区)投放点B</t>
+          <t>三元巷6号三元公寓投放点渗透</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -14504,32 +14567,32 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
@@ -14537,17 +14600,20 @@
       </c>
       <c r="M26" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N26" s="10" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>1174535930061524992</t>
+          <t>813294194703020032</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
+          <t>打钉巷金鼎湾国际投放点</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -14557,32 +14623,32 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L27" s="7" t="n">
@@ -14590,17 +14656,20 @@
       </c>
       <c r="M27" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>0a838699l1lyun3by28du7fus2rjdmuu</t>
+          <t>1174627346911133696</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>剪子巷40号夫子庙秦淮风光带投放点</t>
+          <t>南京市秦淮区洪武路街道户部街长发银座</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -14610,32 +14679,32 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L28" s="7" t="n">
@@ -14643,17 +14712,20 @@
       </c>
       <c r="M28" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N28" s="10" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>1174618792617238528</t>
+          <t>732955142450266112</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区朝天宫街道建邺路建邺路住宅小区</t>
+          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -14663,54 +14735,53 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1ldsbrxkzcxei46ckdztk7h</t>
+          <t>1174622729575776256</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>中山南路91号江苏文化大厦投放点A</t>
+          <t>南京市秦淮区常府街地铁站3号口</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -14720,32 +14791,32 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L30" s="7" t="n">
@@ -14753,17 +14824,20 @@
       </c>
       <c r="M30" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N30" s="10" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>1110456076207075328</t>
+          <t>1174535134415278080</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区双塘街道升州路夫子庙秦淮风光带</t>
+          <t>南京市秦淮区夫子庙街道箍桶巷夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -14773,32 +14847,32 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L31" s="7" t="n">
@@ -14806,17 +14880,20 @@
       </c>
       <c r="M31" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N31" s="10" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>874549501386596352</t>
+          <t>1174535134415278080</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
+          <t>南京市秦淮区夫子庙街道箍桶巷夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -14833,25 +14910,25 @@
         <v>20</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L32" s="7" t="n">
@@ -14859,17 +14936,20 @@
       </c>
       <c r="M32" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N32" s="10" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>0a838e37l1ls23rim2x3aaf2bwvtsyi2</t>
+          <t>0a836146l1lm5w7r6duyverna8nzapss</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>秦淮区红花街道卡子门地铁站</t>
+          <t>中山东路南京航空航天大学(明故宫校区)投放点B</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -14879,32 +14959,32 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L33" s="7" t="n">
@@ -14912,79 +14992,81 @@
       </c>
       <c r="M33" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N33" s="10" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>854249531796738048</t>
+          <t>0a838699l1lyun3by28du7fus2rjdmuu</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-金马路地铁站</t>
+          <t>剪子巷40号夫子庙秦淮风光带投放点</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t>31☂</t>
-        </is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="10" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>849243610630791168</t>
+          <t>0a83a497l1ldsbrxkzcxei46ckdztk7h</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-地铁-马群站</t>
+          <t>中山南路91号江苏文化大厦投放点A</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -14996,25 +15078,25 @@
         <v>20</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L35" s="7" t="n">
@@ -15022,79 +15104,81 @@
       </c>
       <c r="M35" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N35" s="10" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
+          <t>874549501386596352</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2A</t>
+          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t>15☂</t>
-        </is>
-      </c>
-      <c r="M36" s="8" t="inlineStr">
-        <is>
-          <t>25☂</t>
-        </is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="10" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>754365148238000128</t>
+          <t>0a838e37l1ls23rim2x3aaf2bwvtsyi2</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>玄武区四牌楼63号</t>
+          <t>秦淮区红花街道卡子门地铁站</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -15103,28 +15187,28 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L37" s="7" t="n">
@@ -15132,74 +15216,76 @@
       </c>
       <c r="M37" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N37" s="10" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>849243610630791168</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>25-早峰-地铁-马群站</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t>42☂</t>
-        </is>
-      </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t>76☂</t>
-        </is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="10" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>0a89a0cdl1luijmqd4buxi8s686ps96i</t>
+          <t>939772435800334336</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>鱼嘴湿地公园江豚广场南京鱼嘴湿地公园投放点</t>
+          <t>南京市建邺区江心洲街道红星街洲岛家园</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -15216,43 +15302,46 @@
         <v>15</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L39" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="N39" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>0a83e80al1ldxqqv34qytix6br5r7zzh</t>
+          <t>1206516292750213120</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>江提路投放点</t>
+          <t>中山北路宏图大厦渗透</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -15269,25 +15358,25 @@
         <v>15</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L40" s="7" t="n">
@@ -15295,17 +15384,20 @@
       </c>
       <c r="M40" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N40" s="10" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>1206516292750213120</t>
+          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>中山北路宏图大厦渗透</t>
+          <t>集贤路鼓楼创新广场投放点B</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -15322,25 +15414,25 @@
         <v>15</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L41" s="7" t="n">
@@ -15348,22 +15440,25 @@
       </c>
       <c r="M41" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N41" s="10" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
+          <t>0a836587l1l7hr5eaanydw8fnf2xk6r4</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>集贤路鼓楼创新广场投放点B</t>
+          <t>张家村东方万汇城投放点</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -15372,28 +15467,28 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L42" s="7" t="n">
@@ -15401,52 +15496,55 @@
       </c>
       <c r="M42" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N42" s="10" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l2ehxa2pgziwbi3i3kp6ct</t>
+          <t>1110455098857938944</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>红山路辅路常发广场投放点B</t>
+          <t>浦珠南路中国海油协和石油加油站(江浦站)投放点渗透</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L43" s="7" t="n">
@@ -15454,75 +15552,81 @@
       </c>
       <c r="M43" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N43" s="10" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1lyau4xnzsbvbjunbxguey8</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>浦珠南路南京工业大学江浦校区投放点A</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="H44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="n">
-        <v>0</v>
+      <c r="L44" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="M44" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N44" s="9" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l7hr5eaanydw8fnf2xk6r4</t>
+          <t>e5189cd954054116aa19db28790cc606</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>张家村东方万汇城投放点</t>
+          <t>25-晚峰-地铁站-高新地铁站-30</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -15531,157 +15635,166 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="H45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="L45" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M45" s="7" t="n">
-        <v>0</v>
+      <c r="M45" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N45" s="9" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>1153706318256898048</t>
+          <t>1123869816929062912</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>浦口大道投放点渗透</t>
+          <t>六合大道南京葛塘汽车客运站投放点A</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="7" t="n">
-        <v>0</v>
+      <c r="N46" s="9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>1110455098857938944</t>
+          <t>1174593029863960576</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>浦珠南路中国海油协和石油加油站(江浦站)投放点渗透</t>
+          <t>25-全天-高校-师范大学渗透</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G47" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="H47" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="n">
-        <v>0</v>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="M47" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N47" s="10" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>0a8331f1l1ld9wgam59z73ha4yn6qxdr</t>
+          <t>1153706342168625152</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>镇南河路东方万汇城投放点E</t>
+          <t>鼓楼东南大学渗透</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -15690,51 +15803,54 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F48" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G48" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="H48" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L48" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M48" s="7" t="n">
-        <v>0</v>
+      <c r="M48" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="N48" s="10" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>0a83d1c7l1lae4s7r5hq76dmaivv9ibv</t>
+          <t>1206515660536758272</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>迎江路玖印府(建设中)投放点</t>
+          <t>南京邮电大学渗透</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -15743,108 +15859,110 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="N49" s="10" t="n">
         <v>25</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>1174597131085402112</t>
+          <t>1098070146307002368</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-地铁站-云南路地铁站渗透</t>
+          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="M50" s="8" t="inlineStr">
-        <is>
-          <t>17☂</t>
-        </is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="N50" s="10" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>998560699433394176</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>广志路南京万达茂投放点D</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -15853,104 +15971,110 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F51" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G51" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H51" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L51" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M51" s="7" t="n">
-        <v>0</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="N51" s="10" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>e5189cd954054116aa19db28790cc606</t>
+          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-高新地铁站-30</t>
+          <t>中山东路228号新世纪广场A幢投放点</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H52" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>41</v>
+        <v>183</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L52" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M52" s="9" t="n">
-        <v>41</v>
+      <c r="M52" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="N52" s="10" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>1123869816929062912</t>
+          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>六合大道南京葛塘汽车客运站投放点A</t>
+          <t>大行宫6号口渗透</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -15962,101 +16086,107 @@
         <v>30</v>
       </c>
       <c r="F53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G53" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H53" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>25</v>
+        <v>158</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L53" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M53" s="9" t="n">
-        <v>25</v>
+      <c r="M53" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="N53" s="10" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>1174593029863960576</t>
+          <t>1176722757207629824</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>25-全天-高校-师范大学渗透</t>
+          <t>规划建设展览馆渗透</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H54" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L54" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="M54" s="7" t="n">
-        <v>0</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="N54" s="10" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>1153706342168625152</t>
+          <t>816513511474413568</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>鼓楼东南大学渗透</t>
+          <t>熊猫</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -16065,51 +16195,54 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G55" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H55" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M55" s="10" t="n">
-        <v>16</v>
+        <v>43</v>
+      </c>
+      <c r="N55" s="10" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>1206515660536758272</t>
+          <t>0a83fddcl1ln2kvc5pnasw3i47tp2gxk</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>南京邮电大学渗透</t>
+          <t>中新大道投放点D</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -16121,25 +16254,25 @@
         <v>15</v>
       </c>
       <c r="F56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G56" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H56" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L56" s="7" t="n">
@@ -16148,21 +16281,24 @@
       <c r="M56" s="10" t="n">
         <v>22</v>
       </c>
+      <c r="N56" s="10" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>1098070146307002368</t>
+          <t>0a83a497l1lumz6c4kkm73jypiiknrwb</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
+          <t>中新大道南京气象局投放点</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -16171,51 +16307,54 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G57" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H57" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="10" t="n">
-        <v>56</v>
+        <v>20</v>
+      </c>
+      <c r="N57" s="10" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>998560699433394176</t>
+          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>广志路南京万达茂投放点D</t>
+          <t>中和路阿里中心·南京投放点A</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -16224,210 +16363,222 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G58" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H58" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L58" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M58" s="10" t="n">
-        <v>39</v>
+        <v>15</v>
+      </c>
+      <c r="N58" s="10" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
+          <t>0a83933al1lzugykf9cbvd6hi2rqf8qn</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>中山东路228号新世纪广场A幢投放点</t>
+          <t>环岛东路投放点C</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H59" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="10" t="n">
-        <v>83</v>
+        <v>15</v>
+      </c>
+      <c r="N59" s="10" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
+          <t>724131086902996992</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>大行宫6号口渗透</t>
+          <t>迈皋桥公交场站渗透</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G60" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H60" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L60" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M60" s="10" t="n">
-        <v>98</v>
+        <v>57</v>
+      </c>
+      <c r="N60" s="10" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>1176722757207629824</t>
+          <t>0a83a497l1lj8cs3vsnr7r56rr3rgrgj</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>规划建设展览馆渗透</t>
+          <t>新浦路投放点B</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G61" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G61" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H61" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="10" t="n">
-        <v>111</v>
+        <v>62</v>
+      </c>
+      <c r="N61" s="10" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>816513511474413568</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>熊猫</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -16436,51 +16587,54 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="10" t="n">
-        <v>43</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="M62" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="N62" s="9" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>0a83fddcl1ln2kvc5pnasw3i47tp2gxk</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>中新大道投放点D</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -16489,51 +16643,54 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="F63" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L63" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="10" t="n">
-        <v>22</v>
+      <c r="M63" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N63" s="9" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lumz6c4kkm73jypiiknrwb</t>
+          <t>594063e60b264e419feea65370752c3f</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>中新大道南京气象局投放点</t>
+          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -16542,51 +16699,54 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="10" t="n">
-        <v>20</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="M64" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N64" s="9" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
+          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>中和路阿里中心·南京投放点A</t>
+          <t>淮海路远洋国际中心投放点A</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -16595,169 +16755,178 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="10" t="n">
-        <v>15</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="M65" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="N65" s="9" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>939772435800334336</t>
+          <t>854196782092722176</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区江心洲街道红星街洲岛家园</t>
+          <t>工作日-全天-居民区-好的渗透</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="10" t="n">
-        <v>18</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="M66" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="N66" s="9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>0a83933al1lzugykf9cbvd6hi2rqf8qn</t>
+          <t>3a7505a7b50d415583454f997bbdbf0e</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>环岛东路投放点C</t>
+          <t>六合区宁六路54号</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L67" s="7" t="n">
-        <v>0</v>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="n">
+        <v>25</v>
       </c>
       <c r="M67" s="10" t="n">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="N67" s="9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>724131086902996992</t>
+          <t>778851422965239808</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>迈皋桥公交场站渗透</t>
+          <t>25-早峰-居民区-仙林新村</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>1</v>
@@ -16766,51 +16935,58 @@
         <v>1</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="10" t="n">
-        <v>57</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>23☂</t>
+        </is>
+      </c>
+      <c r="M68" s="8" t="inlineStr">
+        <is>
+          <t>24☂</t>
+        </is>
+      </c>
+      <c r="N68" s="10" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lj8cs3vsnr7r56rr3rgrgj</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>新浦路投放点B</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>1</v>
@@ -16819,60 +16995,67 @@
         <v>1</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L69" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="10" t="n">
-        <v>62</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L69" s="8" t="inlineStr">
+        <is>
+          <t>11☂</t>
+        </is>
+      </c>
+      <c r="M69" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>788321551519383552</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>玄武区鹤鸣路37号</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -16881,51 +17064,58 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L70" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="M70" s="9" t="n">
-        <v>22</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L70" s="8" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="inlineStr">
+        <is>
+          <t>16☂</t>
+        </is>
+      </c>
+      <c r="N70" s="10" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>30</v>
+        <v>107</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -16934,30 +17124,33 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L71" s="9" t="n">
-        <v>15</v>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L71" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="M71" s="9" t="n">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="N71" s="9" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>594063e60b264e419feea65370752c3f</t>
+          <t>1174624598576300032</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
+          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -16966,46 +17159,49 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G72" s="3" t="n">
+      <c r="M72" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L72" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="M72" s="9" t="n">
-        <v>10</v>
+      <c r="N72" s="10" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>1174624598576300032</t>
+          <t>1174618792617238528</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
+          <t>南京市秦淮区朝天宫街道建邺路建邺路住宅小区</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -17015,23 +17211,23 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -17040,51 +17236,58 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L73" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M73" s="9" t="n">
-        <v>2</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L73" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="M73" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="N73" s="10" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
+          <t>854249531796738048</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>淮海路远洋国际中心投放点A</t>
+          <t>25-全天-地铁站-金马路地铁站</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -17093,51 +17296,58 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L74" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="M74" s="9" t="n">
-        <v>20</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L74" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="M74" s="8" t="inlineStr">
+        <is>
+          <t>31☂</t>
+        </is>
+      </c>
+      <c r="N74" s="10" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>854196782092722176</t>
+          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-居民区-好的渗透</t>
+          <t>钟灵街2A</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -17146,51 +17356,58 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L75" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="M75" s="9" t="n">
-        <v>20</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>15☂</t>
+        </is>
+      </c>
+      <c r="M75" s="8" t="inlineStr">
+        <is>
+          <t>25☂</t>
+        </is>
+      </c>
+      <c r="N75" s="10" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
+          <t>948393128847777792</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>鼓楼区童家山2-3号楼</t>
+          <t>30-工作日-全天-地铁-明故宫2渗透</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -17199,51 +17416,54 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L76" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="M76" s="9" t="n">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="M76" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="N76" s="9" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>554207268614606848</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>55</v>
+        <v>189</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -17252,30 +17472,37 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L77" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="M77" s="9" t="n">
-        <v>31</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L77" s="8" t="inlineStr">
+        <is>
+          <t>42☂</t>
+        </is>
+      </c>
+      <c r="M77" s="8" t="inlineStr">
+        <is>
+          <t>76☂</t>
+        </is>
+      </c>
+      <c r="N77" s="10" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>3a7505a7b50d415583454f997bbdbf0e</t>
+          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>六合区宁六路54号</t>
+          <t>鼓楼区童家山2-3号楼</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -17284,19 +17511,19 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -17305,30 +17532,33 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L78" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="M78" s="10" t="n">
-        <v>36</v>
+        <v>9</v>
+      </c>
+      <c r="M78" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N78" s="10" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>1153706291117858816</t>
+          <t>554207268614606848</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
+          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -17340,16 +17570,16 @@
         <v>50</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -17358,30 +17588,33 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L79" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="M79" s="10" t="n">
-        <v>167</v>
+        <v>24</v>
+      </c>
+      <c r="M79" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="N79" s="10" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
+          <t>1098069901166710784</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
+          <t>25-全天-地铁站-工业大学地铁站2号口渗透</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -17390,19 +17623,19 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -17411,51 +17644,54 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L80" s="10" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="M80" s="9" t="n">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="N80" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>0a83612el1l7zifsq9sdudan8qjz6v28</t>
+          <t>1174597131085402112</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>中华路夫子庙秦淮风光带投放点G</t>
+          <t>25-早峰-地铁站-云南路地铁站渗透</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -17464,30 +17700,37 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L81" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="M81" s="10" t="n">
-        <v>17</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L81" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="M81" s="8" t="inlineStr">
+        <is>
+          <t>17☂</t>
+        </is>
+      </c>
+      <c r="N81" s="10" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>732956028185985024</t>
+          <t>1153706291117858816</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>下马坊地铁站</t>
+          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -17496,19 +17739,19 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H82" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G82" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H82" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I82" s="3" t="n">
-        <v>75</v>
+        <v>342</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -17517,30 +17760,33 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L82" s="9" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="M82" s="10" t="n">
-        <v>50</v>
+        <v>167</v>
+      </c>
+      <c r="N82" s="10" t="n">
+        <v>161</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>0a838699l1lzri8zeup3f4zan2nxpmck</t>
+          <t>0a83612el1l7zifsq9sdudan8qjz6v28</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>童卫路南理工科技创新园投放点</t>
+          <t>中华路夫子庙秦淮风光带投放点G</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -17549,19 +17795,19 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F83" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G83" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I83" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -17570,30 +17816,33 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L83" s="9" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="M83" s="10" t="n">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="N83" s="10" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>948393128847777792</t>
+          <t>732956028185985024</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>30-工作日-全天-地铁-明故宫2渗透</t>
+          <t>下马坊地铁站</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -17602,19 +17851,19 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H84" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G84" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I84" s="3" t="n">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -17623,30 +17872,33 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L84" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M84" s="10" t="n">
-        <v>41</v>
+        <v>50</v>
+      </c>
+      <c r="N84" s="10" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>1206467184454987776</t>
+          <t>0a838699l1lzri8zeup3f4zan2nxpmck</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
+          <t>童卫路南理工科技创新园投放点</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -17655,19 +17907,19 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F85" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H85" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G85" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I85" s="3" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -17676,51 +17928,54 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L85" s="10" t="n">
-        <v>46</v>
-      </c>
-      <c r="M85" s="9" t="n">
-        <v>18</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L85" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="M85" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="N85" s="10" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>1098069901166710784</t>
+          <t>857508296047517696</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-工业大学地铁站2号口渗透</t>
+          <t>钟灵街2b</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H86" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G86" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I86" s="3" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -17729,30 +17984,33 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L86" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="M86" s="9" t="n">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="M86" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="N86" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>554207268778184704</t>
+          <t>852043013396557824</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路3号口</t>
+          <t>玄武区长江路108号</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -17761,19 +18019,19 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H87" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -17782,30 +18040,33 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L87" s="10" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="M87" s="10" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="N87" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
+          <t>1206467184454987776</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁口-仙林中心站1号口</t>
+          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -17814,19 +18075,19 @@
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>362</v>
+        <v>102</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -17835,30 +18096,33 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L88" s="10" t="n">
-        <v>153</v>
-      </c>
-      <c r="M88" s="10" t="n">
-        <v>209</v>
+        <v>46</v>
+      </c>
+      <c r="M88" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="N88" s="10" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>584636981105418240</t>
+          <t>554207268778184704</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-羊山公园2号口</t>
+          <t>25-晚峰-地铁站-柳州东路3号口</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -17870,16 +18134,16 @@
         <v>50</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -17892,21 +18156,24 @@
         </is>
       </c>
       <c r="L89" s="10" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="M89" s="10" t="n">
-        <v>146</v>
+        <v>55</v>
+      </c>
+      <c r="N89" s="10" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>1123869911569338368</t>
+          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>学衡路南京师范大学仙林校区投放点B</t>
+          <t>25-全天-地铁口-仙林中心站1号口</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -17916,23 +18183,23 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>70</v>
+        <v>577</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -17945,47 +18212,50 @@
         </is>
       </c>
       <c r="L90" s="10" t="n">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="M90" s="10" t="n">
-        <v>47</v>
+        <v>209</v>
+      </c>
+      <c r="N90" s="10" t="n">
+        <v>215</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>1174621727109263360</t>
+          <t>584636981105418240</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
+          <t>25-全天-地铁-羊山公园2号口</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>97</v>
+        <v>415</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -17998,47 +18268,50 @@
         </is>
       </c>
       <c r="L91" s="10" t="n">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="M91" s="10" t="n">
-        <v>43</v>
+        <v>146</v>
+      </c>
+      <c r="N91" s="10" t="n">
+        <v>185</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
+          <t>1123869911569338368</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>石门坎地铁站3号口光华科技产业园投放点</t>
+          <t>学衡路南京师范大学仙林校区投放点B</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -18051,47 +18324,50 @@
         </is>
       </c>
       <c r="L92" s="10" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="M92" s="10" t="n">
-        <v>40</v>
+        <v>47</v>
+      </c>
+      <c r="N92" s="10" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>816505037427507200</t>
+          <t>1174621727109263360</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>玄武区童卫路28-2号</t>
+          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -18104,26 +18380,29 @@
         </is>
       </c>
       <c r="L93" s="10" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M93" s="10" t="n">
-        <v>81</v>
+        <v>43</v>
+      </c>
+      <c r="N93" s="10" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>857508296047517696</t>
+          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2b</t>
+          <t>石门坎地铁站3号口光华科技产业园投放点</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -18135,16 +18414,16 @@
         <v>20</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -18157,26 +18436,29 @@
         </is>
       </c>
       <c r="L94" s="10" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="M94" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="N94" s="10" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>852043013396557824</t>
+          <t>816505037427507200</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>玄武区长江路108号</t>
+          <t>玄武区童卫路28-2号</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -18185,19 +18467,19 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -18210,10 +18492,13 @@
         </is>
       </c>
       <c r="L95" s="10" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="M95" s="10" t="n">
-        <v>56</v>
+        <v>81</v>
+      </c>
+      <c r="N95" s="10" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="96">
@@ -18241,16 +18526,16 @@
         <v>15</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -18267,6 +18552,9 @@
       </c>
       <c r="M96" s="10" t="n">
         <v>31</v>
+      </c>
+      <c r="N96" s="10" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -21693,7 +21981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -21709,6 +21997,7 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21784,6 +22073,11 @@
           <t>07-05(日)</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>07-11(六)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -21810,7 +22104,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -21835,18 +22129,21 @@
         <v>0</v>
       </c>
       <c r="M3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>0a898873l1l2z5yttrk27pq8kwxsxux8</t>
+          <t>0a8398f6l1lgcmyt8mtjtxnw4bwhwj4b</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>高新-小区-瑾家珑熹台（南1门）</t>
+          <t>高新-地铁-交院地铁站2号口a</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -21863,7 +22160,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -21888,18 +22185,21 @@
         <v>0</v>
       </c>
       <c r="M4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>0a8398f6l1lgcmyt8mtjtxnw4bwhwj4b</t>
+          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>高新-地铁-交院地铁站2号口a</t>
+          <t>龙眠大道海丰小视科技中心(建设中)站点</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -21916,7 +22216,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -21941,18 +22241,21 @@
         <v>0</v>
       </c>
       <c r="M5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
+          <t>0a83a414l1l7iaxy7ybfmcgce27jr5vm</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道海丰小视科技中心(建设中)站点</t>
+          <t>修文路保利·梧桐语站点Z18</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -21969,7 +22272,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -21994,23 +22297,26 @@
         <v>0</v>
       </c>
       <c r="M6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1l7iaxy7ybfmcgce27jr5vm</t>
+          <t>893749163098365952</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>修文路保利·梧桐语站点Z18</t>
+          <t>玉堂巷2-1号小里新寓站点A</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -22022,7 +22328,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -22047,23 +22353,26 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>893749163098365952</t>
+          <t>0a8339f4l1lh4xmtqcvwzga6zi8snxmx</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>玉堂巷2-1号小里新寓站点A</t>
+          <t>灵谷寺4</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -22072,10 +22381,10 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -22100,23 +22409,26 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>893750907107000320</t>
+          <t>0a898873l1l2z5yttrk27pq8kwxsxux8</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>新医路27-2号小里新寓站点</t>
+          <t>高新-小区-瑾家珑熹台（南1门）</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -22128,25 +22440,25 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L9" s="7" t="n">
@@ -22154,17 +22466,20 @@
       </c>
       <c r="M9" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>893715809572151296</t>
+          <t>893750907107000320</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>土山路华意泰富花苑站点A</t>
+          <t>新医路27-2号小里新寓站点</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -22181,25 +22496,25 @@
         <v>11</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L10" s="7" t="n">
@@ -22207,22 +22522,25 @@
       </c>
       <c r="M10" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
+          <t>893715809572151296</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>竹山路地铁1号口</t>
+          <t>土山路华意泰富花苑站点A</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -22234,25 +22552,25 @@
         <v>11</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L11" s="7" t="n">
@@ -22260,17 +22578,20 @@
       </c>
       <c r="M11" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lyxfkh7vjgmkyih6st4gkb</t>
+          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>经贸学院路保利·樾广场站点A</t>
+          <t>竹山路地铁1号口</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -22287,25 +22608,25 @@
         <v>11</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L12" s="7" t="n">
@@ -22313,74 +22634,76 @@
       </c>
       <c r="M12" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>1158025287508230144</t>
+          <t>0a83a414l1lyxfkh7vjgmkyih6st4gkb</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>3号门</t>
+          <t>经贸学院路保利·樾广场站点A</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>374</v>
+        <v>11</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>220☂</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>154☂</t>
-        </is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0a8339f4l1lh4xmtqcvwzga6zi8snxmx</t>
+          <t>1158030564174917632</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺4</t>
+          <t>东山头</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -22397,25 +22720,25 @@
         <v>10</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L14" s="7" t="n">
@@ -22423,22 +22746,25 @@
       </c>
       <c r="M14" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1158030564174917632</t>
+          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>东山头</t>
+          <t>鹏山路东方·龙湖湾站点Z2</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -22447,46 +22773,49 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="n">
-        <v>0</v>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
+          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>鹏山路东方·龙湖湾站点Z2</t>
+          <t>高新-小区-瑾家珑熹台（南2门）</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -22503,48 +22832,51 @@
         <v>11</v>
       </c>
       <c r="F16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="n">
-        <v>8</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>35</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
+          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>高新-小区-瑾家珑熹台（南2门）</t>
+          <t>土山路东域城站点A</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -22556,48 +22888,51 @@
         <v>11</v>
       </c>
       <c r="F17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L17" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
+          <t>1158025279480332288</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>土山路东域城站点A</t>
+          <t>2号门</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -22606,72 +22941,75 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="n">
-        <v>0</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>44</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>12</v>
+        <v>44</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
+          <t>1158025287508230144</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>严南路金辉禹洲金陵铭著站点A</t>
+          <t>3号门</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>28</v>
+        <v>492</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -22680,25 +23018,32 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L19" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="M19" s="9" t="n">
-        <v>10</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>220☂</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>154☂</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>118</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
+          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>胜太西路太平花苑北苑站点C</t>
+          <t>严南路金辉禹洲金陵铭著站点A</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -22715,16 +23060,16 @@
         <v>11</v>
       </c>
       <c r="F20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I20" s="3" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -22733,25 +23078,28 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="n">
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="M20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="M20" s="10" t="n">
-        <v>11</v>
+      <c r="N20" s="10" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
+          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>胜太西路天琪雅居站点</t>
+          <t>胜太西路太平花苑北苑站点C</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -22768,16 +23116,16 @@
         <v>11</v>
       </c>
       <c r="F21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I21" s="3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -22786,25 +23134,28 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L21" s="9" t="n">
         <v>10</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>26</v>
+        <v>11</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
+          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>平泰街太平花苑站点</t>
+          <t>胜太西路天琪雅居站点</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -22821,16 +23172,16 @@
         <v>11</v>
       </c>
       <c r="F22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I22" s="3" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -22839,30 +23190,33 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L22" s="9" t="n">
         <v>10</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>889665664809402368</t>
+          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科南门C</t>
+          <t>平泰街太平花苑站点</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -22874,16 +23228,16 @@
         <v>11</v>
       </c>
       <c r="F23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I23" s="3" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -22892,30 +23246,33 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="M23" s="9" t="n">
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="n">
         <v>10</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>889466722646794240</t>
+          <t>889665664809402368</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>胜太东路江宁供销商厦站点</t>
+          <t>高新-高校-金科南门C</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -22927,16 +23284,16 @@
         <v>11</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I24" s="3" t="n">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -22945,30 +23302,33 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" s="10" t="n">
-        <v>12</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
+          <t>889466722646794240</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>胜太西路47号汇金新天地广场站点</t>
+          <t>胜太东路江宁供销商厦站点</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -22980,16 +23340,16 @@
         <v>11</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -22998,25 +23358,28 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L25" s="10" t="n">
-        <v>22</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>45</v>
+        <v>12</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
+          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>胜太西路45号汇金新天地广场站点</t>
+          <t>胜太西路47号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -23033,16 +23396,16 @@
         <v>11</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -23055,21 +23418,24 @@
         </is>
       </c>
       <c r="L26" s="10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M26" s="10" t="n">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="N26" s="10" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>0a838de0l1lnurtzrb4hnycbdpmcz7tn</t>
+          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>吉印大道东南大学(九龙湖校区)站点H</t>
+          <t>胜太西路45号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -23086,16 +23452,16 @@
         <v>11</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>215</v>
+        <v>63</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -23108,21 +23474,24 @@
         </is>
       </c>
       <c r="L27" s="10" t="n">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
+          <t>0a838de0l1lnurtzrb4hnycbdpmcz7tn</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>吉印大道融信·铂岸中心站点</t>
+          <t>吉印大道东南大学(九龙湖校区)站点H</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -23139,16 +23508,16 @@
         <v>11</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>26</v>
+        <v>296</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -23161,21 +23530,24 @@
         </is>
       </c>
       <c r="L28" s="10" t="n">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v>13</v>
+        <v>56</v>
+      </c>
+      <c r="N28" s="10" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
+          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
+          <t>吉印大道融信·铂岸中心站点</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -23192,43 +23564,46 @@
         <v>11</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N29" s="10" t="n">
         <v>36</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L29" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="M29" s="10" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
+          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
+          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -23245,16 +23620,16 @@
         <v>11</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -23267,26 +23642,29 @@
         </is>
       </c>
       <c r="L30" s="10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="N30" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>897042860272709632</t>
+          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>鹏山路中粮悦天地(建设中)站点B</t>
+          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -23298,16 +23676,16 @@
         <v>11</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -23320,21 +23698,24 @@
         </is>
       </c>
       <c r="L31" s="10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M31" s="10" t="n">
-        <v>22</v>
+        <v>11</v>
+      </c>
+      <c r="N31" s="10" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>897053191954571264</t>
+          <t>897042860272709632</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>知行路中粮悦天地(建设中)站点F</t>
+          <t>鹏山路中粮悦天地(建设中)站点B</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -23351,16 +23732,16 @@
         <v>11</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -23373,26 +23754,29 @@
         </is>
       </c>
       <c r="L32" s="10" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M32" s="10" t="n">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="N32" s="10" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>1158030570667700224</t>
+          <t>897053191954571264</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>美龄宫</t>
+          <t>知行路中粮悦天地(建设中)站点F</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -23401,19 +23785,19 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>832</v>
+        <v>104</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -23426,21 +23810,24 @@
         </is>
       </c>
       <c r="L33" s="10" t="n">
-        <v>436</v>
+        <v>11</v>
       </c>
       <c r="M33" s="10" t="n">
-        <v>396</v>
+        <v>38</v>
+      </c>
+      <c r="N33" s="10" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>1158030572869709824</t>
+          <t>1158030570667700224</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>东沟停车场</t>
+          <t>美龄宫</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -23457,16 +23844,16 @@
         <v>50</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>759</v>
+        <v>1387</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -23479,21 +23866,24 @@
         </is>
       </c>
       <c r="L34" s="10" t="n">
-        <v>341</v>
+        <v>436</v>
       </c>
       <c r="M34" s="10" t="n">
-        <v>418</v>
+        <v>396</v>
+      </c>
+      <c r="N34" s="10" t="n">
+        <v>555</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>1158030569614929920</t>
+          <t>1158030572869709824</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>海底世界站台</t>
+          <t>东沟停车场</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -23510,16 +23900,16 @@
         <v>50</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>342</v>
+        <v>1315</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -23532,21 +23922,24 @@
         </is>
       </c>
       <c r="L35" s="10" t="n">
-        <v>143</v>
+        <v>341</v>
       </c>
       <c r="M35" s="10" t="n">
-        <v>199</v>
+        <v>418</v>
+      </c>
+      <c r="N35" s="10" t="n">
+        <v>556</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>1158030573943451648</t>
+          <t>1158030569614929920</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>中山陵7号门</t>
+          <t>海底世界站台</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -23560,19 +23953,19 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>264</v>
+        <v>485</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -23585,21 +23978,24 @@
         </is>
       </c>
       <c r="L36" s="10" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="M36" s="10" t="n">
-        <v>132</v>
+        <v>199</v>
+      </c>
+      <c r="N36" s="10" t="n">
+        <v>143</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>1158030568570548224</t>
+          <t>1158030573943451648</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>海底世界</t>
+          <t>中山陵7号门</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -23616,16 +24012,16 @@
         <v>15</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>131</v>
+        <v>340</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -23638,21 +24034,24 @@
         </is>
       </c>
       <c r="L37" s="10" t="n">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>66</v>
+        <v>132</v>
+      </c>
+      <c r="N37" s="10" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>1158030571808550912</t>
+          <t>1158030568570548224</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>1号门</t>
+          <t>海底世界</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -23666,19 +24065,19 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -23691,21 +24090,24 @@
         </is>
       </c>
       <c r="L38" s="10" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="M38" s="10" t="n">
-        <v>33</v>
+        <v>66</v>
+      </c>
+      <c r="N38" s="10" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>1158025279480332288</t>
+          <t>1158030571808550912</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>2号门</t>
+          <t>1号门</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -23722,16 +24124,16 @@
         <v>10</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -23744,10 +24146,13 @@
         </is>
       </c>
       <c r="L39" s="10" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>44</v>
+        <v>33</v>
+      </c>
+      <c r="N39" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -24184,22 +24589,22 @@
         <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -24213,22 +24618,22 @@
         <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -24242,7 +24647,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -24271,22 +24676,22 @@
         <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="E6" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -24300,22 +24705,22 @@
         <v>26</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
     </row>
@@ -24329,22 +24734,22 @@
         <v>9</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -24358,22 +24763,22 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -24387,22 +24792,22 @@
         <v>13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
     </row>
@@ -24416,22 +24821,22 @@
         <v>3</v>
       </c>
       <c r="C11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -24445,22 +24850,22 @@
         <v>9</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
     </row>
@@ -24753,13 +25158,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -24768,7 +25173,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
@@ -24782,22 +25187,22 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -24811,22 +25216,22 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>40.0%</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -24840,22 +25245,22 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -24869,22 +25274,22 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -591,12 +591,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
     </row>
@@ -654,14 +654,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20260701 ~ 20260711</t>
+          <t>数据范围: 20260701 ~ 20260712</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 8天, 周末: 3天</t>
+          <t>工作日: 8天, 周末: 4天</t>
         </is>
       </c>
     </row>
@@ -13163,7 +13163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N96"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13180,6 +13180,7 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13260,6 +13261,11 @@
           <t>07-11(六)</t>
         </is>
       </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>07-12(日)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -13286,7 +13292,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -13314,6 +13320,9 @@
         <v>0</v>
       </c>
       <c r="N3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13372,6 +13381,11 @@
       <c r="N4" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -13428,6 +13442,11 @@
       <c r="N5" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -13454,7 +13473,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -13482,6 +13501,9 @@
         <v>0</v>
       </c>
       <c r="N6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13540,6 +13562,11 @@
       <c r="N7" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -13596,6 +13623,11 @@
       <c r="N8" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -13652,6 +13684,11 @@
       <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -13678,7 +13715,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -13706,6 +13743,9 @@
         <v>0</v>
       </c>
       <c r="N10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13764,6 +13804,11 @@
       <c r="N11" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -13820,51 +13865,56 @@
       <c r="N12" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lbekztkg9bb795bdwjee85</t>
+          <t>813294194703020032</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>天润城地铁站2号口天润城十一街区投放点A</t>
+          <t>打钉巷金鼎湾国际投放点</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L13" s="7" t="n">
@@ -13873,54 +13923,57 @@
       <c r="M13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="9" t="n">
-        <v>8</v>
+      <c r="N13" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>684268350256898048</t>
+          <t>1174627346911133696</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-学则路</t>
+          <t>南京市秦淮区洪武路街道户部街长发银座</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L14" s="7" t="n">
@@ -13929,54 +13982,57 @@
       <c r="M14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="9" t="n">
-        <v>23</v>
+      <c r="N14" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
+          <t>1174622729575776256</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
+          <t>南京市秦淮区常府街地铁站3号口</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L15" s="7" t="n">
@@ -13985,19 +14041,22 @@
       <c r="M15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="9" t="n">
-        <v>17</v>
+      <c r="N15" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1150704239247155200</t>
+          <t>0a836146l1lm5w7r6duyverna8nzapss</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带A</t>
+          <t>中山东路南京航空航天大学(明故宫校区)投放点B</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -14007,32 +14066,32 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L16" s="7" t="n">
@@ -14041,24 +14100,27 @@
       <c r="M16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="9" t="n">
-        <v>15</v>
+      <c r="N16" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1174535930061524992</t>
+          <t>0a836587l1lbekztkg9bb795bdwjee85</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
+          <t>天润城地铁站2号口天润城十一街区投放点A</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -14067,7 +14129,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>3</v>
@@ -14079,7 +14141,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -14098,23 +14160,28 @@
         <v>0</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>754365148238000128</t>
+          <t>684268350256898048</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>玄武区四牌楼63号</t>
+          <t>25-全天-地铁-学则路</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -14123,7 +14190,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>3</v>
@@ -14135,7 +14202,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -14154,23 +14221,28 @@
         <v>0</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l2ehxa2pgziwbi3i3kp6ct</t>
+          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>红山路辅路常发广场投放点B</t>
+          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -14179,7 +14251,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>3</v>
@@ -14191,7 +14263,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -14210,32 +14282,37 @@
         <v>0</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1lyau4xnzsbvbjunbxguey8</t>
+          <t>1150704239247155200</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>浦珠南路南京工业大学江浦校区投放点A</t>
+          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带A</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>3</v>
@@ -14247,7 +14324,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -14266,23 +14343,28 @@
         <v>0</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1153706318256898048</t>
+          <t>1174535930061524992</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>浦口大道投放点渗透</t>
+          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -14291,7 +14373,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>3</v>
@@ -14303,7 +14385,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -14322,23 +14404,28 @@
         <v>0</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>0a8331f1l1ld9wgam59z73ha4yn6qxdr</t>
+          <t>754365148238000128</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>镇南河路东方万汇城投放点E</t>
+          <t>玄武区四牌楼63号</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -14347,7 +14434,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>3</v>
@@ -14359,7 +14446,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -14378,23 +14465,28 @@
         <v>0</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a83d1c7l1lae4s7r5hq76dmaivv9ibv</t>
+          <t>0a836587l1l2ehxa2pgziwbi3i3kp6ct</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>迎江路玖印府(建设中)投放点</t>
+          <t>红山路辅路常发广场投放点B</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -14415,7 +14507,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -14434,23 +14526,28 @@
         <v>0</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>24</v>
+        <v>2</v>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>732956182771253248</t>
+          <t>1153706318256898048</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>25-全天-商超-金茂汇渗透</t>
+          <t>浦口大道投放点渗透</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -14459,7 +14556,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>3</v>
@@ -14468,10 +14565,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -14480,7 +14577,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
@@ -14489,24 +14586,29 @@
       <c r="M24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="10" t="n">
-        <v>29</v>
+      <c r="N24" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>5☂</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
+          <t>0a8331f1l1ld9wgam59z73ha4yn6qxdr</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>九家圩路世茂外滩新城投放点A</t>
+          <t>镇南河路东方万汇城投放点E</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -14515,7 +14617,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>3</v>
@@ -14524,10 +14626,10 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -14536,7 +14638,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L25" s="7" t="n">
@@ -14545,24 +14647,29 @@
       <c r="M25" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="10" t="n">
-        <v>17</v>
+      <c r="N25" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>19☂</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>1176842717252255744</t>
+          <t>0a83d1c7l1lae4s7r5hq76dmaivv9ibv</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>三元巷6号三元公寓投放点渗透</t>
+          <t>迎江路玖印府(建设中)投放点</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -14571,7 +14678,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>3</v>
@@ -14580,10 +14687,10 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -14592,7 +14699,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
@@ -14601,33 +14708,38 @@
       <c r="M26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="10" t="n">
-        <v>20</v>
+      <c r="N26" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>5☂</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>813294194703020032</t>
+          <t>732956182771253248</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>打钉巷金鼎湾国际投放点</t>
+          <t>25-全天-商超-金茂汇渗透</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>3</v>
@@ -14639,7 +14751,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -14658,32 +14770,37 @@
         <v>0</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>1174627346911133696</t>
+          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道户部街长发银座</t>
+          <t>九家圩路世茂外滩新城投放点A</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>3</v>
@@ -14695,7 +14812,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -14714,18 +14831,23 @@
         <v>0</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>732955142450266112</t>
+          <t>1176842717252255744</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
+          <t>三元巷6号三元公寓投放点渗透</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -14735,11 +14857,11 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>3</v>
@@ -14751,7 +14873,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -14770,18 +14892,23 @@
         <v>0</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>1174622729575776256</t>
+          <t>1174535134415278080</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区常府街地铁站3号口</t>
+          <t>南京市秦淮区夫子庙街道箍桶巷夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -14791,11 +14918,11 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>3</v>
@@ -14807,7 +14934,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -14826,7 +14953,12 @@
         <v>0</v>
       </c>
       <c r="N30" s="10" t="n">
-        <v>20</v>
+        <v>49</v>
+      </c>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -14851,7 +14983,7 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>3</v>
@@ -14884,16 +15016,21 @@
       <c r="N31" s="10" t="n">
         <v>49</v>
       </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>1174535134415278080</t>
+          <t>0a838699l1lyun3by28du7fus2rjdmuu</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道箍桶巷夫子庙秦淮风光带</t>
+          <t>剪子巷40号夫子庙秦淮风光带投放点</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -14907,7 +15044,7 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>3</v>
@@ -14919,7 +15056,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -14938,18 +15075,23 @@
         <v>0</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>49</v>
+        <v>16</v>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1lm5w7r6duyverna8nzapss</t>
+          <t>0a83a497l1ldsbrxkzcxei46ckdztk7h</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>中山东路南京航空航天大学(明故宫校区)投放点B</t>
+          <t>中山南路91号江苏文化大厦投放点A</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -14959,7 +15101,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
@@ -14975,7 +15117,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -14994,18 +15136,23 @@
         <v>0</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>0a838699l1lyun3by28du7fus2rjdmuu</t>
+          <t>874549501386596352</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>剪子巷40号夫子庙秦淮风光带投放点</t>
+          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -15019,7 +15166,7 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>3</v>
@@ -15031,7 +15178,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -15050,18 +15197,23 @@
         <v>0</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="O34" s="8" t="inlineStr">
+        <is>
+          <t>19☂</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1ldsbrxkzcxei46ckdztk7h</t>
+          <t>0a838e37l1ls23rim2x3aaf2bwvtsyi2</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>中山南路91号江苏文化大厦投放点A</t>
+          <t>秦淮区红花街道卡子门地铁站</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -15075,7 +15227,7 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>3</v>
@@ -15087,7 +15239,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -15106,23 +15258,28 @@
         <v>0</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>37☂</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>874549501386596352</t>
+          <t>849243610630791168</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
+          <t>25-早峰-地铁-马群站</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -15143,7 +15300,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -15162,23 +15319,28 @@
         <v>0</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>0a838e37l1ls23rim2x3aaf2bwvtsyi2</t>
+          <t>939772435800334336</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>秦淮区红花街道卡子门地铁站</t>
+          <t>南京市建邺区江心洲街道红星街洲岛家园</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -15199,7 +15361,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -15214,27 +15376,32 @@
       <c r="L37" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="10" t="n">
-        <v>17</v>
+      <c r="M37" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>849243610630791168</t>
+          <t>1206516292750213120</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-地铁-马群站</t>
+          <t>中山北路宏图大厦渗透</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -15243,7 +15410,7 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>3</v>
@@ -15255,7 +15422,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -15274,18 +15441,23 @@
         <v>0</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="O38" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>939772435800334336</t>
+          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区江心洲街道红星街洲岛家园</t>
+          <t>集贤路鼓楼创新广场投放点B</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -15311,7 +15483,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -15326,27 +15498,32 @@
       <c r="L39" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="N39" s="7" t="n">
-        <v>0</v>
+      <c r="M39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>1206516292750213120</t>
+          <t>0a836587l1l7hr5eaanydw8fnf2xk6r4</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>中山北路宏图大厦渗透</t>
+          <t>张家村东方万汇城投放点</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -15355,7 +15532,7 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>3</v>
@@ -15367,7 +15544,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -15386,74 +15563,82 @@
         <v>0</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="O40" s="8" t="inlineStr">
+        <is>
+          <t>7☂</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
+          <t>1123869816929062912</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>集贤路鼓楼创新广场投放点B</t>
+          <t>六合大道南京葛塘汽车客运站投放点A</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="N41" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="10" t="n">
-        <v>15</v>
+      <c r="O41" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l7hr5eaanydw8fnf2xk6r4</t>
+          <t>0a836146l1lyau4xnzsbvbjunbxguey8</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>张家村东方万汇城投放点</t>
+          <t>浦珠南路南京工业大学江浦校区投放点A</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -15463,32 +15648,32 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L42" s="7" t="n">
@@ -15497,36 +15682,39 @@
       <c r="M42" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N42" s="10" t="n">
-        <v>25</v>
+      <c r="N42" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>1110455098857938944</t>
+          <t>788321551519383552</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>浦珠南路中国海油协和石油加油站(江浦站)投放点渗透</t>
+          <t>玄武区鹤鸣路37号</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>1</v>
@@ -15535,222 +15723,246 @@
         <v>1</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="7" t="n">
-        <v>0</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t>16☂</t>
+        </is>
       </c>
       <c r="N43" s="10" t="n">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="O43" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>732955142450266112</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L44" s="9" t="n">
-        <v>8</v>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N44" s="9" t="n">
-        <v>68</v>
+      <c r="N44" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="O44" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>e5189cd954054116aa19db28790cc606</t>
+          <t>854249531796738048</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-高新地铁站-30</t>
+          <t>25-全天-地铁站-金马路地铁站</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="N45" s="9" t="n">
-        <v>40</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>31☂</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="O45" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>1123869816929062912</t>
+          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>六合大道南京葛塘汽车客运站投放点A</t>
+          <t>钟灵街2A</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="N46" s="9" t="n">
-        <v>3</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>15☂</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t>25☂</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="O46" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>1174593029863960576</t>
+          <t>1110455098857938944</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>25-全天-高校-师范大学渗透</t>
+          <t>浦珠南路中国海油协和石油加油站(江浦站)投放点渗透</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>2</v>
@@ -15759,54 +15971,57 @@
         <v>1</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L47" s="9" t="n">
-        <v>5</v>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="10" t="n">
-        <v>26</v>
+        <v>38</v>
+      </c>
+      <c r="O47" s="9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>1153706342168625152</t>
+          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>鼓楼东南大学渗透</t>
+          <t>中山东路228号新世纪广场A幢投放点</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>2</v>
@@ -15815,54 +16030,57 @@
         <v>2</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L48" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="10" t="n">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="O48" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>1206515660536758272</t>
+          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>南京邮电大学渗透</t>
+          <t>大行宫6号口渗透</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>2</v>
@@ -15871,54 +16089,57 @@
         <v>2</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="10" t="n">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="N49" s="10" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="O49" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>1098070146307002368</t>
+          <t>1176722757207629824</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
+          <t>规划建设展览馆渗透</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>2</v>
@@ -15927,42 +16148,45 @@
         <v>2</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M50" s="10" t="n">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="N50" s="10" t="n">
-        <v>84</v>
+        <v>66</v>
+      </c>
+      <c r="O50" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>998560699433394176</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>广志路南京万达茂投放点D</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -15971,7 +16195,7 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F51" s="3" t="n">
         <v>3</v>
@@ -15980,10 +16204,10 @@
         <v>2</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -15992,42 +16216,47 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="N51" s="10" t="n">
-        <v>45</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
+          <t>e5189cd954054116aa19db28790cc606</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>中山东路228号新世纪广场A幢投放点</t>
+          <t>25-晚峰-地铁站-高新地铁站-30</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>3</v>
@@ -16036,10 +16265,10 @@
         <v>2</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -16048,42 +16277,47 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L52" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M52" s="10" t="n">
-        <v>83</v>
-      </c>
-      <c r="N52" s="10" t="n">
-        <v>100</v>
+      <c r="M52" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N52" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="O52" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
+          <t>1174593029863960576</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>大行宫6号口渗透</t>
+          <t>25-全天-高校-师范大学渗透</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>3</v>
@@ -16092,10 +16326,10 @@
         <v>2</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -16104,42 +16338,47 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="10" t="n">
-        <v>98</v>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N53" s="10" t="n">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>1176722757207629824</t>
+          <t>1153706342168625152</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>规划建设展览馆渗透</t>
+          <t>鼓楼东南大学渗透</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F54" s="3" t="n">
         <v>3</v>
@@ -16151,7 +16390,7 @@
         <v>2</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>177</v>
+        <v>32</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -16167,26 +16406,31 @@
         <v>0</v>
       </c>
       <c r="M54" s="10" t="n">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>66</v>
+        <v>16</v>
+      </c>
+      <c r="O54" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>816513511474413568</t>
+          <t>1206515660536758272</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>熊猫</t>
+          <t>南京邮电大学渗透</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -16195,7 +16439,7 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F55" s="3" t="n">
         <v>3</v>
@@ -16207,7 +16451,7 @@
         <v>2</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -16223,26 +16467,31 @@
         <v>0</v>
       </c>
       <c r="M55" s="10" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="N55" s="10" t="n">
-        <v>48</v>
+        <v>25</v>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>0a83fddcl1ln2kvc5pnasw3i47tp2gxk</t>
+          <t>1098070146307002368</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>中新大道投放点D</t>
+          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -16251,7 +16500,7 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>3</v>
@@ -16263,7 +16512,7 @@
         <v>2</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -16279,26 +16528,31 @@
         <v>0</v>
       </c>
       <c r="M56" s="10" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="N56" s="10" t="n">
-        <v>35</v>
+        <v>84</v>
+      </c>
+      <c r="O56" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lumz6c4kkm73jypiiknrwb</t>
+          <t>998560699433394176</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>中新大道南京气象局投放点</t>
+          <t>广志路南京万达茂投放点D</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -16307,7 +16561,7 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>3</v>
@@ -16319,7 +16573,7 @@
         <v>2</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -16335,26 +16589,31 @@
         <v>0</v>
       </c>
       <c r="M57" s="10" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="N57" s="10" t="n">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
+          <t>816513511474413568</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>中和路阿里中心·南京投放点A</t>
+          <t>熊猫</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -16363,7 +16622,7 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F58" s="3" t="n">
         <v>3</v>
@@ -16375,7 +16634,7 @@
         <v>2</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>30</v>
+        <v>107</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -16391,21 +16650,26 @@
         <v>0</v>
       </c>
       <c r="M58" s="10" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N58" s="10" t="n">
-        <v>15</v>
+        <v>48</v>
+      </c>
+      <c r="O58" s="8" t="inlineStr">
+        <is>
+          <t>16☂</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>0a83933al1lzugykf9cbvd6hi2rqf8qn</t>
+          <t>0a83fddcl1ln2kvc5pnasw3i47tp2gxk</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>环岛东路投放点C</t>
+          <t>中新大道投放点D</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -16431,7 +16695,7 @@
         <v>2</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -16447,26 +16711,31 @@
         <v>0</v>
       </c>
       <c r="M59" s="10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N59" s="10" t="n">
-        <v>15</v>
+        <v>35</v>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>724131086902996992</t>
+          <t>0a83a497l1lumz6c4kkm73jypiiknrwb</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>迈皋桥公交场站渗透</t>
+          <t>中新大道南京气象局投放点</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -16475,7 +16744,7 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F60" s="3" t="n">
         <v>3</v>
@@ -16487,7 +16756,7 @@
         <v>2</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -16503,26 +16772,31 @@
         <v>0</v>
       </c>
       <c r="M60" s="10" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="N60" s="10" t="n">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="O60" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lj8cs3vsnr7r56rr3rgrgj</t>
+          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>新浦路投放点B</t>
+          <t>中和路阿里中心·南京投放点A</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -16531,7 +16805,7 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>3</v>
@@ -16543,7 +16817,7 @@
         <v>2</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -16559,26 +16833,31 @@
         <v>0</v>
       </c>
       <c r="M61" s="10" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="N61" s="10" t="n">
-        <v>37</v>
+        <v>15</v>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>0a83933al1lzugykf9cbvd6hi2rqf8qn</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>环岛东路投放点C</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -16587,54 +16866,59 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F62" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L62" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="M62" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="N62" s="9" t="n">
-        <v>27</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="N62" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="O62" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>724131086902996992</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>迈皋桥公交场站渗透</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -16643,54 +16927,59 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F63" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L63" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="M63" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="N63" s="9" t="n">
-        <v>18</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="N63" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O63" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>594063e60b264e419feea65370752c3f</t>
+          <t>0a83a497l1lj8cs3vsnr7r56rr3rgrgj</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
+          <t>新浦路投放点B</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -16699,66 +16988,71 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L64" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="M64" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="N64" s="9" t="n">
-        <v>9</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="N64" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="O64" s="8" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
+          <t>854196782092722176</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>淮海路远洋国际中心投放点A</t>
+          <t>工作日-全天-居民区-好的渗透</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>3</v>
@@ -16767,11 +17061,11 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
@@ -16780,29 +17074,32 @@
         </is>
       </c>
       <c r="L65" s="9" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M65" s="9" t="n">
         <v>20</v>
       </c>
       <c r="N65" s="9" t="n">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="O65" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>854196782092722176</t>
+          <t>3a7505a7b50d415583454f997bbdbf0e</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-居民区-好的渗透</t>
+          <t>六合区宁六路54号</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -16814,51 +17111,54 @@
         <v>30</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L66" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="M66" s="9" t="n">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="M66" s="10" t="n">
+        <v>36</v>
       </c>
       <c r="N66" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="O66" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>3a7505a7b50d415583454f997bbdbf0e</t>
+          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>六合区宁六路54号</t>
+          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -16867,10 +17167,10 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>3</v>
@@ -16879,123 +17179,125 @@
         <v>1</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L67" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="M67" s="10" t="n">
-        <v>36</v>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L67" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="M67" s="9" t="n">
+        <v>19</v>
       </c>
       <c r="N67" s="9" t="n">
-        <v>2</v>
+        <v>28</v>
+      </c>
+      <c r="O67" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>778851422965239808</t>
+          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-仙林新村</t>
+          <t>鼓楼区童家山2-3号楼</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L68" s="8" t="inlineStr">
-        <is>
-          <t>23☂</t>
-        </is>
-      </c>
-      <c r="M68" s="8" t="inlineStr">
-        <is>
-          <t>24☂</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M68" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="N68" s="10" t="n">
-        <v>46</v>
+        <v>16</v>
+      </c>
+      <c r="O68" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -17004,58 +17306,59 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L69" s="8" t="inlineStr">
-        <is>
-          <t>11☂</t>
-        </is>
-      </c>
-      <c r="M69" s="8" t="inlineStr">
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="M69" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="N69" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="O69" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
-      </c>
-      <c r="N69" s="10" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>788321551519383552</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>玄武区鹤鸣路37号</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -17064,46 +17367,47 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L70" s="8" t="inlineStr">
-        <is>
-          <t>20☂</t>
-        </is>
-      </c>
-      <c r="M70" s="8" t="inlineStr">
-        <is>
-          <t>16☂</t>
-        </is>
-      </c>
-      <c r="N70" s="10" t="n">
-        <v>20</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="M70" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N70" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="O70" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
+          <t>594063e60b264e419feea65370752c3f</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
+          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>3</v>
@@ -17112,10 +17416,10 @@
         <v>3</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -17124,28 +17428,33 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L71" s="10" t="n">
-        <v>60</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="n">
+        <v>25</v>
       </c>
       <c r="M71" s="9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N71" s="9" t="n">
-        <v>28</v>
+        <v>9</v>
+      </c>
+      <c r="O71" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>1174624598576300032</t>
+          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
+          <t>淮海路远洋国际中心投放点A</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -17159,7 +17468,7 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>3</v>
@@ -17168,10 +17477,10 @@
         <v>3</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -17180,28 +17489,33 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L72" s="9" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="M72" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N72" s="10" t="n">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="N72" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="O72" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>1174618792617238528</t>
+          <t>1174624598576300032</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区朝天宫街道建邺路建邺路住宅小区</t>
+          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -17211,17 +17525,17 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>1</v>
@@ -17236,37 +17550,38 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L73" s="8" t="inlineStr">
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M73" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N73" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="O73" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
-      </c>
-      <c r="M73" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="N73" s="10" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>854249531796738048</t>
+          <t>1174618792617238528</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-金马路地铁站</t>
+          <t>南京市秦淮区朝天宫街道建邺路建邺路住宅小区</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -17275,19 +17590,19 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -17296,7 +17611,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L74" s="8" t="inlineStr">
@@ -17306,48 +17621,51 @@
       </c>
       <c r="M74" s="8" t="inlineStr">
         <is>
-          <t>31☂</t>
+          <t>0☂</t>
         </is>
       </c>
       <c r="N74" s="10" t="n">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="O74" s="9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
+          <t>948393128847777792</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2A</t>
+          <t>30-工作日-全天-地铁-明故宫2渗透</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -17356,32 +17674,33 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L75" s="8" t="inlineStr">
-        <is>
-          <t>15☂</t>
-        </is>
-      </c>
-      <c r="M75" s="8" t="inlineStr">
-        <is>
-          <t>25☂</t>
-        </is>
-      </c>
-      <c r="N75" s="10" t="n">
-        <v>32</v>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="M75" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="N75" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="O75" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>948393128847777792</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>30-工作日-全天-地铁-明故宫2渗透</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -17391,23 +17710,23 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
         <v>30</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>93</v>
+        <v>209</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -17416,54 +17735,61 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L76" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="M76" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="N76" s="9" t="n">
-        <v>26</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>42☂</t>
+        </is>
+      </c>
+      <c r="M76" s="8" t="inlineStr">
+        <is>
+          <t>76☂</t>
+        </is>
+      </c>
+      <c r="N76" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="O76" s="9" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>554207268614606848</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -17472,37 +17798,38 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
-        <is>
-          <t>42☂</t>
-        </is>
-      </c>
-      <c r="M77" s="8" t="inlineStr">
-        <is>
-          <t>76☂</t>
-        </is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="M77" s="9" t="n">
+        <v>31</v>
       </c>
       <c r="N77" s="10" t="n">
-        <v>71</v>
+        <v>119</v>
+      </c>
+      <c r="O77" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
+          <t>1098069901166710784</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>鼓楼区童家山2-3号楼</t>
+          <t>25-全天-地铁站-工业大学地铁站2号口渗透</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -17511,19 +17838,19 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -17532,54 +17859,57 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L78" s="9" t="n">
-        <v>9</v>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L78" s="10" t="n">
+        <v>32</v>
       </c>
       <c r="M78" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="N78" s="10" t="n">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="N78" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="O78" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>554207268614606848</t>
+          <t>1174597131085402112</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
+          <t>25-早峰-地铁站-云南路地铁站渗透</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -17588,54 +17918,61 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L79" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="M79" s="9" t="n">
-        <v>31</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="M79" s="8" t="inlineStr">
+        <is>
+          <t>17☂</t>
+        </is>
       </c>
       <c r="N79" s="10" t="n">
-        <v>119</v>
+        <v>43</v>
+      </c>
+      <c r="O79" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>1098069901166710784</t>
+          <t>778851422965239808</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-工业大学地铁站2号口渗透</t>
+          <t>25-早峰-居民区-仙林新村</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -17644,33 +17981,40 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L80" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="M80" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="N80" s="9" t="n">
-        <v>22</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>23☂</t>
+        </is>
+      </c>
+      <c r="M80" s="8" t="inlineStr">
+        <is>
+          <t>24☂</t>
+        </is>
+      </c>
+      <c r="N80" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="O80" s="10" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>1174597131085402112</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-地铁站-云南路地铁站渗透</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -17679,19 +18023,19 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -17705,16 +18049,19 @@
       </c>
       <c r="L81" s="8" t="inlineStr">
         <is>
+          <t>11☂</t>
+        </is>
+      </c>
+      <c r="M81" s="8" t="inlineStr">
+        <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="M81" s="8" t="inlineStr">
-        <is>
-          <t>17☂</t>
-        </is>
-      </c>
       <c r="N81" s="10" t="n">
-        <v>43</v>
+        <v>24</v>
+      </c>
+      <c r="O81" s="10" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="82">
@@ -17751,7 +18098,7 @@
         <v>2</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>342</v>
+        <v>395</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -17772,6 +18119,11 @@
       <c r="N82" s="10" t="n">
         <v>161</v>
       </c>
+      <c r="O82" s="8" t="inlineStr">
+        <is>
+          <t>53☂</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -17828,6 +18180,11 @@
       <c r="N83" s="10" t="n">
         <v>26</v>
       </c>
+      <c r="O83" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -17884,6 +18241,11 @@
       <c r="N84" s="10" t="n">
         <v>40</v>
       </c>
+      <c r="O84" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -17940,6 +18302,11 @@
       <c r="N85" s="10" t="n">
         <v>53</v>
       </c>
+      <c r="O85" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -17975,7 +18342,7 @@
         <v>2</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -17996,6 +18363,11 @@
       <c r="N86" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="O86" s="8" t="inlineStr">
+        <is>
+          <t>23☂</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -18052,6 +18424,11 @@
       <c r="N87" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="O87" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -18087,7 +18464,7 @@
         <v>2</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -18108,6 +18485,11 @@
       <c r="N88" s="10" t="n">
         <v>38</v>
       </c>
+      <c r="O88" s="8" t="inlineStr">
+        <is>
+          <t>25☂</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -18164,6 +18546,11 @@
       <c r="N89" s="10" t="n">
         <v>100</v>
       </c>
+      <c r="O89" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -18220,6 +18607,11 @@
       <c r="N90" s="10" t="n">
         <v>215</v>
       </c>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -18276,21 +18668,26 @@
       <c r="N91" s="10" t="n">
         <v>185</v>
       </c>
+      <c r="O91" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>1123869911569338368</t>
+          <t>1174621727109263360</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>学衡路南京师范大学仙林校区投放点B</t>
+          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -18299,19 +18696,19 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -18320,28 +18717,31 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L92" s="10" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="M92" s="10" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N92" s="10" t="n">
-        <v>46</v>
+        <v>71</v>
+      </c>
+      <c r="O92" s="9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>1174621727109263360</t>
+          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
+          <t>石门坎地铁站3号口光华科技产业园投放点</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -18351,11 +18751,11 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F93" s="3" t="n">
         <v>3</v>
@@ -18367,7 +18767,7 @@
         <v>3</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -18380,29 +18780,34 @@
         </is>
       </c>
       <c r="L93" s="10" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="M93" s="10" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N93" s="10" t="n">
-        <v>71</v>
+        <v>42</v>
+      </c>
+      <c r="O93" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
+          <t>816505037427507200</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>石门坎地铁站3号口光华科技产业园投放点</t>
+          <t>玄武区童卫路28-2号</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -18423,7 +18828,7 @@
         <v>3</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -18436,29 +18841,34 @@
         </is>
       </c>
       <c r="L94" s="10" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="M94" s="10" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="N94" s="10" t="n">
-        <v>42</v>
+        <v>128</v>
+      </c>
+      <c r="O94" s="8" t="inlineStr">
+        <is>
+          <t>23☂</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>816505037427507200</t>
+          <t>1153706290333523968</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>玄武区童卫路28-2号</t>
+          <t>鼓楼区集庆门大街268号</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -18467,7 +18877,7 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F95" s="3" t="n">
         <v>3</v>
@@ -18479,7 +18889,7 @@
         <v>3</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>259</v>
+        <v>80</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -18492,50 +18902,55 @@
         </is>
       </c>
       <c r="L95" s="10" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="M95" s="10" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="N95" s="10" t="n">
-        <v>128</v>
+        <v>30</v>
+      </c>
+      <c r="O95" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>1153706290333523968</t>
+          <t>1123869911569338368</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>鼓楼区集庆门大街268号</t>
+          <t>学衡路南京师范大学仙林校区投放点B</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -18548,13 +18963,16 @@
         </is>
       </c>
       <c r="L96" s="10" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M96" s="10" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="N96" s="10" t="n">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="O96" s="10" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -21981,7 +22399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -21998,6 +22416,7 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22078,6 +22497,11 @@
           <t>07-11(六)</t>
         </is>
       </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>07-12(日)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -22104,7 +22528,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -22132,6 +22556,9 @@
         <v>0</v>
       </c>
       <c r="N3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22160,7 +22587,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -22188,6 +22615,9 @@
         <v>0</v>
       </c>
       <c r="N4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22216,7 +22646,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -22244,23 +22674,26 @@
         <v>0</v>
       </c>
       <c r="N5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1l7iaxy7ybfmcgce27jr5vm</t>
+          <t>893749163098365952</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>修文路保利·梧桐语站点Z18</t>
+          <t>玉堂巷2-1号小里新寓站点A</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -22272,7 +22705,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -22300,23 +22733,26 @@
         <v>0</v>
       </c>
       <c r="N6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>893749163098365952</t>
+          <t>0a8339f4l1lh4xmtqcvwzga6zi8snxmx</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>玉堂巷2-1号小里新寓站点A</t>
+          <t>灵谷寺4</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -22325,10 +22761,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -22356,23 +22792,26 @@
         <v>0</v>
       </c>
       <c r="N7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>0a8339f4l1lh4xmtqcvwzga6zi8snxmx</t>
+          <t>0a898873l1l2z5yttrk27pq8kwxsxux8</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺4</t>
+          <t>高新-小区-瑾家珑熹台（南1门）</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -22381,28 +22820,28 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -22411,19 +22850,22 @@
       <c r="M8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="7" t="n">
+      <c r="N8" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="O8" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>0a898873l1l2z5yttrk27pq8kwxsxux8</t>
+          <t>0a83a414l1l7iaxy7ybfmcgce27jr5vm</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>高新-小区-瑾家珑熹台（南1门）</t>
+          <t>修文路保利·梧桐语站点Z18</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -22440,7 +22882,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>1</v>
@@ -22449,16 +22891,16 @@
         <v>1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L9" s="7" t="n">
@@ -22467,8 +22909,11 @@
       <c r="M9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="10" t="n">
-        <v>12</v>
+      <c r="N9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -22496,7 +22941,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>1</v>
@@ -22509,12 +22954,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L10" s="7" t="n">
@@ -22526,6 +22971,9 @@
       <c r="N10" s="10" t="n">
         <v>12</v>
       </c>
+      <c r="O10" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -22552,7 +23000,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>1</v>
@@ -22565,12 +23013,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L11" s="7" t="n">
@@ -22582,21 +23030,24 @@
       <c r="N11" s="10" t="n">
         <v>12</v>
       </c>
+      <c r="O11" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
+          <t>1158030564174917632</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>竹山路地铁1号口</t>
+          <t>东山头</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -22605,10 +23056,10 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1</v>
@@ -22617,16 +23068,16 @@
         <v>1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L12" s="7" t="n">
@@ -22636,23 +23087,26 @@
         <v>0</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lyxfkh7vjgmkyih6st4gkb</t>
+          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>经贸学院路保利·樾广场站点A</t>
+          <t>鹏山路东方·龙湖湾站点Z2</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -22664,46 +23118,49 @@
         <v>11</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="n">
-        <v>0</v>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1158030564174917632</t>
+          <t>1158025287508230144</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>东山头</t>
+          <t>3号门</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -22713,14 +23170,14 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>1</v>
@@ -22729,42 +23186,49 @@
         <v>1</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11</v>
+        <v>492</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>0</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>220☂</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>154☂</t>
+        </is>
       </c>
       <c r="N14" s="10" t="n">
-        <v>11</v>
+        <v>118</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
+          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>鹏山路东方·龙湖湾站点Z2</t>
+          <t>土山路东域城站点A</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -22776,51 +23240,54 @@
         <v>11</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>0</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
+          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>高新-小区-瑾家珑熹台（南2门）</t>
+          <t>竹山路地铁1号口</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -22832,7 +23299,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>2</v>
@@ -22841,20 +23308,20 @@
         <v>2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>35</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>0</v>
@@ -22862,21 +23329,24 @@
       <c r="N16" s="10" t="n">
         <v>12</v>
       </c>
+      <c r="O16" s="10" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
+          <t>0a83a414l1lyxfkh7vjgmkyih6st4gkb</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>土山路东域城站点A</t>
+          <t>经贸学院路保利·樾广场站点A</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -22888,7 +23358,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>2</v>
@@ -22897,26 +23367,29 @@
         <v>2</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="10" t="n">
-        <v>12</v>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="O17" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -22944,7 +23417,7 @@
         <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>2</v>
@@ -22957,12 +23430,12 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L18" s="10" t="n">
@@ -22974,81 +23447,83 @@
       <c r="N18" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="O18" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1158025287508230144</t>
+          <t>889466722646794240</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>3号门</t>
+          <t>胜太东路江宁供销商厦站点</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>492</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>220☂</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t>154☂</t>
-        </is>
+      <c r="M19" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>118</v>
+        <v>11</v>
+      </c>
+      <c r="O19" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
+          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>严南路金辉禹洲金陵铭著站点A</t>
+          <t>高新-小区-瑾家珑熹台（南2门）</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -23060,51 +23535,54 @@
         <v>11</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L20" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="M20" s="9" t="n">
-        <v>10</v>
+        <v>35</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N20" s="10" t="n">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="O20" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
+          <t>897042860272709632</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>胜太西路太平花苑北苑站点C</t>
+          <t>鹏山路中粮悦天地(建设中)站点B</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -23116,51 +23594,54 @@
         <v>11</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>10</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>22</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="O21" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
+          <t>1158030570667700224</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>胜太西路天琪雅居站点</t>
+          <t>美龄宫</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -23169,54 +23650,57 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>47</v>
+        <v>1387</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L22" s="9" t="n">
-        <v>10</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>436</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>26</v>
+        <v>396</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>11</v>
+        <v>555</v>
+      </c>
+      <c r="O22" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
+          <t>1158030569614929920</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>平泰街太平花苑站点</t>
+          <t>海底世界站台</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -23225,54 +23709,57 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>51</v>
+        <v>485</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>10</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>143</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>30</v>
+        <v>199</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>11</v>
+        <v>143</v>
+      </c>
+      <c r="O23" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>889665664809402368</t>
+          <t>1158030573943451648</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科南门C</t>
+          <t>中山陵7号门</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -23281,54 +23768,57 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>93</v>
+        <v>340</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L24" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>10</v>
+        <v>132</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>132</v>
       </c>
       <c r="N24" s="10" t="n">
-        <v>48</v>
+        <v>76</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>889466722646794240</t>
+          <t>1158030568570548224</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>胜太东路江宁供销商厦站点</t>
+          <t>海底世界</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -23337,54 +23827,57 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>24</v>
+        <v>212</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="n">
-        <v>1</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="N25" s="10" t="n">
-        <v>11</v>
+        <v>81</v>
+      </c>
+      <c r="O25" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
+          <t>1158030571808550912</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>胜太西路47号汇金新天地广场站点</t>
+          <t>1号门</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -23393,10 +23886,10 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>3</v>
@@ -23405,37 +23898,40 @@
         <v>3</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L26" s="10" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M26" s="10" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>52</v>
+        <v>12</v>
+      </c>
+      <c r="O26" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
+          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>胜太西路45号汇金新天地广场站点</t>
+          <t>严南路金辉禹洲金陵铭著站点A</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -23452,16 +23948,16 @@
         <v>11</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -23470,28 +23966,31 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L27" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="M27" s="10" t="n">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="O27" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>0a838de0l1lnurtzrb4hnycbdpmcz7tn</t>
+          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>吉印大道东南大学(九龙湖校区)站点H</t>
+          <t>胜太西路太平花苑北苑站点C</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -23508,16 +24007,16 @@
         <v>11</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>296</v>
+        <v>43</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -23526,28 +24025,31 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="n">
-        <v>159</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>81</v>
+        <v>11</v>
+      </c>
+      <c r="O28" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
+          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>吉印大道融信·铂岸中心站点</t>
+          <t>胜太西路天琪雅居站点</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -23564,16 +24066,16 @@
         <v>11</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -23582,28 +24084,31 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L29" s="10" t="n">
-        <v>13</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>36</v>
+        <v>11</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
+          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
+          <t>平泰街太平花苑站点</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -23620,16 +24125,16 @@
         <v>11</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -23638,33 +24143,36 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L30" s="10" t="n">
-        <v>24</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="N30" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="O30" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
+          <t>889665664809402368</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
+          <t>高新-高校-金科南门C</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -23676,16 +24184,16 @@
         <v>11</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -23694,33 +24202,36 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L31" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="M31" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N31" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="O31" s="10" t="n">
         <v>11</v>
-      </c>
-      <c r="N31" s="10" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>897042860272709632</t>
+          <t>1158030572869709824</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>鹏山路中粮悦天地(建设中)站点B</t>
+          <t>东沟停车场</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -23729,19 +24240,19 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>66</v>
+        <v>1349</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -23750,33 +24261,36 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L32" s="10" t="n">
-        <v>22</v>
+        <v>341</v>
       </c>
       <c r="M32" s="10" t="n">
-        <v>22</v>
+        <v>418</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>22</v>
+        <v>556</v>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>897053191954571264</t>
+          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>知行路中粮悦天地(建设中)站点F</t>
+          <t>胜太西路47号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -23788,16 +24302,16 @@
         <v>11</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -23810,29 +24324,32 @@
         </is>
       </c>
       <c r="L33" s="10" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M33" s="10" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="O33" s="10" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>1158030570667700224</t>
+          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>美龄宫</t>
+          <t>胜太西路45号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -23841,19 +24358,19 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1387</v>
+        <v>85</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -23866,29 +24383,32 @@
         </is>
       </c>
       <c r="L34" s="10" t="n">
-        <v>436</v>
+        <v>20</v>
       </c>
       <c r="M34" s="10" t="n">
-        <v>396</v>
+        <v>28</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>555</v>
+        <v>15</v>
+      </c>
+      <c r="O34" s="10" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>1158030572869709824</t>
+          <t>0a838de0l1lnurtzrb4hnycbdpmcz7tn</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>东沟停车场</t>
+          <t>吉印大道东南大学(九龙湖校区)站点H</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -23897,19 +24417,19 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1315</v>
+        <v>359</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -23922,29 +24442,32 @@
         </is>
       </c>
       <c r="L35" s="10" t="n">
-        <v>341</v>
+        <v>159</v>
       </c>
       <c r="M35" s="10" t="n">
-        <v>418</v>
+        <v>56</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>556</v>
+        <v>81</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>1158030569614929920</t>
+          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>海底世界站台</t>
+          <t>吉印大道融信·铂岸中心站点</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -23953,19 +24476,19 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>485</v>
+        <v>74</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -23978,29 +24501,32 @@
         </is>
       </c>
       <c r="L36" s="10" t="n">
-        <v>143</v>
+        <v>13</v>
       </c>
       <c r="M36" s="10" t="n">
-        <v>199</v>
+        <v>13</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>143</v>
+        <v>36</v>
+      </c>
+      <c r="O36" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>1158030573943451648</t>
+          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>中山陵7号门</t>
+          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -24009,19 +24535,19 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>340</v>
+        <v>60</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -24034,29 +24560,32 @@
         </is>
       </c>
       <c r="L37" s="10" t="n">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>76</v>
+        <v>12</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>1158030568570548224</t>
+          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>海底世界</t>
+          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -24065,19 +24594,19 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>212</v>
+        <v>76</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -24090,29 +24619,32 @@
         </is>
       </c>
       <c r="L38" s="10" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="M38" s="10" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>81</v>
+        <v>24</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>1158030571808550912</t>
+          <t>897053191954571264</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>1号门</t>
+          <t>知行路中粮悦天地(建设中)站点F</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -24121,19 +24653,19 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -24149,10 +24681,13 @@
         <v>11</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>12</v>
+        <v>55</v>
+      </c>
+      <c r="O39" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -24618,7 +25153,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>22</v>
@@ -24628,12 +25163,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -24647,7 +25182,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -24676,22 +25211,22 @@
         <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -24705,22 +25240,22 @@
         <v>26</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>27</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
     </row>
@@ -24734,7 +25269,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>17</v>
@@ -24744,12 +25279,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -24763,22 +25298,22 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>38.5%</t>
         </is>
       </c>
     </row>
@@ -24792,22 +25327,22 @@
         <v>13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>17</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>43.6%</t>
         </is>
       </c>
     </row>
@@ -24850,22 +25385,22 @@
         <v>9</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>7</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
     </row>
@@ -25158,13 +25693,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -25173,7 +25708,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -25187,22 +25722,22 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>22</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -25216,17 +25751,17 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -25245,22 +25780,22 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25809,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>7</v>
@@ -25284,12 +25819,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -591,12 +591,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>40.9%</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>71.8%</t>
         </is>
       </c>
     </row>
@@ -654,14 +654,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20260701 ~ 20260717</t>
+          <t>数据范围: 20260701 ~ 20260719</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 13天, 周末: 4天</t>
+          <t>工作日: 13天, 周末: 6天</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:Q96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16084,6 +16084,8 @@
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16169,6 +16171,16 @@
           <t>07-12(日)</t>
         </is>
       </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>07-18(六)</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>07-19(日)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -16195,7 +16207,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -16226,18 +16238,24 @@
         <v>0</v>
       </c>
       <c r="O3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1lb75b2rkfyy7vkvm675giz</t>
+          <t>0a836587l1luwpb8icj8s7h27qzgfz6h</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>南京建邺吾悦广场(3号门)吾悦广场(南京建邺店)投放点</t>
+          <t>新安江街河西CBD投放点</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -16251,10 +16269,10 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -16285,6 +16303,14 @@
         <v>0</v>
       </c>
       <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -16293,29 +16319,29 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1luwpb8icj8s7h27qzgfz6h</t>
+          <t>1153706292829134848</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>新安江街河西CBD投放点</t>
+          <t>广志路投放点A</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -16345,21 +16371,25 @@
       <c r="N5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="O5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1153706292829134848</t>
+          <t>0a836146l1lyjs7c5zcucbu58t8qkunu</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>广志路投放点A</t>
+          <t>茂民路御湖仕家投放点</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -16369,7 +16399,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -16406,24 +16436,34 @@
       <c r="N6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="7" t="n">
-        <v>0</v>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1lyjs7c5zcucbu58t8qkunu</t>
+          <t>5331e3a58a50481dbc8e7273561f4e25</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>茂民路御湖仕家投放点</t>
+          <t>工作日-全天-地铁站-夫子庙2号口-10</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -16432,10 +16472,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -16466,6 +16506,14 @@
         <v>0</v>
       </c>
       <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -16474,17 +16522,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>5331e3a58a50481dbc8e7273561f4e25</t>
+          <t>0a89a0cdl1luijmqd4buxi8s686ps96i</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-地铁站-夫子庙2号口-10</t>
+          <t>鱼嘴湿地公园江豚广场南京鱼嘴湿地公园投放点</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -16493,10 +16541,10 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -16527,6 +16575,14 @@
         <v>0</v>
       </c>
       <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -16535,12 +16591,12 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>0a89a0cdl1luijmqd4buxi8s686ps96i</t>
+          <t>0a83e80al1ldxqqv34qytix6br5r7zzh</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>鱼嘴湿地公园江豚广场南京鱼嘴湿地公园投放点</t>
+          <t>江提路投放点</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -16557,7 +16613,7 @@
         <v>15</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -16588,6 +16644,14 @@
         <v>0</v>
       </c>
       <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -16596,17 +16660,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>0a83e80al1ldxqqv34qytix6br5r7zzh</t>
+          <t>684268350256898048</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>江提路投放点</t>
+          <t>25-全天-地铁-学则路</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -16615,40 +16679,48 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="L10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="7" t="n">
-        <v>0</v>
+      <c r="N10" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -16657,12 +16729,12 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>813294194703020032</t>
+          <t>1174535930061524992</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>打钉巷金鼎湾国际投放点</t>
+          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -16672,11 +16744,11 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>4</v>
@@ -16685,10 +16757,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -16697,7 +16769,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L11" s="7" t="n">
@@ -16706,36 +16778,46 @@
       <c r="M11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="O11" s="7" t="n">
-        <v>0</v>
+      <c r="N11" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1174627346911133696</t>
+          <t>754365148238000128</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道户部街长发银座</t>
+          <t>玄武区四牌楼63号</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>4</v>
@@ -16744,10 +16826,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -16756,7 +16838,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L12" s="7" t="n">
@@ -16765,36 +16847,46 @@
       <c r="M12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>0</v>
+      <c r="N12" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>80☂</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>1174622729575776256</t>
+          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区常府街地铁站3号口</t>
+          <t>九家圩路世茂外滩新城投放点A</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>4</v>
@@ -16806,7 +16898,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -16825,35 +16917,45 @@
         <v>0</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1lm5w7r6duyverna8nzapss</t>
+          <t>0a836146l1lb75b2rkfyy7vkvm675giz</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>中山东路南京航空航天大学(明故宫校区)投放点B</t>
+          <t>南京建邺吾悦广场(3号门)吾悦广场(南京建邺店)投放点</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>4</v>
@@ -16865,7 +16967,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -16883,27 +16985,37 @@
       <c r="M14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="O14" s="7" t="n">
-        <v>0</v>
+      <c r="N14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lbekztkg9bb795bdwjee85</t>
+          <t>0a838699l1lyun3by28du7fus2rjdmuu</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>天润城地铁站2号口天润城十一街区投放点A</t>
+          <t>剪子巷40号夫子庙秦淮风光带投放点</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -16912,28 +17024,28 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L15" s="7" t="n">
@@ -16942,10 +17054,18 @@
       <c r="M15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="10" t="n">
-        <v>8</v>
+      <c r="N15" s="9" t="n">
+        <v>16</v>
       </c>
       <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -16954,17 +17074,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>684268350256898048</t>
+          <t>939772435800334336</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-学则路</t>
+          <t>南京市建邺区江心洲街道红星街洲岛家园</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -16973,40 +17093,48 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="10" t="n">
-        <v>23</v>
+      <c r="M16" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -17015,17 +17143,17 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
+          <t>1206516292750213120</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
+          <t>中山北路宏图大厦渗透</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -17034,28 +17162,28 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L17" s="7" t="n">
@@ -17064,10 +17192,18 @@
       <c r="M17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="10" t="n">
-        <v>17</v>
+      <c r="N17" s="9" t="n">
+        <v>16</v>
       </c>
       <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -17076,12 +17212,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1150704239247155200</t>
+          <t>813294194703020032</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带A</t>
+          <t>打钉巷金鼎湾国际投放点</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -17091,23 +17227,23 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -17116,7 +17252,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L18" s="7" t="n">
@@ -17125,24 +17261,28 @@
       <c r="M18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="N18" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1174535930061524992</t>
+          <t>1174627346911133696</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
+          <t>南京市秦淮区洪武路街道户部街长发银座</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -17152,84 +17292,88 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="O19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="Q19" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>754365148238000128</t>
+          <t>1174622729575776256</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>玄武区四牌楼63号</t>
+          <t>南京市秦淮区常府街地铁站3号口</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -17238,7 +17382,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L20" s="7" t="n">
@@ -17247,29 +17391,33 @@
       <c r="M20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="N20" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q20" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l2ehxa2pgziwbi3i3kp6ct</t>
+          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>红山路辅路常发广场投放点B</t>
+          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -17278,23 +17426,23 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -17309,23 +17457,31 @@
         <v>0</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="O21" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>10☂</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1153706318256898048</t>
+          <t>0a83d1c7l1lae4s7r5hq76dmaivv9ibv</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>浦口大道投放点渗透</t>
+          <t>迎江路玖印府(建设中)投放点</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -17342,20 +17498,20 @@
         <v>25</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -17370,28 +17526,36 @@
         <v>0</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O22" s="8" t="inlineStr">
         <is>
           <t>5☂</t>
+        </is>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a8331f1l1ld9wgam59z73ha4yn6qxdr</t>
+          <t>0a836587l1lbekztkg9bb795bdwjee85</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>镇南河路东方万汇城投放点E</t>
+          <t>天润城地铁站2号口天润城十一街区投放点A</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -17400,28 +17564,28 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="I23" s="3" t="n">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L23" s="7" t="n">
@@ -17431,28 +17595,36 @@
         <v>0</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O23" s="8" t="inlineStr">
         <is>
-          <t>19☂</t>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P23" s="9" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>0a83d1c7l1lae4s7r5hq76dmaivv9ibv</t>
+          <t>1150704239247155200</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>迎江路玖印府(建设中)投放点</t>
+          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带A</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -17461,28 +17633,28 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="I24" s="3" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
@@ -17492,28 +17664,36 @@
         <v>0</v>
       </c>
       <c r="N24" s="10" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O24" s="8" t="inlineStr">
         <is>
-          <t>5☂</t>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P24" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>7☂</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>732956182771253248</t>
+          <t>1174535134415278080</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>25-全天-商超-金茂汇渗透</t>
+          <t>南京市秦淮区夫子庙街道箍桶巷夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -17522,28 +17702,28 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L25" s="7" t="n">
@@ -17553,9 +17733,17 @@
         <v>0</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -17564,17 +17752,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
+          <t>1174535134415278080</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>九家圩路世茂外滩新城投放点A</t>
+          <t>南京市秦淮区夫子庙街道箍桶巷夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -17583,28 +17771,28 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
@@ -17614,9 +17802,17 @@
         <v>0</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P26" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -17625,12 +17821,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>1176842717252255744</t>
+          <t>732955142450266112</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>三元巷6号三元公寓投放点渗透</t>
+          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -17647,25 +17843,25 @@
         <v>20</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L27" s="7" t="n">
@@ -17675,9 +17871,17 @@
         <v>0</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>1☂</t>
+        </is>
+      </c>
+      <c r="P27" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -17686,17 +17890,17 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>1174535134415278080</t>
+          <t>1174593029863960576</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道箍桶巷夫子庙秦淮风光带</t>
+          <t>25-全天-高校-师范大学渗透</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -17705,40 +17909,48 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="n">
-        <v>0</v>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -17747,17 +17959,17 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>1174535134415278080</t>
+          <t>0a836587l1l2ehxa2pgziwbi3i3kp6ct</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道箍桶巷夫子庙秦淮风光带</t>
+          <t>红山路辅路常发广场投放点B</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -17766,28 +17978,28 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L29" s="7" t="n">
@@ -17796,10 +18008,18 @@
       <c r="M29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="9" t="n">
-        <v>49</v>
+      <c r="N29" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -17808,17 +18028,17 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>732955142450266112</t>
+          <t>0a836587l1l7hr5eaanydw8fnf2xk6r4</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
+          <t>张家村东方万汇城投放点</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -17827,28 +18047,28 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L30" s="7" t="n">
@@ -17862,24 +18082,32 @@
       </c>
       <c r="O30" s="8" t="inlineStr">
         <is>
-          <t>1☂</t>
+          <t>7☂</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>25☂</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>0a838699l1lyun3by28du7fus2rjdmuu</t>
+          <t>1153706318256898048</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>剪子巷40号夫子庙秦淮风光带投放点</t>
+          <t>浦口大道投放点渗透</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -17888,28 +18116,28 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L31" s="7" t="n">
@@ -17918,29 +18146,37 @@
       <c r="M31" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="9" t="n">
-        <v>16</v>
+      <c r="N31" s="10" t="n">
+        <v>18</v>
       </c>
       <c r="O31" s="8" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>5☂</t>
+        </is>
+      </c>
+      <c r="P31" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>23☂</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1ldsbrxkzcxei46ckdztk7h</t>
+          <t>0a8331f1l1ld9wgam59z73ha4yn6qxdr</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>中山南路91号江苏文化大厦投放点A</t>
+          <t>镇南河路东方万汇城投放点E</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -17949,28 +18185,28 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L32" s="7" t="n">
@@ -17979,90 +18215,106 @@
       <c r="M32" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="9" t="n">
-        <v>20</v>
+      <c r="N32" s="10" t="n">
+        <v>24</v>
       </c>
       <c r="O32" s="8" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>19☂</t>
+        </is>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>22☂</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>874549501386596352</t>
+          <t>1174597131085402112</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
+          <t>25-早峰-地铁站-云南路地铁站渗透</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="7" t="n">
-        <v>0</v>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>17☂</t>
+        </is>
       </c>
       <c r="N33" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="O33" s="8" t="inlineStr">
-        <is>
-          <t>19☂</t>
-        </is>
+        <v>43</v>
+      </c>
+      <c r="O33" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>0a838e37l1ls23rim2x3aaf2bwvtsyi2</t>
+          <t>732956182771253248</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>秦淮区红花街道卡子门地铁站</t>
+          <t>25-全天-商超-金茂汇渗透</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -18074,25 +18326,25 @@
         <v>15</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L34" s="7" t="n">
@@ -18102,28 +18354,36 @@
         <v>0</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="O34" s="8" t="inlineStr">
         <is>
-          <t>37☂</t>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P34" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>20☂</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>849243610630791168</t>
+          <t>1206515660536758272</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-地铁-马群站</t>
+          <t>南京邮电大学渗透</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -18132,40 +18392,48 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L35" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="7" t="n">
-        <v>0</v>
+      <c r="M35" s="9" t="n">
+        <v>22</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -18174,78 +18442,86 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>939772435800334336</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区江心洲街道红星街洲岛家园</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="N36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>11☂</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="N36" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="P36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>1206516292750213120</t>
+          <t>1176842717252255744</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>中山北路宏图大厦渗透</t>
+          <t>三元巷6号三元公寓投放点渗透</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -18254,28 +18530,28 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L37" s="7" t="n">
@@ -18285,89 +18561,101 @@
         <v>0</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O37" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
+        </is>
+      </c>
+      <c r="P37" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q37" s="8" t="inlineStr">
+        <is>
+          <t>20☂</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
+          <t>732955142450266112</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>集贤路鼓楼创新广场投放点B</t>
+          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="O38" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="Q38" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l7hr5eaanydw8fnf2xk6r4</t>
+          <t>0a83a497l1ldsbrxkzcxei46ckdztk7h</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>张家村东方万汇城投放点</t>
+          <t>中山南路91号江苏文化大厦投放点A</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -18376,28 +18664,28 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L39" s="7" t="n">
@@ -18407,37 +18695,45 @@
         <v>0</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O39" s="8" t="inlineStr">
         <is>
-          <t>7☂</t>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P39" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>1123869816929062912</t>
+          <t>874549501386596352</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>六合大道南京葛塘汽车客运站投放点A</t>
+          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>4</v>
@@ -18446,10 +18742,10 @@
         <v>2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -18458,45 +18754,55 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L40" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="N40" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O40" s="7" t="n">
-        <v>0</v>
+      <c r="M40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="O40" s="8" t="inlineStr">
+        <is>
+          <t>19☂</t>
+        </is>
+      </c>
+      <c r="P40" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1lyau4xnzsbvbjunbxguey8</t>
+          <t>0a838e37l1ls23rim2x3aaf2bwvtsyi2</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>浦珠南路南京工业大学江浦校区投放点A</t>
+          <t>秦淮区红花街道卡子门地铁站</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>4</v>
@@ -18505,10 +18811,10 @@
         <v>2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -18517,7 +18823,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L41" s="7" t="n">
@@ -18526,22 +18832,32 @@
       <c r="M41" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N41" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="O41" s="10" t="n">
-        <v>4</v>
+      <c r="N41" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>37☂</t>
+        </is>
+      </c>
+      <c r="P41" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t>22☂</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>788321551519383552</t>
+          <t>854249531796738048</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>玄武区鹤鸣路37号</t>
+          <t>25-全天-地铁站-金马路地铁站</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -18558,16 +18874,16 @@
         <v>20</v>
       </c>
       <c r="F42" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H42" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -18581,44 +18897,50 @@
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>20☂</t>
+          <t>0☂</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>16☂</t>
+          <t>31☂</t>
         </is>
       </c>
       <c r="N42" s="9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q42" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>732955142450266112</t>
+          <t>849243610630791168</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
+          <t>25-早峰-地铁-马群站</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>4</v>
@@ -18627,10 +18949,10 @@
         <v>2</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -18639,7 +18961,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L43" s="7" t="n">
@@ -18649,21 +18971,31 @@
         <v>0</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="O43" s="10" t="n">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P43" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t>18☂</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>854249531796738048</t>
+          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-金马路地铁站</t>
+          <t>钟灵街2A</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -18680,16 +19012,16 @@
         <v>20</v>
       </c>
       <c r="F44" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H44" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -18703,56 +19035,62 @@
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>15☂</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>31☂</t>
+          <t>25☂</t>
         </is>
       </c>
       <c r="N44" s="9" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="O44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q44" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
+          <t>0a83fddcl1ln2kvc5pnasw3i47tp2gxk</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2A</t>
+          <t>中新大道投放点D</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F45" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="H45" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -18764,42 +19102,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="L45" s="8" t="inlineStr">
-        <is>
-          <t>15☂</t>
-        </is>
-      </c>
-      <c r="M45" s="8" t="inlineStr">
-        <is>
-          <t>25☂</t>
-        </is>
+      <c r="L45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>22</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="O45" s="7" t="n">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>1110455098857938944</t>
+          <t>0a83a497l1lumz6c4kkm73jypiiknrwb</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>浦珠南路中国海油协和石油加油站(江浦站)投放点渗透</t>
+          <t>中新大道南京气象局投放点</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
@@ -18812,10 +19156,10 @@
         <v>2</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -18824,45 +19168,55 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L46" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M46" s="7" t="n">
-        <v>0</v>
+      <c r="M46" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="O46" s="10" t="n">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="O46" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
+          <t>0a83933al1lzugykf9cbvd6hi2rqf8qn</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>中山东路228号新世纪广场A幢投放点</t>
+          <t>环岛东路投放点C</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>4</v>
@@ -18874,7 +19228,7 @@
         <v>2</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>183</v>
+        <v>30</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -18890,38 +19244,48 @@
         <v>0</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="O47" s="7" t="n">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
+          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>大行宫6号口渗透</t>
+          <t>集贤路鼓楼创新广场投放点B</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>4</v>
@@ -18933,7 +19297,7 @@
         <v>2</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>158</v>
+        <v>45</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -18948,30 +19312,40 @@
       <c r="L48" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M48" s="9" t="n">
-        <v>98</v>
+      <c r="M48" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="O48" s="7" t="n">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="O48" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P48" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q48" s="8" t="inlineStr">
+        <is>
+          <t>15☂</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>1176722757207629824</t>
+          <t>0a836146l1lm5w7r6duyverna8nzapss</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>规划建设展览馆渗透</t>
+          <t>中山东路南京航空航天大学(明故宫校区)投放点B</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -18980,19 +19354,19 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -19007,86 +19381,96 @@
       <c r="L49" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="9" t="n">
-        <v>111</v>
+      <c r="M49" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="O49" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P49" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q49" s="9" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>大行宫6号口渗透</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F50" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G50" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G50" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H50" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>76</v>
+        <v>198</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L50" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="M50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="O50" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="N50" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="O50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>e5189cd954054116aa19db28790cc606</t>
+          <t>1123869816929062912</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-高新地铁站-30</t>
+          <t>六合大道南京葛塘汽车客运站投放点A</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -19096,84 +19480,88 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F51" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="N51" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G51" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="N51" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="O51" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="O51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q51" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>1174593029863960576</t>
+          <t>854196782092722176</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>25-全天-高校-师范大学渗透</t>
+          <t>工作日-全天-居民区-好的渗透</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -19182,59 +19570,63 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L52" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="M52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="O52" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="M52" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N52" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="O52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q52" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>1153706342168625152</t>
+          <t>0a836146l1lyau4xnzsbvbjunbxguey8</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>鼓楼东南大学渗透</t>
+          <t>浦珠南路南京工业大学江浦校区投放点A</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -19243,155 +19635,167 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L53" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M53" s="9" t="n">
+      <c r="M53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="O53" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P53" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="N53" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="O53" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="Q53" s="10" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>1206515660536758272</t>
+          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>南京邮电大学渗透</t>
+          <t>鼓楼区童家山2-3号楼</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G54" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="L54" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M54" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N54" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="O54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H54" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="N54" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="O54" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="Q54" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>1098070146307002368</t>
+          <t>1110455098857938944</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
+          <t>浦珠南路中国海油协和石油加油站(江浦站)投放点渗透</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="O55" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P55" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q55" s="9" t="n">
         <v>25</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="N55" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="O55" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>998560699433394176</t>
+          <t>1123869911569338368</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>广志路南京万达茂投放点D</t>
+          <t>学衡路南京师范大学仙林校区投放点B</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -19401,23 +19805,23 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -19429,56 +19833,60 @@
           <t>67%</t>
         </is>
       </c>
-      <c r="L56" s="7" t="n">
-        <v>0</v>
+      <c r="L56" s="9" t="n">
+        <v>23</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="N56" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="O56" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>46</v>
+      </c>
+      <c r="O56" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="P56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>816513511474413568</t>
+          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>熊猫</t>
+          <t>中山东路228号新世纪广场A幢投放点</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>107</v>
+        <v>390</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -19494,52 +19902,56 @@
         <v>0</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="N57" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="O57" s="8" t="inlineStr">
-        <is>
-          <t>16☂</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="O57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="9" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q57" s="9" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>0a83fddcl1ln2kvc5pnasw3i47tp2gxk</t>
+          <t>1176722757207629824</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>中新大道投放点D</t>
+          <t>规划建设展览馆渗透</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>57</v>
+        <v>321</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -19555,31 +19967,35 @@
         <v>0</v>
       </c>
       <c r="M58" s="9" t="n">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="N58" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="O58" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>66</v>
+      </c>
+      <c r="O58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q58" s="9" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lumz6c4kkm73jypiiknrwb</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>中新大道南京气象局投放点</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -19588,40 +20004,48 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F59" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G59" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H59" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="N59" s="9" t="n">
-        <v>30</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L59" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="M59" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="N59" s="10" t="n">
+        <v>27</v>
       </c>
       <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -19630,17 +20054,17 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
+          <t>594063e60b264e419feea65370752c3f</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>中和路阿里中心·南京投放点A</t>
+          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -19649,40 +20073,48 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F60" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G60" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H60" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="N60" s="9" t="n">
-        <v>15</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L60" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M60" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N60" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="O60" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -19691,17 +20123,17 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>0a83933al1lzugykf9cbvd6hi2rqf8qn</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>环岛东路投放点C</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -19710,40 +20142,48 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G61" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H61" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="N61" s="9" t="n">
-        <v>15</v>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L61" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="10" t="n">
+        <v>68</v>
       </c>
       <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P61" s="9" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q61" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -19752,17 +20192,17 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>724131086902996992</t>
+          <t>e5189cd954054116aa19db28790cc606</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>迈皋桥公交场站渗透</t>
+          <t>25-晚峰-地铁站-高新地铁站-30</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -19771,59 +20211,67 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F62" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G62" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H62" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L62" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M62" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="N62" s="9" t="n">
-        <v>50</v>
+      <c r="M62" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="N62" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="O62" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
+        </is>
+      </c>
+      <c r="P62" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q62" s="8" t="inlineStr">
+        <is>
+          <t>36☂</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lj8cs3vsnr7r56rr3rgrgj</t>
+          <t>1153706342168625152</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>新浦路投放点B</t>
+          <t>鼓楼东南大学渗透</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -19832,68 +20280,76 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F63" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G63" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="N63" s="9" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="O63" s="8" t="inlineStr">
         <is>
-          <t>20☂</t>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P63" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q63" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>854196782092722176</t>
+          <t>1174618792617238528</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-居民区-好的渗透</t>
+          <t>南京市秦淮区朝天宫街道建邺路建邺路住宅小区</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>4</v>
@@ -19902,10 +20358,10 @@
         <v>3</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -19914,45 +20370,55 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L64" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="M64" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="N64" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="O64" s="7" t="n">
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="N64" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="O64" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P64" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q64" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>3a7505a7b50d415583454f997bbdbf0e</t>
+          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>六合区宁六路54号</t>
+          <t>中和路阿里中心·南京投放点A</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F65" s="3" t="n">
         <v>4</v>
@@ -19961,10 +20427,10 @@
         <v>3</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -19973,45 +20439,55 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L65" s="10" t="n">
-        <v>25</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="N65" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O65" s="7" t="n">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="N65" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="O65" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P65" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q65" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
+          <t>0a83a497l1lj8cs3vsnr7r56rr3rgrgj</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
+          <t>新浦路投放点B</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>4</v>
@@ -20020,10 +20496,10 @@
         <v>3</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -20032,45 +20508,55 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L66" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="M66" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="N66" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="O66" s="7" t="n">
-        <v>0</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="N66" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="O66" s="8" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="P66" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q66" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
+          <t>1098070146307002368</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>鼓楼区童家山2-3号楼</t>
+          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>4</v>
@@ -20079,10 +20565,10 @@
         <v>3</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>36</v>
+        <v>205</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -20091,36 +20577,46 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L67" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="M67" s="10" t="n">
-        <v>11</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="9" t="n">
+        <v>56</v>
       </c>
       <c r="N67" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="O67" s="7" t="n">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="O67" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P67" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q67" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>998560699433394176</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>广志路南京万达茂投放点D</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -20129,40 +20625,48 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L68" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="M68" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="N68" s="10" t="n">
-        <v>27</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="N68" s="9" t="n">
+        <v>45</v>
       </c>
       <c r="O68" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P68" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q68" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -20171,139 +20675,155 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>778851422965239808</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>25-早峰-居民区-仙林新村</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L69" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="M69" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="N69" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="O69" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L69" s="8" t="inlineStr">
+        <is>
+          <t>23☂</t>
+        </is>
+      </c>
+      <c r="M69" s="8" t="inlineStr">
+        <is>
+          <t>24☂</t>
+        </is>
+      </c>
+      <c r="N69" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="O69" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="P69" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q69" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>594063e60b264e419feea65370752c3f</t>
+          <t>788321551519383552</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
+          <t>玄武区鹤鸣路37号</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L70" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="M70" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="N70" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="O70" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L70" s="8" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="inlineStr">
+        <is>
+          <t>16☂</t>
+        </is>
+      </c>
+      <c r="N70" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="O70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q70" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
+          <t>816513511474413568</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>淮海路远洋国际中心投放点A</t>
+          <t>熊猫</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -20312,122 +20832,136 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>71</v>
+        <v>194</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L71" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="M71" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="N71" s="10" t="n">
-        <v>20</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="N71" s="9" t="n">
+        <v>48</v>
       </c>
       <c r="O71" s="8" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>16☂</t>
+        </is>
+      </c>
+      <c r="P71" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q71" s="8" t="inlineStr">
+        <is>
+          <t>38☂</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>1174618792617238528</t>
+          <t>1153706290333523968</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区朝天宫街道建邺路建邺路住宅小区</t>
+          <t>鼓楼区集庆门大街268号</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L72" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="M72" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="M72" s="9" t="n">
+        <v>31</v>
       </c>
       <c r="N72" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="O72" s="10" t="n">
-        <v>3</v>
+        <v>30</v>
+      </c>
+      <c r="O72" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>948393128847777792</t>
+          <t>724131086902996992</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>30-工作日-全天-地铁-明故宫2渗透</t>
+          <t>迈皋桥公交场站渗透</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -20436,40 +20970,48 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L73" s="10" t="n">
-        <v>26</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="N73" s="10" t="n">
-        <v>26</v>
+        <v>57</v>
+      </c>
+      <c r="N73" s="9" t="n">
+        <v>50</v>
       </c>
       <c r="O73" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P73" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q73" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -20478,141 +21020,147 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>3a7505a7b50d415583454f997bbdbf0e</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>六合区宁六路54号</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
         <v>30</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L74" s="8" t="inlineStr">
-        <is>
-          <t>42☂</t>
-        </is>
-      </c>
-      <c r="M74" s="8" t="inlineStr">
-        <is>
-          <t>76☂</t>
-        </is>
-      </c>
-      <c r="N74" s="9" t="n">
-        <v>71</v>
-      </c>
-      <c r="O74" s="10" t="n">
-        <v>20</v>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="L74" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M74" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="N74" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q74" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>554207268614606848</t>
+          <t>1098069901166710784</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
+          <t>25-全天-地铁站-工业大学地铁站2号口渗透</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L75" s="10" t="n">
-        <v>24</v>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="n">
+        <v>32</v>
       </c>
       <c r="M75" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="N75" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="O75" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="N75" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="O75" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P75" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q75" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>1098069901166710784</t>
+          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-工业大学地铁站2号口渗透</t>
+          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -20621,204 +21169,222 @@
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L76" s="9" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="M76" s="10" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N76" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="O76" s="10" t="n">
-        <v>8</v>
+        <v>28</v>
+      </c>
+      <c r="O76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q76" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>1174597131085402112</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-地铁站-云南路地铁站渗透</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L77" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="F77" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H77" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="M77" s="8" t="inlineStr">
-        <is>
-          <t>17☂</t>
-        </is>
-      </c>
-      <c r="N77" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="O77" s="10" t="n">
-        <v>12</v>
+      <c r="M77" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="N77" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="O77" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P77" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q77" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>778851422965239808</t>
+          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-仙林新村</t>
+          <t>淮海路远洋国际中心投放点A</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L78" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="M78" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="F78" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H78" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L78" s="8" t="inlineStr">
-        <is>
-          <t>23☂</t>
-        </is>
-      </c>
-      <c r="M78" s="8" t="inlineStr">
-        <is>
-          <t>24☂</t>
-        </is>
-      </c>
-      <c r="N78" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="O78" s="9" t="n">
-        <v>23</v>
+      <c r="N78" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="O78" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P78" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q78" s="8" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>948393128847777792</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>30-工作日-全天-地铁-明故宫2渗透</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>58</v>
+        <v>215</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -20827,40 +21393,46 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L79" s="8" t="inlineStr">
-        <is>
-          <t>11☂</t>
-        </is>
-      </c>
-      <c r="M79" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="N79" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="O79" s="9" t="n">
-        <v>23</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L79" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="M79" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N79" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="O79" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P79" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q79" s="8" t="inlineStr">
+        <is>
+          <t>52☂</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>1153706291117858816</t>
+          <t>554207268614606848</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
+          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -20872,16 +21444,16 @@
         <v>50</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H80" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>395</v>
+        <v>291</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -20890,33 +21462,41 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L80" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="M80" s="9" t="n">
-        <v>167</v>
+        <v>24</v>
+      </c>
+      <c r="M80" s="10" t="n">
+        <v>31</v>
       </c>
       <c r="N80" s="9" t="n">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="O80" s="8" t="inlineStr">
         <is>
-          <t>53☂</t>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P80" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q80" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>0a83612el1l7zifsq9sdudan8qjz6v28</t>
+          <t>1153706291117858816</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>中华路夫子庙秦淮风光带投放点G</t>
+          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -20930,19 +21510,19 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F81" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G81" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I81" s="3" t="n">
-        <v>56</v>
+        <v>490</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -20951,19 +21531,27 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L81" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M81" s="9" t="n">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="N81" s="9" t="n">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="O81" s="8" t="inlineStr">
+        <is>
+          <t>53☂</t>
+        </is>
+      </c>
+      <c r="P81" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q81" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -20972,38 +21560,38 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>732956028185985024</t>
+          <t>1174621727109263360</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>下马坊地铁站</t>
+          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F82" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H82" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G82" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H82" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I82" s="3" t="n">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -21012,38 +21600,42 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L82" s="10" t="n">
-        <v>25</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="n">
+        <v>54</v>
       </c>
       <c r="M82" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N82" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="O82" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>71</v>
+      </c>
+      <c r="O82" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P82" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q82" s="10" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>0a838699l1lzri8zeup3f4zan2nxpmck</t>
+          <t>0a83612el1l7zifsq9sdudan8qjz6v28</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>童卫路南理工科技创新园投放点</t>
+          <t>中华路夫子庙秦淮风光带投放点G</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -21052,19 +21644,19 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F83" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G83" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I83" s="3" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -21073,33 +21665,41 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L83" s="10" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="M83" s="9" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="N83" s="9" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="O83" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
+        </is>
+      </c>
+      <c r="P83" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q83" s="8" t="inlineStr">
+        <is>
+          <t>26☂</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>857508296047517696</t>
+          <t>732956028185985024</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2b</t>
+          <t>下马坊地铁站</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -21113,19 +21713,19 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F84" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H84" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G84" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I84" s="3" t="n">
-        <v>103</v>
+        <v>226</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -21134,38 +21734,46 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L84" s="9" t="n">
-        <v>21</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="n">
+        <v>25</v>
       </c>
       <c r="M84" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="N84" s="10" t="n">
-        <v>17</v>
+        <v>50</v>
+      </c>
+      <c r="N84" s="9" t="n">
+        <v>40</v>
       </c>
       <c r="O84" s="8" t="inlineStr">
         <is>
-          <t>23☂</t>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P84" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q84" s="8" t="inlineStr">
+        <is>
+          <t>43☂</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>852043013396557824</t>
+          <t>0a838699l1lzri8zeup3f4zan2nxpmck</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>玄武区长江路108号</t>
+          <t>童卫路南理工科技创新园投放点</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -21174,19 +21782,19 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F85" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H85" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G85" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I85" s="3" t="n">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -21195,38 +21803,46 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L85" s="9" t="n">
-        <v>97</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L85" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="M85" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="N85" s="10" t="n">
-        <v>17</v>
+        <v>41</v>
+      </c>
+      <c r="N85" s="9" t="n">
+        <v>53</v>
       </c>
       <c r="O85" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
+        </is>
+      </c>
+      <c r="P85" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q85" s="8" t="inlineStr">
+        <is>
+          <t>22☂</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>1206467184454987776</t>
+          <t>857508296047517696</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
+          <t>钟灵街2b</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -21235,19 +21851,19 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F86" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H86" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G86" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I86" s="3" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -21256,59 +21872,67 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L86" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="M86" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="N86" s="9" t="n">
-        <v>38</v>
+        <v>21</v>
+      </c>
+      <c r="M86" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="N86" s="10" t="n">
+        <v>17</v>
       </c>
       <c r="O86" s="8" t="inlineStr">
         <is>
-          <t>25☂</t>
+          <t>23☂</t>
+        </is>
+      </c>
+      <c r="P86" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q86" s="8" t="inlineStr">
+        <is>
+          <t>20☂</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>554207268778184704</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路3号口</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H87" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>233</v>
+        <v>359</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -21317,38 +21941,46 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L87" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="M87" s="9" t="n">
-        <v>55</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>42☂</t>
+        </is>
+      </c>
+      <c r="M87" s="8" t="inlineStr">
+        <is>
+          <t>76☂</t>
+        </is>
       </c>
       <c r="N87" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="O87" s="8" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>71</v>
+      </c>
+      <c r="O87" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="P87" s="9" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q87" s="9" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
+          <t>852043013396557824</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁口-仙林中心站1号口</t>
+          <t>玄武区长江路108号</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -21357,19 +21989,19 @@
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>577</v>
+        <v>465</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -21378,38 +22010,46 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L88" s="9" t="n">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="M88" s="9" t="n">
-        <v>209</v>
-      </c>
-      <c r="N88" s="9" t="n">
-        <v>215</v>
+        <v>56</v>
+      </c>
+      <c r="N88" s="10" t="n">
+        <v>17</v>
       </c>
       <c r="O88" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
+        </is>
+      </c>
+      <c r="P88" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q88" s="8" t="inlineStr">
+        <is>
+          <t>61☂</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>584636981105418240</t>
+          <t>1206467184454987776</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-羊山公园2号口</t>
+          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -21418,19 +22058,19 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>415</v>
+        <v>174</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -21439,47 +22079,55 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L89" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="M89" s="9" t="n">
-        <v>146</v>
+        <v>46</v>
+      </c>
+      <c r="M89" s="10" t="n">
+        <v>18</v>
       </c>
       <c r="N89" s="9" t="n">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="O89" s="8" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>25☂</t>
+        </is>
+      </c>
+      <c r="P89" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q89" s="8" t="inlineStr">
+        <is>
+          <t>22☂</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>1174621727109263360</t>
+          <t>554207268778184704</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
+          <t>25-晚峰-地铁站-柳州东路3号口</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F90" s="3" t="n">
         <v>4</v>
@@ -21488,10 +22136,10 @@
         <v>4</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>178</v>
+        <v>308</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -21500,36 +22148,46 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L90" s="9" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="M90" s="9" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="N90" s="9" t="n">
-        <v>71</v>
-      </c>
-      <c r="O90" s="10" t="n">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P90" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q90" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>1153706291117858816</t>
+          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
+          <t>25-全天-地铁口-仙林中心站1号口</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -21538,19 +22196,19 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>395</v>
+        <v>816</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -21563,34 +22221,42 @@
         </is>
       </c>
       <c r="L91" s="9" t="n">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="M91" s="9" t="n">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="N91" s="9" t="n">
-        <v>161</v>
+        <v>215</v>
       </c>
       <c r="O91" s="8" t="inlineStr">
         <is>
-          <t>53☂</t>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="P91" s="9" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q91" s="8" t="inlineStr">
+        <is>
+          <t>50☂</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
+          <t>584636981105418240</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>石门坎地铁站3号口光华科技产业园投放点</t>
+          <t>25-全天-地铁-羊山公园2号口</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -21599,19 +22265,19 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>118</v>
+        <v>572</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -21624,34 +22290,42 @@
         </is>
       </c>
       <c r="L92" s="9" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="M92" s="9" t="n">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="N92" s="9" t="n">
-        <v>42</v>
+        <v>185</v>
       </c>
       <c r="O92" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
+        </is>
+      </c>
+      <c r="P92" s="9" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q92" s="8" t="inlineStr">
+        <is>
+          <t>25☂</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>816505037427507200</t>
+          <t>1153706291117858816</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>玄武区童卫路28-2号</t>
+          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -21660,19 +22334,19 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>282</v>
+        <v>490</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -21685,34 +22359,42 @@
         </is>
       </c>
       <c r="L93" s="9" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="M93" s="9" t="n">
-        <v>81</v>
+        <v>167</v>
       </c>
       <c r="N93" s="9" t="n">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="O93" s="8" t="inlineStr">
         <is>
-          <t>23☂</t>
+          <t>53☂</t>
+        </is>
+      </c>
+      <c r="P93" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q93" s="8" t="inlineStr">
+        <is>
+          <t>0☂</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>1153706290333523968</t>
+          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>鼓楼区集庆门大街268号</t>
+          <t>石门坎地铁站3号口光华科技产业园投放点</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -21721,19 +22403,19 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -21746,39 +22428,47 @@
         </is>
       </c>
       <c r="L94" s="9" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="M94" s="9" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="N94" s="9" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O94" s="8" t="inlineStr">
         <is>
           <t>0☂</t>
+        </is>
+      </c>
+      <c r="P94" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q94" s="8" t="inlineStr">
+        <is>
+          <t>60☂</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>1123869911569338368</t>
+          <t>816505037427507200</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>学衡路南京师范大学仙林校区投放点B</t>
+          <t>玄武区童卫路28-2号</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
@@ -21794,7 +22484,7 @@
         <v>4</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>139</v>
+        <v>487</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -21807,16 +22497,26 @@
         </is>
       </c>
       <c r="L95" s="9" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="N95" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="O95" s="9" t="n">
-        <v>23</v>
+        <v>128</v>
+      </c>
+      <c r="O95" s="8" t="inlineStr">
+        <is>
+          <t>23☂</t>
+        </is>
+      </c>
+      <c r="P95" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q95" s="8" t="inlineStr">
+        <is>
+          <t>86☂</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -21844,16 +22544,16 @@
         <v>10</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -21875,6 +22575,12 @@
         <v>16</v>
       </c>
       <c r="O96" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="P96" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q96" s="9" t="n">
         <v>26</v>
       </c>
     </row>
@@ -26114,7 +26820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -26132,6 +26838,8 @@
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26217,16 +26925,26 @@
           <t>07-12(日)</t>
         </is>
       </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>07-18(六)</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>07-19(日)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>0a835aeel1lkinjudbqkx66gewwuzmq6</t>
+          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科南门B</t>
+          <t>龙眠大道海丰小视科技中心(建设中)站点</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -26243,25 +26961,25 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -26274,18 +26992,24 @@
         <v>0</v>
       </c>
       <c r="O3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q3" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
+          <t>0a835aeel1lkinjudbqkx66gewwuzmq6</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道海丰小视科技中心(建设中)站点</t>
+          <t>高新-高校-金科南门B</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -26302,25 +27026,25 @@
         <v>11</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
@@ -26334,6 +27058,12 @@
       </c>
       <c r="O4" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q4" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -26361,25 +27091,25 @@
         <v>11</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L5" s="7" t="n">
@@ -26393,6 +27123,12 @@
       </c>
       <c r="O5" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -26420,25 +27156,25 @@
         <v>10</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -26452,6 +27188,12 @@
       </c>
       <c r="O6" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" s="9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -26479,25 +27221,25 @@
         <v>11</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -26512,6 +27254,12 @@
       <c r="O7" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="P7" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -26538,25 +27286,25 @@
         <v>11</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -26569,6 +27317,12 @@
         <v>0</v>
       </c>
       <c r="O8" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q8" s="9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -26597,25 +27351,25 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L9" s="7" t="n">
@@ -26630,6 +27384,12 @@
       <c r="O9" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="P9" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -26656,25 +27416,25 @@
         <v>11</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L10" s="7" t="n">
@@ -26689,16 +27449,22 @@
       <c r="O10" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="P10" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>1158030564174917632</t>
+          <t>1158030571808550912</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>东山头</t>
+          <t>1号门</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -26715,54 +27481,60 @@
         <v>10</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>0</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>33</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
+          <t>1158025279480332288</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>鹏山路东方·龙湖湾站点Z2</t>
+          <t>2号门</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -26771,19 +27543,19 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -26792,31 +27564,37 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="9" t="n">
-        <v>23</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>1158025287508230144</t>
+          <t>1158030564174917632</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>3号门</t>
+          <t>东山头</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -26826,23 +27604,23 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>492</v>
+        <v>33</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -26854,37 +27632,39 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>220☂</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>154☂</t>
-        </is>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="O13" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P13" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
+          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>土山路东域城站点A</t>
+          <t>鹏山路东方·龙湖湾站点Z2</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -26896,54 +27676,60 @@
         <v>11</v>
       </c>
       <c r="F14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="n">
-        <v>12</v>
+      <c r="L14" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O14" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
+          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>竹山路地铁1号口</t>
+          <t>土山路东域城站点A</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -26955,49 +27741,55 @@
         <v>11</v>
       </c>
       <c r="F15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H15" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="7" t="n">
-        <v>0</v>
+      <c r="M15" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="N15" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="O15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="9" t="n">
         <v>12</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lyxfkh7vjgmkyih6st4gkb</t>
+          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>经贸学院路保利·樾广场站点A</t>
+          <t>竹山路地铁1号口</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -27014,25 +27806,25 @@
         <v>11</v>
       </c>
       <c r="F16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H16" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L16" s="7" t="n">
@@ -27042,26 +27834,32 @@
         <v>0</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O16" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q16" s="9" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1158025279480332288</t>
+          <t>0a83a414l1lyxfkh7vjgmkyih6st4gkb</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>2号门</t>
+          <t>经贸学院路保利·樾广场站点A</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -27070,66 +27868,72 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H17" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="M17" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="7" t="n">
-        <v>0</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>889466722646794240</t>
+          <t>1158025287508230144</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>胜太东路江宁供销商厦站点</t>
+          <t>3号门</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>4</v>
@@ -27138,10 +27942,10 @@
         <v>3</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>24</v>
+        <v>580</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -27150,36 +27954,46 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="9" t="n">
-        <v>12</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>220☂</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>154☂</t>
+        </is>
       </c>
       <c r="N18" s="9" t="n">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="O18" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
+          <t>889466722646794240</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>高新-小区-瑾家珑熹台（南2门）</t>
+          <t>胜太东路江宁供销商厦站点</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -27191,49 +28005,55 @@
         <v>11</v>
       </c>
       <c r="F19" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="I19" s="3" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>0</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="O19" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="O19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q19" s="9" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>897042860272709632</t>
+          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>鹏山路中粮悦天地(建设中)站点B</t>
+          <t>高新-小区-瑾家珑熹台（南2门）</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -27250,54 +28070,60 @@
         <v>11</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="M20" s="9" t="n">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="O20" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="O20" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1158030570667700224</t>
+          <t>897042860272709632</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>美龄宫</t>
+          <t>鹏山路中粮悦天地(建设中)站点B</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -27306,52 +28132,58 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1387</v>
+        <v>120</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>436</v>
+        <v>22</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>396</v>
+        <v>22</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>555</v>
+        <v>22</v>
       </c>
       <c r="O21" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P21" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q21" s="9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1158030569614929920</t>
+          <t>1158030570667700224</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>海底世界站台</t>
+          <t>美龄宫</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -27368,49 +28200,55 @@
         <v>50</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>485</v>
+        <v>2348</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>143</v>
+        <v>436</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>199</v>
+        <v>396</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>143</v>
+        <v>555</v>
       </c>
       <c r="O22" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P22" s="9" t="n">
+        <v>532</v>
+      </c>
+      <c r="Q22" s="9" t="n">
+        <v>429</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>1158030573943451648</t>
+          <t>1158030569614929920</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>中山陵7号门</t>
+          <t>海底世界站台</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -27424,52 +28262,58 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>340</v>
+        <v>903</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="O23" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P23" s="9" t="n">
+        <v>341</v>
+      </c>
+      <c r="Q23" s="9" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>1158030568570548224</t>
+          <t>1158030573943451648</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>海底世界</t>
+          <t>中山陵7号门</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -27486,49 +28330,55 @@
         <v>15</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>212</v>
+        <v>806</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="O24" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P24" s="9" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1158030571808550912</t>
+          <t>1158030568570548224</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>1号门</t>
+          <t>海底世界</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -27542,41 +28392,47 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>56</v>
+        <v>388</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="O25" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="26">
@@ -27604,16 +28460,16 @@
         <v>11</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -27622,7 +28478,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L26" s="9" t="n">
@@ -27637,6 +28493,12 @@
       <c r="O26" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="P26" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -27663,16 +28525,16 @@
         <v>11</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -27681,7 +28543,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L27" s="10" t="n">
@@ -27696,6 +28558,12 @@
       <c r="O27" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="P27" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q27" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -27722,16 +28590,16 @@
         <v>11</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -27740,7 +28608,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L28" s="10" t="n">
@@ -27755,6 +28623,12 @@
       <c r="O28" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="P28" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q28" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -27781,16 +28655,16 @@
         <v>11</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -27799,7 +28673,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L29" s="10" t="n">
@@ -27814,6 +28688,12 @@
       <c r="O29" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="P29" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q29" s="9" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -27840,16 +28720,16 @@
         <v>11</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -27858,7 +28738,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L30" s="9" t="n">
@@ -27873,6 +28753,12 @@
       <c r="O30" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="P30" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q30" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -27899,16 +28785,16 @@
         <v>50</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1349</v>
+        <v>2234</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -27917,7 +28803,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L31" s="9" t="n">
@@ -27932,6 +28818,12 @@
       <c r="O31" s="10" t="n">
         <v>34</v>
       </c>
+      <c r="P31" s="9" t="n">
+        <v>639</v>
+      </c>
+      <c r="Q31" s="9" t="n">
+        <v>246</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -27958,16 +28850,16 @@
         <v>11</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>153</v>
+        <v>231</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -27991,6 +28883,12 @@
       <c r="O32" s="9" t="n">
         <v>34</v>
       </c>
+      <c r="P32" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -28017,16 +28915,16 @@
         <v>11</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -28050,6 +28948,12 @@
       <c r="O33" s="9" t="n">
         <v>22</v>
       </c>
+      <c r="P33" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -28076,16 +28980,16 @@
         <v>11</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>359</v>
+        <v>494</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -28109,6 +29013,12 @@
       <c r="O34" s="9" t="n">
         <v>63</v>
       </c>
+      <c r="P34" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -28135,16 +29045,16 @@
         <v>11</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -28168,6 +29078,12 @@
       <c r="O35" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="P35" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q35" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -28194,16 +29110,16 @@
         <v>11</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -28227,6 +29143,12 @@
       <c r="O36" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="P36" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q36" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -28253,16 +29175,16 @@
         <v>11</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -28286,6 +29208,12 @@
       <c r="O37" s="9" t="n">
         <v>22</v>
       </c>
+      <c r="P37" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -28312,16 +29240,16 @@
         <v>11</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -28345,6 +29273,12 @@
       <c r="O38" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="P38" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q38" s="9" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -28371,16 +29305,16 @@
         <v>11</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>177</v>
+        <v>232</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -28403,6 +29337,12 @@
       </c>
       <c r="O39" s="9" t="n">
         <v>11</v>
+      </c>
+      <c r="P39" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q39" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -28839,13 +29779,13 @@
         <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -28854,7 +29794,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -28868,22 +29808,22 @@
         <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -28897,22 +29837,22 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -28926,22 +29866,22 @@
         <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -28955,22 +29895,22 @@
         <v>26</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>45.9%</t>
         </is>
       </c>
     </row>
@@ -28984,22 +29924,22 @@
         <v>9</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -29013,22 +29953,22 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -29042,22 +29982,22 @@
         <v>13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -29071,22 +30011,22 @@
         <v>3</v>
       </c>
       <c r="C11" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -29100,22 +30040,22 @@
         <v>9</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -29408,13 +30348,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -29423,7 +30363,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>93.3%</t>
         </is>
       </c>
     </row>
@@ -29437,22 +30377,22 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>67.2%</t>
         </is>
       </c>
     </row>
@@ -29466,22 +30406,22 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -29495,22 +30435,22 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="E6" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -29524,22 +30464,22 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -46,11 +46,11 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <color rgb="00FF0000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="微软雅黑"/>
-      <color rgb="00FF0000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -111,15 +111,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -553,12 +553,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -603,12 +603,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>97.8%</t>
         </is>
       </c>
     </row>
@@ -641,14 +641,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20260801 ~ 20260802</t>
+          <t>数据范围: 20260801 ~ 20260803</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 0天, 周末: 2天</t>
+          <t>工作日: 1天, 周末: 2天</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -698,6 +698,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,33 +764,38 @@
           <t>补足率</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>08-03(一)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lfmy2n3ksr3ftxi64ycwsh</t>
+          <t>0a89826bl1l59cpgauqj57mi6t47n2cn</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>钟阜路建宁路55号院投放点</t>
+          <t>软件大道润和创智中心投放点</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -810,33 +816,36 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
+          <t>0a832df0l1lzt76pzug378mk28gwp223</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>九家圩路世茂外滩新城投放点A</t>
+          <t>西春路云密城投放点A</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -857,21 +866,24 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L4" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>1178909948933013504</t>
+          <t>0a83e334l1l38kski9q2syd6gczb42g8</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-商圈-香格里拉渗透</t>
+          <t>云密路汇智城(建设中)投放点</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -880,10 +892,10 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -904,21 +916,24 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L5" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0a83612el1lx8dxfbxif2vsjehjqtwrj</t>
+          <t>1030603996343898112</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>江山路投放点H</t>
+          <t>学衡路南京师范大学仙林校区投放点B</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -927,10 +942,10 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -951,21 +966,24 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L6" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>1174621727109263360</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -974,10 +992,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -998,21 +1016,24 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L7" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>e5189cd954054116aa19db28790cc606</t>
+          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-高新地铁站-30</t>
+          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1021,10 +1042,10 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1045,33 +1066,36 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L8" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>554207268778184704</t>
+          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路3号口</t>
+          <t>中和路阿里中心·南京投放点A</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -1092,33 +1116,36 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L9" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>594063e60b264e419feea65370752c3f</t>
+          <t>0a836146l1leh9rgc924wv39dv6m7mvs</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
+          <t>梦都大街东地铁站4B口江苏中烟工业有限责任公司南京卷烟投放点A</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -1139,33 +1166,36 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L10" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>1077190082872029184</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>南京市建邺区沙洲街道嘉陵江东街地铁站</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -1186,33 +1216,36 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L11" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>597639530744799232</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>南京市建邺区沙洲街道中胜地铁站5号口明基医院</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1233,33 +1266,36 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L12" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1l77t6e64cbw8rqk9kqakwh</t>
+          <t>0a83a497l1lj8cs3vsnr7r56rr3rgrgj</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>江山路明发滨江新城三期投放点A</t>
+          <t>新浦路投放点B</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -1280,33 +1316,36 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>732955501476995072</t>
+          <t>1206467184454987776</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-威尼斯三街区</t>
+          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -1327,33 +1366,36 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L14" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>626976116946362368</t>
+          <t>1098069901166710784</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-润泰花园东30</t>
+          <t>25-全天-地铁站-工业大学地铁站2号口渗透</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -1374,33 +1416,36 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L15" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>732956005347999744</t>
+          <t>1153706318256898048</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城十街区</t>
+          <t>浦口大道投放点渗透</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0</v>
@@ -1421,16 +1466,19 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>777073646895747072</t>
+          <t>0a83612el1lx8dxfbxif2vsjehjqtwrj</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>25-全天-商场-1914街区</t>
+          <t>江山路投放点H</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1440,44 +1488,47 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="L17" s="8" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>732955785461030912</t>
+          <t>732956005347999744</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城5街区</t>
+          <t>25-早峰-居民区-天润城十街区</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1491,40 +1542,43 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="L18" s="8" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>732955983377653760</t>
+          <t>732955785461030912</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城1-4街区</t>
+          <t>25-早峰-居民区-天润城5街区</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1538,45 +1592,48 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="L19" s="8" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>732955258519240704</t>
+          <t>0a83b42bl1lurmqhqrwviu2qvdiirgcs</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路1号口</t>
+          <t>安德门大街楚翘城投放点G</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1585,40 +1642,43 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="L20" s="8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>0a838c9fl1l9eahd7x3xm2ecvtjwbbdv</t>
+          <t>0a83384dl1lbqqk7xa7gxkbhz9gpmyzs</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>沙县小吃(南京第099店)凤翔新城投放点</t>
+          <t>西春路48号云密城投放点</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1628,49 +1688,52 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="L21" s="8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>0a835aeel1lazxwqtfa664yxtxendmyu</t>
+          <t>1174535930061524992</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>汇智路南海生物科技园投放点</t>
+          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1679,45 +1742,48 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="L22" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a8398f6l1lw2mup86pcczvtx5uv56gv</t>
+          <t>854196782092722176</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>宁双路软件谷垠坤·南京大数据产业基地投放点</t>
+          <t>工作日-全天-居民区-好的渗透</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1726,92 +1792,98 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="L23" s="8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>0a83b42bl1lurmqhqrwviu2qvdiirgcs</t>
+          <t>0a83eb4fl1lyh6gadse7cuxyngppbre5</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>安德门大街楚翘城投放点G</t>
+          <t>中胜地铁站2C口投放点</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="L24" s="8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0a89826bl1l59cpgauqj57mi6t47n2cn</t>
+          <t>724131086902996992</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>软件大道润和创智中心投放点</t>
+          <t>迈皋桥公交场站渗透</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1820,327 +1892,348 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="L25" s="8" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a832df0l1lzt76pzug378mk28gwp223</t>
+          <t>0a836587l1lduskfcd7fg98zc4m8acq2</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>西春路云密城投放点A</t>
+          <t>望江路正荣润锦城投放点C</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="L26" s="8" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>0a83384dl1lbqqk7xa7gxkbhz9gpmyzs</t>
+          <t>1153706370345959424</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>西春路48号云密城投放点</t>
+          <t>新浦路长江时代·雍澜悦府投放点渗透</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="L27" s="8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>0a83e334l1l38kski9q2syd6gczb42g8</t>
+          <t>0a836587l1lfmy2n3ksr3ftxi64ycwsh</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>云密路汇智城(建设中)投放点</t>
+          <t>钟阜路建宁路55号院投放点</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>584636981105418240</t>
+          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-羊山公园2号口</t>
+          <t>九家圩路世茂外滩新城投放点A</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
+          <t>1178909948933013504</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁口-仙林中心站1号口</t>
+          <t>25-早峰-商圈-香格里拉渗透</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>684268350256898048</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-学则路</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>1098070146307002368</t>
+          <t>e5189cd954054116aa19db28790cc606</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
+          <t>25-晚峰-地铁站-高新地铁站-30</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2149,45 +2242,48 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>1023193174134530048</t>
+          <t>554207268778184704</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>仙林大道投放点N</t>
+          <t>25-晚峰-地铁站-柳州东路3号口</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -2196,45 +2292,48 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>162</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>998560699433394176</t>
+          <t>594063e60b264e419feea65370752c3f</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>广志路南京万达茂投放点D</t>
+          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -2243,374 +2342,398 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>778851422965239808</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-仙林新村</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>213</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>161</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>1030603996343898112</t>
+          <t>0a836146l1l77t6e64cbw8rqk9kqakwh</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>学衡路南京师范大学仙林校区投放点B</t>
+          <t>江山路明发滨江新城三期投放点A</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>0a83eb4fl1lz4hvkvkpdqc8mwis9httv</t>
+          <t>732955501476995072</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>仙林中心(地铁站)投放点A</t>
+          <t>25-早峰-居民区-威尼斯三街区</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
+          <t>626976116946362368</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>中山东路228号新世纪广场A幢投放点</t>
+          <t>25-早峰-居民区-润泰花园东30</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>1153706291117858816</t>
+          <t>777073646895747072</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
+          <t>25-全天-商场-1914街区</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
+          <t>732955983377653760</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
+          <t>25-早峰-居民区-天润城1-4街区</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>1176842717252255744</t>
+          <t>732955258519240704</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>三元巷6号三元公寓投放点渗透</t>
+          <t>25-晚峰-地铁站-柳州东路1号口</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -2619,92 +2742,98 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>1174622373773963264</t>
+          <t>0a838c9fl1l9eahd7x3xm2ecvtjwbbdv</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道常府街地铁站</t>
+          <t>沙县小吃(南京第099店)凤翔新城投放点</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>133</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>1174621727109263360</t>
+          <t>0a835aeel1lazxwqtfa664yxtxendmyu</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
+          <t>汇智路南海生物科技园投放点</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -2713,139 +2842,148 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>1174627346911133696</t>
+          <t>0a8398f6l1lw2mup86pcczvtx5uv56gv</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道户部街长发银座</t>
+          <t>宁双路软件谷垠坤·南京大数据产业基地投放点</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>1174535930061524992</t>
+          <t>584636981105418240</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
+          <t>25-全天-地铁-羊山公园2号口</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
+          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>石门坎地铁站3号口光华科技产业园投放点</t>
+          <t>25-全天-地铁口-仙林中心站1号口</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -2854,139 +2992,148 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="n">
+        <v>231</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
+          <t>684268350256898048</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>淮海路远洋国际中心投放点A</t>
+          <t>25-全天-地铁-学则路</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>5331e3a58a50481dbc8e7273561f4e25</t>
+          <t>1098070146307002368</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-地铁站-夫子庙2号口-10</t>
+          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>874549501386596352</t>
+          <t>1023193174134530048</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
+          <t>仙林大道投放点N</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -2995,45 +3142,48 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>f72b5a964e164de7930e4077acb795b0</t>
+          <t>998560699433394176</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道中华路宜必思酒店(南京夫子庙店)</t>
+          <t>广志路南京万达茂投放点D</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -3042,92 +3192,98 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lhbuznwmz926qn65svufex</t>
+          <t>778851422965239808</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>中山南路280号张府园小区投放点A</t>
+          <t>25-早峰-居民区-仙林新村</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>732951617602912256</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -3136,45 +3292,48 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>732956028185985024</t>
+          <t>0a83eb4fl1lz4hvkvkpdqc8mwis9httv</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>下马坊地铁站</t>
+          <t>仙林中心(地铁站)投放点A</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -3183,45 +3342,48 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>854249531796738048</t>
+          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-金马路地铁站</t>
+          <t>中山东路228号新世纪广场A幢投放点</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -3230,45 +3392,48 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="n">
+        <v>174</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>816505037427507200</t>
+          <t>1153706291117858816</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>玄武区童卫路28-2号</t>
+          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -3277,45 +3442,48 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
+          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
+          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -3324,92 +3492,98 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lbvs3sx44tiwdb7kvc7kap</t>
+          <t>1176842717252255744</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>苏园路江苏软件园二期投放点A</t>
+          <t>三元巷6号三元公寓投放点渗透</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>857508296047517696</t>
+          <t>1174622373773963264</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2b</t>
+          <t>南京市秦淮区洪武路街道常府街地铁站</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -3418,374 +3592,398 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="n">
+        <v>318</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>0a838699l1lzri8zeup3f4zan2nxpmck</t>
+          <t>1174627346911133696</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>童卫路南理工科技创新园投放点</t>
+          <t>南京市秦淮区洪武路街道户部街长发银座</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>788321551519383552</t>
+          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>玄武区鹤鸣路37号</t>
+          <t>石门坎地铁站3号口光华科技产业园投放点</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
+          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2A</t>
+          <t>淮海路远洋国际中心投放点A</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>0a833ecdl1lcqyspwc7ejjhwh8vz5pfp</t>
+          <t>5331e3a58a50481dbc8e7273561f4e25</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>石狮路辅路INS Mall·浪里投放点B</t>
+          <t>工作日-全天-地铁站-夫子庙2号口-10</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>948393128847777792</t>
+          <t>874549501386596352</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>30-工作日-全天-地铁-明故宫2渗透</t>
+          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
+          <t>f72b5a964e164de7930e4077acb795b0</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>大行宫6号口渗透</t>
+          <t>南京市秦淮区洪武路街道中华路宜必思酒店(南京夫子庙店)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>816513511474413568</t>
+          <t>0a83a497l1lhbuznwmz926qn65svufex</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>熊猫</t>
+          <t>中山南路280号张府园小区投放点A</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>732951617602912256</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -3794,186 +3992,198 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>1176722757207629824</t>
+          <t>732956028185985024</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>规划建设展览馆渗透</t>
+          <t>下马坊地铁站</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>754365148238000128</t>
+          <t>854249531796738048</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>玄武区四牌楼63号</t>
+          <t>25-全天-地铁站-金马路地铁站</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>854196782092722176</t>
+          <t>816505037427507200</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-居民区-好的渗透</t>
+          <t>玄武区童卫路28-2号</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>732955102642126848</t>
+          <t>0a836587l1lbvs3sx44tiwdb7kvc7kap</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>玄武区丹凤街69号</t>
+          <t>苏园路江苏软件园二期投放点A</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -3982,139 +4192,148 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
+          <t>857508296047517696</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
+          <t>钟灵街2b</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>732954989023625216</t>
+          <t>0a838699l1lzri8zeup3f4zan2nxpmck</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-地铁站-鸡鸣寺地铁站渗透</t>
+          <t>童卫路南理工科技创新园投放点</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
+          <t>788321551519383552</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>中和路阿里中心·南京投放点A</t>
+          <t>玄武区鹤鸣路37号</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -4123,233 +4342,248 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1leh9rgc924wv39dv6m7mvs</t>
+          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>梦都大街东地铁站4B口江苏中烟工业有限责任公司南京卷烟投放点A</t>
+          <t>钟灵街2A</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
+          <t>0a833ecdl1lcqyspwc7ejjhwh8vz5pfp</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>集贤路鼓楼创新广场投放点B</t>
+          <t>石狮路辅路INS Mall·浪里投放点B</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>1206516292750213120</t>
+          <t>948393128847777792</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>中山北路宏图大厦渗透</t>
+          <t>30-工作日-全天-地铁-明故宫2渗透</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
+          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>鼓楼区童家山2-3号楼</t>
+          <t>大行宫6号口渗透</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>f25bafa6cea44ac49303d053fcda9045</t>
+          <t>816513511474413568</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道中胜地铁站2A口</t>
+          <t>熊猫</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -4358,45 +4592,48 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L79" s="9" t="n">
+        <v>129</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>1077190082872029184</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道嘉陵江东街地铁站</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -4405,139 +4642,148 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="n">
+        <v>167</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>d0f80f128e074902a9109772ebc0edc6</t>
+          <t>1176722757207629824</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道中胜地铁站1A</t>
+          <t>规划建设展览馆渗透</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>1174597131085402112</t>
+          <t>754365148238000128</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-地铁站-云南路地铁站渗透</t>
+          <t>玄武区四牌楼63号</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>0a83eb4fl1lyh6gadse7cuxyngppbre5</t>
+          <t>732955102642126848</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>中胜地铁站2C口投放点</t>
+          <t>玄武区丹凤街69号</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -4546,92 +4792,98 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L83" s="9" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>1076695373435187200</t>
+          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区吴侯街地铁站</t>
+          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L84" s="9" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>0a8331f1l1lfxks8nftfew7gr7y37gvu</t>
+          <t>732954989023625216</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>西城路建邺科技创新产业园投放点A</t>
+          <t>工作日-全天-地铁站-鸡鸣寺地铁站渗透</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -4640,40 +4892,43 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L85" s="9" t="n">
+        <v>176</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>1153706290333523968</t>
+          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>鼓楼区集庆门大街268号</t>
+          <t>集贤路鼓楼创新广场投放点B</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -4690,37 +4945,40 @@
         <v>15</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L86" s="9" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>597639530744799232</t>
+          <t>1206516292750213120</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道中胜地铁站5号口明基医院</t>
+          <t>中山北路宏图大厦渗透</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -4730,143 +4988,152 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L87" s="9" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>554207268614606848</t>
+          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
+          <t>鼓楼区童家山2-3号楼</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L88" s="9" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>724131086902996992</t>
+          <t>f25bafa6cea44ac49303d053fcda9045</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>迈皋桥公交场站渗透</t>
+          <t>南京市建邺区沙洲街道中胜地铁站2A口</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L89" s="9" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>1177090611149664256</t>
+          <t>d0f80f128e074902a9109772ebc0edc6</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>柚米社区</t>
+          <t>南京市建邺区沙洲街道中胜地铁站1A</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -4875,45 +5142,48 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L90" s="9" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>723758596467601408</t>
+          <t>1174597131085402112</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>全天-居民区-颐和府邸投放点A</t>
+          <t>25-早峰-地铁站-云南路地铁站渗透</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -4922,181 +5192,193 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L91" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>1008726508792258560</t>
+          <t>1076695373435187200</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-南砖新村</t>
+          <t>南京市建邺区吴侯街地铁站</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L92" s="9" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>857062808558088192</t>
+          <t>0a8331f1l1lfxks8nftfew7gr7y37gvu</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>23早高峰-全天-居民区-金浦御龙湾D区</t>
+          <t>西城路建邺科技创新产业园投放点A</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L93" s="9" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>690088208255492096</t>
+          <t>1153706290333523968</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>迈化路长营村15号小区投放点</t>
+          <t>鼓楼区集庆门大街268号</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L94" s="9" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>892408647821217792</t>
+          <t>554207268614606848</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-融创玉兰公馆</t>
+          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5106,44 +5388,47 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L95" s="9" t="n">
+        <v>193</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>1084472481506824192</t>
+          <t>1177090611149664256</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>栖霞区宜春街40号</t>
+          <t>柚米社区</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -5153,44 +5438,47 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L96" s="9" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>836164410974330880</t>
+          <t>723758596467601408</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>全天-居民区-愉景湾北门</t>
+          <t>全天-居民区-颐和府邸投放点A</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -5207,37 +5495,40 @@
         <v>20</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L97" s="9" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>854565226235502592</t>
+          <t>1008726508792258560</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>北苑西路枫桥雅筑投放点渗透</t>
+          <t>25-早峰-居民区-南砖新村</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -5254,37 +5545,40 @@
         <v>25</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>754151861948555264</t>
+          <t>857062808558088192</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>23早高峰-全天-居民区-金浦御龙湾F区</t>
+          <t>23早高峰-全天-居民区-金浦御龙湾D区</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -5301,37 +5595,40 @@
         <v>25</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L99" s="9" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>754151029387345920</t>
+          <t>690088208255492096</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>工作日-早峰-居民区-颐和家园</t>
+          <t>迈化路长营村15号小区投放点</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -5348,37 +5645,40 @@
         <v>20</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L100" s="9" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>853114235179171840</t>
+          <t>892408647821217792</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>全天-居民区-和燕花苑</t>
+          <t>25-早峰-居民区-融创玉兰公馆</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5395,42 +5695,45 @@
         <v>25</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L101" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lj8cs3vsnr7r56rr3rgrgj</t>
+          <t>1084472481506824192</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>新浦路投放点B</t>
+          <t>栖霞区宜春街40号</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -5442,230 +5745,245 @@
         <v>25</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L102" s="9" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>1206467184454987776</t>
+          <t>836164410974330880</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
+          <t>全天-居民区-愉景湾北门</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L103" s="9" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>1098069901166710784</t>
+          <t>854565226235502592</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-工业大学地铁站2号口渗透</t>
+          <t>北苑西路枫桥雅筑投放点渗透</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L104" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lduskfcd7fg98zc4m8acq2</t>
+          <t>754151861948555264</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>望江路正荣润锦城投放点C</t>
+          <t>23早高峰-全天-居民区-金浦御龙湾F区</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L105" s="9" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>1153706318256898048</t>
+          <t>754151029387345920</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>浦口大道投放点渗透</t>
+          <t>工作日-早峰-居民区-颐和家园</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="F106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L106" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>1153706370345959424</t>
+          <t>853114235179171840</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>新浦路长江时代·雍澜悦府投放点渗透</t>
+          <t>全天-居民区-和燕花苑</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -5677,26 +5995,29 @@
         <v>25</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L107" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="108">
@@ -5724,26 +6045,29 @@
         <v>15</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L108" s="9" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="109">
@@ -5771,26 +6095,29 @@
         <v>10</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L109" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -9723,7 +10050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9737,6 +10064,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9802,33 +10130,38 @@
           <t>补足率</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>08-03(一)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
+          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>胜太西路47号汇金新天地广场站点</t>
+          <t>土山路东域城站点A</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -9849,16 +10182,19 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="L3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
+          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>吉印大道融信·铂岸中心站点</t>
+          <t>胜太西路47号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -9868,44 +10204,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
+          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
+          <t>吉印大道融信·铂岸中心站点</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -9915,44 +10254,47 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
+          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>胜太西路45号汇金新天地广场站点</t>
+          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -9962,44 +10304,47 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
+          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>严南路金辉禹洲金陵铭著站点A</t>
+          <t>胜太西路45号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10009,44 +10354,47 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
+          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
+          <t>严南路金辉禹洲金陵铭著站点A</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -10056,44 +10404,47 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
+          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>平泰街太平花苑站点</t>
+          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -10110,37 +10461,40 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
+          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>胜太西路天琪雅居站点</t>
+          <t>平泰街太平花苑站点</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -10150,44 +10504,47 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
+          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>胜太西路太平花苑北苑站点C</t>
+          <t>胜太西路天琪雅居站点</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -10197,44 +10554,47 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1l4y8jhxjgrp6t9eecq3anb</t>
+          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>胜太路77-4号胜泰新寓站点</t>
+          <t>胜太西路太平花苑北苑站点C</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -10244,91 +10604,97 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>1158030570667700224</t>
+          <t>0a8399c6l1l4y8jhxjgrp6t9eecq3anb</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>美龄宫</t>
+          <t>胜太路77-4号胜泰新寓站点</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1158030572869709824</t>
+          <t>1158030570667700224</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>东沟停车场</t>
+          <t>美龄宫</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -10342,40 +10708,43 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>668</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1158030569614929920</t>
+          <t>1158030572869709824</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>海底世界站台</t>
+          <t>东沟停车场</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -10389,40 +10758,43 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>243</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1158030573943451648</t>
+          <t>1158030569614929920</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>中山陵7号门</t>
+          <t>海底世界站台</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -10439,37 +10811,40 @@
         <v>20</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>209</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1158025287508230144</t>
+          <t>1158030573943451648</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>3号门</t>
+          <t>中山陵7号门</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -10483,40 +10858,43 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1158030563076009984</t>
+          <t>1158025287508230144</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺公园1</t>
+          <t>3号门</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -10533,37 +10911,40 @@
         <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1158030568570548224</t>
+          <t>1158030563076009984</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>海底世界</t>
+          <t>灵谷寺公园1</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -10580,37 +10961,40 @@
         <v>10</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1158030571808550912</t>
+          <t>1158030568570548224</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>1号门</t>
+          <t>海底世界</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -10627,37 +11011,40 @@
         <v>10</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1158025279480332288</t>
+          <t>1158030571808550912</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>2号门</t>
+          <t>1号门</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -10667,49 +11054,52 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>0a83f070l1l3nefxhf3epn6wjp3gniq2</t>
+          <t>1158025279480332288</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>高新-地铁-交院地铁站2号口b</t>
+          <t>2号门</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -10718,40 +11108,43 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a83975dl1l7x9tn88g4jtig37jrdaaw</t>
+          <t>0a83f070l1l3nefxhf3epn6wjp3gniq2</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>知行路江宁高新区人才公寓站点P</t>
+          <t>高新-地铁-交院地铁站2号口b</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -10761,44 +11154,47 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
+          <t>0a83975dl1l7x9tn88g4jtig37jrdaaw</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>高新-小区-瑾家珑熹台（南2门）-工作日-早高峰-12</t>
+          <t>知行路江宁高新区人才公寓站点P</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -10815,37 +11211,40 @@
         <v>11</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0a898873l1l2z5yttrk27pq8kwxsxux8</t>
+          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>高新-小区-瑾家珑熹台(南1门)-工作日-早高峰-12</t>
+          <t>高新-小区-瑾家珑熹台（南2门）-工作日-早高峰-12</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -10855,49 +11254,52 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
+          <t>0a898873l1l2z5yttrk27pq8kwxsxux8</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点H</t>
+          <t>高新-小区-瑾家珑熹台(南1门)-工作日-早高峰-12</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -10909,37 +11311,40 @@
         <v>11</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>0a836758l1lnzcr39623ggbxyhbddncg</t>
+          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点G</t>
+          <t>天元东路辅路南京义乌小商品城站点H</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -10949,91 +11354,97 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>0a837fa4l1l27tpydpm8gjqn4qaqm6ef</t>
+          <t>0a836758l1lnzcr39623ggbxyhbddncg</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>高新-商圈-中粮药膳鸡-全周-午晚高峰-30</t>
+          <t>天元东路辅路南京义乌小商品城站点G</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>897042860272709632</t>
+          <t>0a837fa4l1l27tpydpm8gjqn4qaqm6ef</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>高新-商圈-中粮悦天地西北门B-全周-午晚高峰-50</t>
+          <t>高新-商圈-中粮药膳鸡-全周-午晚高峰-30</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -11043,143 +11454,152 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
+          <t>897042860272709632</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>竹山路地铁1号口</t>
+          <t>高新-商圈-中粮悦天地西北门B-全周-午晚高峰-50</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
+          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>高新-写字楼-海丰小视科技中心-工作日-晚高峰-12</t>
+          <t>竹山路地铁1号口</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>0a8320ecl1lvbzz3tyzcnk28dt6w9vz4</t>
+          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>逸夫医院门口左手</t>
+          <t>高新-写字楼-海丰小视科技中心-工作日-晚高峰-12</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -11191,42 +11611,45 @@
         <v>11</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>0a83975dl1lsfxyiczcx2rt37eb2pmpx</t>
+          <t>0a8320ecl1lvbzz3tyzcnk28dt6w9vz4</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>高新-商圈-中粮好想来-全周-午晚高峰-30</t>
+          <t>逸夫医院门口左手</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -11238,136 +11661,145 @@
         <v>11</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>889855305298198528</t>
+          <t>0a83975dl1lsfxyiczcx2rt37eb2pmpx</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>科建路16号武夷绿洲站点3</t>
+          <t>高新-商圈-中粮好想来-全周-午晚高峰-30</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1l2ef8wtmsfysajshhixta6</t>
+          <t>889855305298198528</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>鹏山路9号1幢金邻生活广场站点C</t>
+          <t>科建路16号武夷绿洲站点3</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>0a83e9a8l1l5gi7n8g39kdamy6h6xzfc</t>
+          <t>0a83a414l1l2ef8wtmsfysajshhixta6</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路城市之光大厦站点</t>
+          <t>鹏山路9号1幢金邻生活广场站点C</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -11379,37 +11811,40 @@
         <v>11</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>889833971314581504</t>
+          <t>0a83e9a8l1l5gi7n8g39kdamy6h6xzfc</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>江宁区天景山锦绣苑</t>
+          <t>天元东路辅路城市之光大厦站点</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -11419,49 +11854,52 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
+          <t>889833971314581504</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>鹏山路东方·龙湖湾站点Z2</t>
+          <t>江宁区天景山锦绣苑</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -11473,42 +11911,45 @@
         <v>11</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>889836462803582976</t>
+          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点A</t>
+          <t>鹏山路东方·龙湖湾站点Z2</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -11520,37 +11961,40 @@
         <v>11</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>0a833b7al1ln8b77uvihj3abdufjp6w4</t>
+          <t>889836462803582976</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道保利·樾广场站点O</t>
+          <t>天元东路辅路南京义乌小商品城站点A</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -11560,44 +12004,47 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a89810cl1lrxjz8hhcesusmyvs7jmw6</t>
+          <t>0a833b7al1ln8b77uvihj3abdufjp6w4</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>湖山路429号天景山公寓站点A</t>
+          <t>龙眠大道保利·樾广场站点O</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -11607,91 +12054,97 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>889466722646794240</t>
+          <t>0a89810cl1lrxjz8hhcesusmyvs7jmw6</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>胜太东路江宁供销商厦站点</t>
+          <t>湖山路429号天景山公寓站点A</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
+          <t>889466722646794240</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>土山路东域城站点A</t>
+          <t>胜太东路江宁供销商厦站点</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -11708,26 +12161,29 @@
         <v>11</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="44">
@@ -11755,26 +12211,29 @@
         <v>11</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="45">
@@ -11802,26 +12261,29 @@
         <v>11</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="46">
@@ -11849,26 +12311,29 @@
         <v>12</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="47">
@@ -11896,26 +12361,29 @@
         <v>11</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="48">
@@ -11943,26 +12411,29 @@
         <v>11</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -13629,22 +14100,22 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -13658,22 +14129,22 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -13687,22 +14158,22 @@
         <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -13716,22 +14187,22 @@
         <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -13745,22 +14216,22 @@
         <v>15</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
@@ -13774,22 +14245,22 @@
         <v>10</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -13803,22 +14274,22 @@
         <v>10</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -13832,22 +14303,22 @@
         <v>14</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -13861,22 +14332,22 @@
         <v>14</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>92.9%</t>
         </is>
       </c>
     </row>
@@ -13890,22 +14361,22 @@
         <v>8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -14343,22 +14814,22 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -14372,22 +14843,22 @@
         <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -14401,22 +14872,22 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -14430,22 +14901,22 @@
         <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -14459,22 +14930,22 @@
         <v>10</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -14488,22 +14959,22 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -553,12 +553,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>79.8%</t>
         </is>
       </c>
     </row>
@@ -603,12 +603,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>97.8%</t>
         </is>
       </c>
     </row>
@@ -641,14 +641,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20260801 ~ 20260804</t>
+          <t>数据范围: 20260801 ~ 20260805</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 2天, 周末: 2天</t>
+          <t>工作日: 3天, 周末: 2天</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M109"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -700,6 +700,7 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,6 +776,11 @@
           <t>08-04(二)</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>08-05(三)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -801,20 +807,20 @@
         <v>25</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -828,6 +834,9 @@
       <c r="M3" s="8" t="n">
         <v>15</v>
       </c>
+      <c r="N3" s="8" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -854,20 +863,20 @@
         <v>25</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -881,6 +890,9 @@
       <c r="M4" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="N4" s="8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -907,20 +919,20 @@
         <v>25</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -934,6 +946,9 @@
       <c r="M5" s="8" t="n">
         <v>16</v>
       </c>
+      <c r="N5" s="8" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -960,25 +975,25 @@
         <v>15</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -987,21 +1002,24 @@
       <c r="M6" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="N6" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0a83e334l1l38kski9q2syd6gczb42g8</t>
+          <t>1174621727109263360</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>云密路汇智城(建设中)投放点</t>
+          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1010,157 +1028,166 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>15</v>
+        <v>40</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>0a83eb4fl1lz4hvkvkpdqc8mwis9httv</t>
+          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>仙林中心(地铁站)投放点A</t>
+          <t>中和路阿里中心·南京投放点A</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="M8" s="7" t="n">
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>1174621727109263360</t>
+          <t>597639530744799232</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
+          <t>南京市建邺区沙洲街道中胜地铁站5号口明基医院</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>40</v>
+        <v>25</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
+          <t>1206467184454987776</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
+          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1169,81 +1196,84 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>12</v>
+        <v>42</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
+          <t>0a83e334l1l38kski9q2syd6gczb42g8</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>中和路阿里中心·南京投放点A</t>
+          <t>云密路汇智城(建设中)投放点</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L11" s="7" t="n">
@@ -1252,122 +1282,131 @@
       <c r="M11" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="N11" s="9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1leh9rgc924wv39dv6m7mvs</t>
+          <t>0a83eb4fl1lz4hvkvkpdqc8mwis9httv</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>梦都大街东地铁站4B口江苏中烟工业有限责任公司南京卷烟投放点A</t>
+          <t>仙林中心(地铁站)投放点A</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="n">
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="M12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="9" t="n">
-        <v>25</v>
+      <c r="N12" s="9" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>1077190082872029184</t>
+          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道嘉陵江东街地铁站</t>
+          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>24</v>
+        <v>12</v>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1076695373435187200</t>
+          <t>0a836146l1leh9rgc924wv39dv6m7mvs</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区吴侯街地铁站</t>
+          <t>梦都大街东地铁站4B口江苏中烟工业有限责任公司南京卷烟投放点A</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1377,50 +1416,53 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="M14" s="7" t="n">
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>597639530744799232</t>
+          <t>1077190082872029184</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道中胜地铁站5号口明基医院</t>
+          <t>南京市建邺区沙洲街道嘉陵江东街地铁站</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1437,154 +1479,163 @@
         <v>15</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1206467184454987776</t>
+          <t>1174597131085402112</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
+          <t>25-早峰-地铁站-云南路地铁站渗透</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="n">
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="N16" s="7" t="n">
         <v>0</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>0a83b42bl1lurmqhqrwviu2qvdiirgcs</t>
+          <t>1076695373435187200</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>安德门大街楚翘城投放点G</t>
+          <t>南京市建邺区吴侯街地铁站</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="M17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>14</v>
+      <c r="N17" s="9" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>0a838c9fl1l6eu5z5992t8pxsi4euarb</t>
+          <t>1153706290333523968</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>凤信路云密城投放点A</t>
+          <t>鼓楼区集庆门大街268号</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1596,48 +1647,51 @@
         <v>15</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="N18" s="7" t="n">
         <v>0</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1174535930061524992</t>
+          <t>0a83b42bl1lurmqhqrwviu2qvdiirgcs</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
+          <t>安德门大街楚翘城投放点G</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1646,19 +1700,19 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1671,26 +1725,29 @@
         </is>
       </c>
       <c r="L19" s="8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>854196782092722176</t>
+          <t>0a838c9fl1l6eu5z5992t8pxsi4euarb</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-居民区-好的渗透</t>
+          <t>凤信路云密城投放点A</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1699,19 +1756,19 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1724,47 +1781,50 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lduskfcd7fg98zc4m8acq2</t>
+          <t>1174535930061524992</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>望江路正荣润锦城投放点C</t>
+          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1777,47 +1837,50 @@
         </is>
       </c>
       <c r="L21" s="8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M21" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="N21" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1153706370345959424</t>
+          <t>854196782092722176</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>新浦路长江时代·雍澜悦府投放点渗透</t>
+          <t>工作日-全天-居民区-好的渗透</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1830,47 +1893,50 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a83612el1lx8dxfbxif2vsjehjqtwrj</t>
+          <t>0a836587l1lduskfcd7fg98zc4m8acq2</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>江山路投放点H</t>
+          <t>望江路正荣润锦城投放点C</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1879,51 +1945,54 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L23" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>96</v>
+        <v>17</v>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>732956005347999744</t>
+          <t>0a83384dl1lbqqk7xa7gxkbhz9gpmyzs</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城十街区</t>
+          <t>西春路48号云密城投放点</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1932,51 +2001,54 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L24" s="8" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>54</v>
+        <v>15</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>732955785461030912</t>
+          <t>754365148238000128</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城5街区</t>
+          <t>玄武区四牌楼63号</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1985,51 +2057,54 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>53</v>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a83384dl1lbqqk7xa7gxkbhz9gpmyzs</t>
+          <t>0a83eb4fl1lyh6gadse7cuxyngppbre5</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>西春路48号云密城投放点</t>
+          <t>中胜地铁站2C口投放点</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2038,51 +2113,54 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L26" s="8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="N26" s="8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>1176842717252255744</t>
+          <t>754151861948555264</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>三元巷6号三元公寓投放点渗透</t>
+          <t>23早高峰-全天-居民区-金浦御龙湾F区</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2091,51 +2169,54 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
+          <t>853114235179171840</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>淮海路远洋国际中心投放点A</t>
+          <t>全天-居民区-和燕花苑</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2144,51 +2225,54 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>19</v>
+        <v>10</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>754365148238000128</t>
+          <t>1153706370345959424</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>玄武区四牌楼63号</t>
+          <t>新浦路长江时代·雍澜悦府投放点渗透</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2197,30 +2281,33 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="n">
-        <v>37</v>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>22</v>
+        <v>13</v>
+      </c>
+      <c r="N29" s="9" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
+          <t>0a83612el1lx8dxfbxif2vsjehjqtwrj</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
+          <t>江山路投放点H</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -2229,19 +2316,19 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>38</v>
+        <v>240</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2250,51 +2337,54 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>8</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>96</v>
+      </c>
+      <c r="N30" s="9" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>0a83eb4fl1lyh6gadse7cuxyngppbre5</t>
+          <t>732956005347999744</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>中胜地铁站2C口投放点</t>
+          <t>25-早峰-居民区-天润城十街区</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2303,51 +2393,54 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L31" s="8" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>29</v>
+        <v>54</v>
+      </c>
+      <c r="N31" s="9" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>724131086902996992</t>
+          <t>732955785461030912</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>迈皋桥公交场站渗透</t>
+          <t>25-早峰-居民区-天润城5街区</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2356,51 +2449,54 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L32" s="8" t="n">
         <v>19</v>
       </c>
       <c r="M32" s="9" t="n">
-        <v>80</v>
+        <v>53</v>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>754151861948555264</t>
+          <t>1098070146307002368</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>23早高峰-全天-居民区-金浦御龙湾F区</t>
+          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2409,51 +2505,54 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>19</v>
+        <v>94</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>853114235179171840</t>
+          <t>1176842717252255744</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>全天-居民区-和燕花苑</t>
+          <t>三元巷6号三元公寓投放点渗透</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2462,51 +2561,54 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lfmy2n3ksr3ftxi64ycwsh</t>
+          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>钟阜路建宁路55号院投放点</t>
+          <t>淮海路远洋国际中心投放点A</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2515,51 +2617,54 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>64</v>
-      </c>
-      <c r="M35" s="9" t="n">
-        <v>39</v>
+        <v>20</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
+          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>九家圩路世茂外滩新城投放点A</t>
+          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2568,51 +2673,54 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="N36" s="9" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>1178909948933013504</t>
+          <t>f25bafa6cea44ac49303d053fcda9045</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-商圈-香格里拉渗透</t>
+          <t>南京市建邺区沙洲街道中胜地铁站2A口</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2621,51 +2729,54 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>41</v>
+        <v>25</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>0a8331f1l1lfxks8nftfew7gr7y37gvu</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>西城路建邺科技创新产业园投放点A</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>490</v>
+        <v>38</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2674,51 +2785,54 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>151</v>
+        <v>15</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>339</v>
+        <v>15</v>
+      </c>
+      <c r="N38" s="8" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>e5189cd954054116aa19db28790cc606</t>
+          <t>724131086902996992</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-高新地铁站-30</t>
+          <t>迈皋桥公交场站渗透</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -2727,51 +2841,54 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L39" s="9" t="n">
-        <v>78</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>152</v>
+        <v>80</v>
+      </c>
+      <c r="N39" s="9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>554207268778184704</t>
+          <t>1110455282713198592</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路3号口</t>
+          <t>25-全天-地铁站-万汇城-渗透</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>305</v>
+        <v>45</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2780,51 +2897,54 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>143</v>
+        <v>17</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>594063e60b264e419feea65370752c3f</t>
+          <t>0a836587l1lfmy2n3ksr3ftxi64ycwsh</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
+          <t>钟阜路建宁路55号院投放点</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>247</v>
+        <v>146</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2837,47 +2957,50 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>139</v>
+        <v>39</v>
+      </c>
+      <c r="N41" s="9" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>九家圩路世茂外滩新城投放点A</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>409</v>
+        <v>108</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2890,26 +3013,29 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>213</v>
+        <v>46</v>
       </c>
       <c r="M42" s="9" t="n">
-        <v>196</v>
+        <v>47</v>
+      </c>
+      <c r="N42" s="9" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>1178909948933013504</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>25-早峰-商圈-香格里拉渗透</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -2918,19 +3044,19 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>373</v>
+        <v>129</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2943,21 +3069,24 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>161</v>
+        <v>32</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>212</v>
+        <v>41</v>
+      </c>
+      <c r="N43" s="9" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1l77t6e64cbw8rqk9kqakwh</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>江山路明发滨江新城三期投放点A</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2967,23 +3096,23 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>178</v>
+        <v>800</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2996,21 +3125,24 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="M44" s="9" t="n">
-        <v>103</v>
+        <v>339</v>
+      </c>
+      <c r="N44" s="9" t="n">
+        <v>310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>732955501476995072</t>
+          <t>e5189cd954054116aa19db28790cc606</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-威尼斯三街区</t>
+          <t>25-晚峰-地铁站-高新地铁站-30</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3020,23 +3152,23 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>220</v>
+        <v>371</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3049,21 +3181,24 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>120</v>
+        <v>152</v>
+      </c>
+      <c r="N45" s="9" t="n">
+        <v>141</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>626976116946362368</t>
+          <t>554207268778184704</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-润泰花园东30</t>
+          <t>25-晚峰-地铁站-柳州东路3号口</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3073,23 +3208,23 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
         <v>30</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>122</v>
+        <v>453</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3102,21 +3237,24 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>44</v>
+        <v>162</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>78</v>
+        <v>143</v>
+      </c>
+      <c r="N46" s="9" t="n">
+        <v>148</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>777073646895747072</t>
+          <t>594063e60b264e419feea65370752c3f</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>25-全天-商场-1914街区</t>
+          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3126,23 +3264,23 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>100</v>
+        <v>424</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3155,21 +3293,24 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>50</v>
+        <v>139</v>
+      </c>
+      <c r="N47" s="9" t="n">
+        <v>177</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>732955983377653760</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城1-4街区</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3179,23 +3320,23 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>164</v>
+        <v>668</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3208,21 +3349,24 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="M48" s="9" t="n">
-        <v>83</v>
+        <v>196</v>
+      </c>
+      <c r="N48" s="9" t="n">
+        <v>259</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>732955258519240704</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路1号口</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3236,19 +3380,19 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>370</v>
+        <v>551</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3261,26 +3405,29 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>250</v>
+        <v>212</v>
+      </c>
+      <c r="N49" s="9" t="n">
+        <v>178</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>0a838c9fl1l9eahd7x3xm2ecvtjwbbdv</t>
+          <t>0a836146l1l77t6e64cbw8rqk9kqakwh</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>沙县小吃(南京第099店)凤翔新城投放点</t>
+          <t>江山路明发滨江新城三期投放点A</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -3289,19 +3436,19 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3314,47 +3461,50 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="M50" s="9" t="n">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="N50" s="9" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>0a835aeel1lazxwqtfa664yxtxendmyu</t>
+          <t>732955501476995072</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>汇智路南海生物科技园投放点</t>
+          <t>25-早峰-居民区-威尼斯三街区</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3367,47 +3517,50 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>15</v>
+        <v>120</v>
+      </c>
+      <c r="N51" s="9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>0a8398f6l1lw2mup86pcczvtx5uv56gv</t>
+          <t>626976116946362368</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>宁双路软件谷垠坤·南京大数据产业基地投放点</t>
+          <t>25-早峰-居民区-润泰花园东30</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>63</v>
+        <v>198</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3420,100 +3573,106 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="M52" s="9" t="n">
-        <v>38</v>
+        <v>78</v>
+      </c>
+      <c r="N52" s="9" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>584636981105418240</t>
+          <t>777073646895747072</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-羊山公园2号口</t>
+          <t>25-全天-商场-1914街区</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>261</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L53" s="9" t="n">
-        <v>112</v>
-      </c>
       <c r="M53" s="9" t="n">
-        <v>149</v>
+        <v>50</v>
+      </c>
+      <c r="N53" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
+          <t>732955983377653760</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁口-仙林中心站1号口</t>
+          <t>25-早峰-居民区-天润城1-4街区</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>455</v>
+        <v>236</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -3526,47 +3685,50 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="M54" s="9" t="n">
-        <v>224</v>
+        <v>83</v>
+      </c>
+      <c r="N54" s="9" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>684268350256898048</t>
+          <t>732955258519240704</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-学则路</t>
+          <t>25-晚峰-地铁站-柳州东路1号口</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>90</v>
+        <v>575</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -3579,47 +3741,50 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>65</v>
+        <v>250</v>
+      </c>
+      <c r="N55" s="9" t="n">
+        <v>205</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>1098070146307002368</t>
+          <t>0a838c9fl1l9eahd7x3xm2ecvtjwbbdv</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
+          <t>沙县小吃(南京第099店)凤翔新城投放点</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>158</v>
+        <v>324</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -3632,26 +3797,29 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>64</v>
+        <v>98</v>
+      </c>
+      <c r="N56" s="9" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>1023193174134530048</t>
+          <t>0a835aeel1lazxwqtfa664yxtxendmyu</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>仙林大道投放点N</t>
+          <t>汇智路南海生物科技园投放点</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -3660,51 +3828,54 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L57" s="9" t="n">
-        <v>49</v>
-      </c>
       <c r="M57" s="9" t="n">
-        <v>50</v>
+        <v>15</v>
+      </c>
+      <c r="N57" s="9" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>998560699433394176</t>
+          <t>0a8398f6l1lw2mup86pcczvtx5uv56gv</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>广志路南京万达茂投放点D</t>
+          <t>宁双路软件谷垠坤·南京大数据产业基地投放点</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -3713,19 +3884,19 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -3741,18 +3912,21 @@
         <v>25</v>
       </c>
       <c r="M58" s="9" t="n">
-        <v>64</v>
+        <v>38</v>
+      </c>
+      <c r="N58" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>778851422965239808</t>
+          <t>584636981105418240</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-仙林新村</t>
+          <t>25-全天-地铁-羊山公园2号口</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3762,23 +3936,23 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>75</v>
+        <v>383</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -3791,21 +3965,24 @@
         </is>
       </c>
       <c r="L59" s="9" t="n">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>50</v>
+        <v>149</v>
+      </c>
+      <c r="N59" s="9" t="n">
+        <v>122</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>25-全天-地铁口-仙林中心站1号口</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3815,23 +3992,23 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>100</v>
+        <v>717</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -3844,21 +4021,24 @@
         </is>
       </c>
       <c r="L60" s="9" t="n">
-        <v>50</v>
+        <v>231</v>
       </c>
       <c r="M60" s="9" t="n">
-        <v>50</v>
+        <v>224</v>
+      </c>
+      <c r="N60" s="9" t="n">
+        <v>262</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>1123869911569338368</t>
+          <t>684268350256898048</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>学衡路南京师范大学仙林校区投放点B</t>
+          <t>25-全天-地铁-学则路</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3868,76 +4048,79 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="F61" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L61" s="9" t="n">
-        <v>125</v>
-      </c>
       <c r="M61" s="9" t="n">
-        <v>125</v>
+        <v>65</v>
+      </c>
+      <c r="N61" s="9" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
+          <t>1023193174134530048</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>中山东路228号新世纪广场A幢投放点</t>
+          <t>仙林大道投放点N</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>298</v>
+        <v>183</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -3950,47 +4133,50 @@
         </is>
       </c>
       <c r="L62" s="9" t="n">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="M62" s="9" t="n">
-        <v>124</v>
+        <v>50</v>
+      </c>
+      <c r="N62" s="9" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>1153706291117858816</t>
+          <t>998560699433394176</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
+          <t>广志路南京万达茂投放点D</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>314</v>
+        <v>162</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4003,47 +4189,50 @@
         </is>
       </c>
       <c r="L63" s="9" t="n">
-        <v>144</v>
+        <v>25</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>170</v>
+        <v>64</v>
+      </c>
+      <c r="N63" s="9" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
+          <t>778851422965239808</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
+          <t>25-早峰-居民区-仙林新村</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>259</v>
+        <v>125</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4056,47 +4245,50 @@
         </is>
       </c>
       <c r="L64" s="9" t="n">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="M64" s="9" t="n">
-        <v>140</v>
+        <v>50</v>
+      </c>
+      <c r="N64" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>1174622373773963264</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道常府街地铁站</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>409</v>
+        <v>150</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4109,47 +4301,50 @@
         </is>
       </c>
       <c r="L65" s="9" t="n">
-        <v>318</v>
+        <v>50</v>
       </c>
       <c r="M65" s="9" t="n">
-        <v>91</v>
+        <v>50</v>
+      </c>
+      <c r="N65" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>1174627346911133696</t>
+          <t>1123869911569338368</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道户部街长发银座</t>
+          <t>学衡路南京师范大学仙林校区投放点B</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>80</v>
+        <v>375</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4162,21 +4357,24 @@
         </is>
       </c>
       <c r="L66" s="9" t="n">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="M66" s="9" t="n">
-        <v>40</v>
+        <v>125</v>
+      </c>
+      <c r="N66" s="9" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
+          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>石门坎地铁站3号口光华科技产业园投放点</t>
+          <t>中山东路228号新世纪广场A幢投放点</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -4190,19 +4388,19 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>159</v>
+        <v>489</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -4215,21 +4413,24 @@
         </is>
       </c>
       <c r="L67" s="9" t="n">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="M67" s="9" t="n">
-        <v>80</v>
+        <v>124</v>
+      </c>
+      <c r="N67" s="9" t="n">
+        <v>191</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>5331e3a58a50481dbc8e7273561f4e25</t>
+          <t>1153706291117858816</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-地铁站-夫子庙2号口-10</t>
+          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -4239,23 +4440,23 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>50</v>
+        <v>385</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -4268,21 +4469,24 @@
         </is>
       </c>
       <c r="L68" s="9" t="n">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="M68" s="9" t="n">
-        <v>25</v>
+        <v>170</v>
+      </c>
+      <c r="N68" s="9" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>874549501386596352</t>
+          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
+          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -4292,23 +4496,23 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>174</v>
+        <v>340</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -4321,21 +4525,24 @@
         </is>
       </c>
       <c r="L69" s="9" t="n">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="M69" s="9" t="n">
-        <v>89</v>
+        <v>140</v>
+      </c>
+      <c r="N69" s="9" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>f72b5a964e164de7930e4077acb795b0</t>
+          <t>1174622373773963264</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道中华路宜必思酒店(南京夫子庙店)</t>
+          <t>南京市秦淮区洪武路街道常府街地铁站</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -4345,23 +4552,23 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>70</v>
+        <v>574</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -4374,21 +4581,24 @@
         </is>
       </c>
       <c r="L70" s="9" t="n">
-        <v>50</v>
+        <v>318</v>
       </c>
       <c r="M70" s="9" t="n">
-        <v>20</v>
+        <v>91</v>
+      </c>
+      <c r="N70" s="9" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lhbuznwmz926qn65svufex</t>
+          <t>1174627346911133696</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>中山南路280号张府园小区投放点A</t>
+          <t>南京市秦淮区洪武路街道户部街长发银座</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4405,16 +4615,16 @@
         <v>20</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -4427,21 +4637,24 @@
         </is>
       </c>
       <c r="L71" s="9" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M71" s="9" t="n">
-        <v>25</v>
+        <v>40</v>
+      </c>
+      <c r="N71" s="9" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>732951617602912256</t>
+          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
+          <t>石门坎地铁站3号口光华科技产业园投放点</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -4451,23 +4664,23 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>286</v>
+        <v>220</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -4480,47 +4693,50 @@
         </is>
       </c>
       <c r="L72" s="9" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="M72" s="9" t="n">
-        <v>198</v>
+        <v>80</v>
+      </c>
+      <c r="N72" s="9" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>732956028185985024</t>
+          <t>5331e3a58a50481dbc8e7273561f4e25</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>下马坊地铁站</t>
+          <t>工作日-全天-地铁站-夫子庙2号口-10</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -4533,47 +4749,50 @@
         </is>
       </c>
       <c r="L73" s="9" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M73" s="9" t="n">
-        <v>50</v>
+        <v>25</v>
+      </c>
+      <c r="N73" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>854249531796738048</t>
+          <t>874549501386596352</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-金马路地铁站</t>
+          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
         <v>40</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>168</v>
+        <v>250</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -4586,47 +4805,50 @@
         </is>
       </c>
       <c r="L74" s="9" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="M74" s="9" t="n">
-        <v>122</v>
+        <v>89</v>
+      </c>
+      <c r="N74" s="9" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>816505037427507200</t>
+          <t>f72b5a964e164de7930e4077acb795b0</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>玄武区童卫路28-2号</t>
+          <t>南京市秦淮区洪武路街道中华路宜必思酒店(南京夫子庙店)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>239</v>
+        <v>116</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -4639,26 +4861,29 @@
         </is>
       </c>
       <c r="L75" s="9" t="n">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="M75" s="9" t="n">
-        <v>153</v>
+        <v>20</v>
+      </c>
+      <c r="N75" s="9" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lbvs3sx44tiwdb7kvc7kap</t>
+          <t>0a83a497l1lhbuznwmz926qn65svufex</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>苏园路江苏软件园二期投放点A</t>
+          <t>中山南路280号张府园小区投放点A</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -4670,16 +4895,16 @@
         <v>20</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -4692,47 +4917,50 @@
         </is>
       </c>
       <c r="L76" s="9" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="M76" s="9" t="n">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="N76" s="9" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>857508296047517696</t>
+          <t>732951617602912256</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2b</t>
+          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>105</v>
+        <v>518</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -4745,21 +4973,24 @@
         </is>
       </c>
       <c r="L77" s="9" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="M77" s="9" t="n">
-        <v>68</v>
+        <v>198</v>
+      </c>
+      <c r="N77" s="9" t="n">
+        <v>232</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>0a838699l1lzri8zeup3f4zan2nxpmck</t>
+          <t>732956028185985024</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>童卫路南理工科技创新园投放点</t>
+          <t>下马坊地铁站</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -4769,23 +5000,23 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -4798,21 +5029,24 @@
         </is>
       </c>
       <c r="L78" s="9" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="M78" s="9" t="n">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="N78" s="9" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>788321551519383552</t>
+          <t>854249531796738048</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>玄武区鹤鸣路37号</t>
+          <t>25-全天-地铁站-金马路地铁站</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -4822,23 +5056,23 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>50</v>
+        <v>258</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -4851,21 +5085,24 @@
         </is>
       </c>
       <c r="L79" s="9" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="M79" s="9" t="n">
-        <v>25</v>
+        <v>122</v>
+      </c>
+      <c r="N79" s="9" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
+          <t>816505037427507200</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2A</t>
+          <t>玄武区童卫路28-2号</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -4879,19 +5116,19 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>60</v>
+        <v>337</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -4904,21 +5141,24 @@
         </is>
       </c>
       <c r="L80" s="9" t="n">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="M80" s="9" t="n">
-        <v>35</v>
+        <v>153</v>
+      </c>
+      <c r="N80" s="9" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>0a833ecdl1lcqyspwc7ejjhwh8vz5pfp</t>
+          <t>0a836587l1lbvs3sx44tiwdb7kvc7kap</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>石狮路辅路INS Mall·浪里投放点B</t>
+          <t>苏园路江苏软件园二期投放点A</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -4928,23 +5168,23 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -4957,26 +5197,29 @@
         </is>
       </c>
       <c r="L81" s="9" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="M81" s="9" t="n">
-        <v>43</v>
+        <v>22</v>
+      </c>
+      <c r="N81" s="9" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>948393128847777792</t>
+          <t>857508296047517696</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>30-工作日-全天-地铁-明故宫2渗透</t>
+          <t>钟灵街2b</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -4985,19 +5228,19 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>272</v>
+        <v>169</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -5010,47 +5253,50 @@
         </is>
       </c>
       <c r="L82" s="9" t="n">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="M82" s="9" t="n">
-        <v>126</v>
+        <v>68</v>
+      </c>
+      <c r="N82" s="9" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
+          <t>0a838699l1lzri8zeup3f4zan2nxpmck</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>大行宫6号口渗透</t>
+          <t>童卫路南理工科技创新园投放点</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>252</v>
+        <v>190</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5063,26 +5309,29 @@
         </is>
       </c>
       <c r="L83" s="9" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="M83" s="9" t="n">
-        <v>132</v>
+        <v>60</v>
+      </c>
+      <c r="N83" s="9" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>816513511474413568</t>
+          <t>788321551519383552</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>熊猫</t>
+          <t>玄武区鹤鸣路37号</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -5094,16 +5343,16 @@
         <v>20</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>244</v>
+        <v>90</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -5116,47 +5365,50 @@
         </is>
       </c>
       <c r="L84" s="9" t="n">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="M84" s="9" t="n">
-        <v>115</v>
+        <v>25</v>
+      </c>
+      <c r="N84" s="9" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>钟灵街2A</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>315</v>
+        <v>96</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -5169,47 +5421,50 @@
         </is>
       </c>
       <c r="L85" s="9" t="n">
-        <v>167</v>
+        <v>25</v>
       </c>
       <c r="M85" s="9" t="n">
-        <v>148</v>
+        <v>35</v>
+      </c>
+      <c r="N85" s="9" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>1176722757207629824</t>
+          <t>0a833ecdl1lcqyspwc7ejjhwh8vz5pfp</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>规划建设展览馆渗透</t>
+          <t>石狮路辅路INS Mall·浪里投放点B</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -5222,21 +5477,24 @@
         </is>
       </c>
       <c r="L86" s="9" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="M86" s="9" t="n">
-        <v>100</v>
+        <v>43</v>
+      </c>
+      <c r="N86" s="9" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>732955102642126848</t>
+          <t>948393128847777792</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>玄武区丹凤街69号</t>
+          <t>30-工作日-全天-地铁-明故宫2渗透</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -5250,19 +5508,19 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>46</v>
+        <v>404</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -5275,21 +5533,24 @@
         </is>
       </c>
       <c r="L87" s="9" t="n">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="M87" s="9" t="n">
-        <v>20</v>
+        <v>126</v>
+      </c>
+      <c r="N87" s="9" t="n">
+        <v>132</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>732954989023625216</t>
+          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-地铁站-鸡鸣寺地铁站渗透</t>
+          <t>大行宫6号口渗透</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -5299,23 +5560,23 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>363</v>
+        <v>435</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -5328,47 +5589,50 @@
         </is>
       </c>
       <c r="L88" s="9" t="n">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="M88" s="9" t="n">
-        <v>187</v>
+        <v>132</v>
+      </c>
+      <c r="N88" s="9" t="n">
+        <v>183</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
+          <t>816513511474413568</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>集贤路鼓楼创新广场投放点B</t>
+          <t>熊猫</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>30</v>
+        <v>358</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -5381,47 +5645,50 @@
         </is>
       </c>
       <c r="L89" s="9" t="n">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="M89" s="9" t="n">
-        <v>15</v>
+        <v>115</v>
+      </c>
+      <c r="N89" s="9" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>1206516292750213120</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>中山北路宏图大厦渗透</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>32</v>
+        <v>484</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -5434,47 +5701,50 @@
         </is>
       </c>
       <c r="L90" s="9" t="n">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="M90" s="9" t="n">
-        <v>17</v>
+        <v>148</v>
+      </c>
+      <c r="N90" s="9" t="n">
+        <v>169</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
+          <t>1176722757207629824</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>鼓楼区童家山2-3号楼</t>
+          <t>规划建设展览馆渗透</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>66</v>
+        <v>224</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -5487,47 +5757,50 @@
         </is>
       </c>
       <c r="L91" s="9" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="M91" s="9" t="n">
-        <v>30</v>
+        <v>100</v>
+      </c>
+      <c r="N91" s="9" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>f25bafa6cea44ac49303d053fcda9045</t>
+          <t>732955102642126848</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道中胜地铁站2A口</t>
+          <t>玄武区丹凤街69号</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -5540,47 +5813,50 @@
         </is>
       </c>
       <c r="L92" s="9" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M92" s="9" t="n">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="N92" s="9" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>d0f80f128e074902a9109772ebc0edc6</t>
+          <t>732954989023625216</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道中胜地铁站1A</t>
+          <t>工作日-全天-地铁站-鸡鸣寺地铁站渗透</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>49</v>
+        <v>393</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -5593,21 +5869,24 @@
         </is>
       </c>
       <c r="L93" s="9" t="n">
-        <v>24</v>
+        <v>176</v>
       </c>
       <c r="M93" s="9" t="n">
-        <v>25</v>
+        <v>187</v>
+      </c>
+      <c r="N93" s="9" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>1174597131085402112</t>
+          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-地铁站-云南路地铁站渗透</t>
+          <t>集贤路鼓楼创新广场投放点B</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5617,23 +5896,23 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -5646,21 +5925,24 @@
         </is>
       </c>
       <c r="L94" s="9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M94" s="9" t="n">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="N94" s="9" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>0a8331f1l1lfxks8nftfew7gr7y37gvu</t>
+          <t>1206516292750213120</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>西城路建邺科技创新产业园投放点A</t>
+          <t>中山北路宏图大厦渗透</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5670,23 +5952,23 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -5702,18 +5984,21 @@
         <v>15</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="N95" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>1153706290333523968</t>
+          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>鼓楼区集庆门大街268号</t>
+          <t>鼓楼区童家山2-3号楼</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -5723,23 +6008,23 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -5752,47 +6037,50 @@
         </is>
       </c>
       <c r="L96" s="9" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M96" s="9" t="n">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="N96" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>554207268614606848</t>
+          <t>d0f80f128e074902a9109772ebc0edc6</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
+          <t>南京市建邺区沙洲街道中胜地铁站1A</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>353</v>
+        <v>74</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -5805,21 +6093,24 @@
         </is>
       </c>
       <c r="L97" s="9" t="n">
-        <v>193</v>
+        <v>24</v>
       </c>
       <c r="M97" s="9" t="n">
-        <v>160</v>
+        <v>25</v>
+      </c>
+      <c r="N97" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>1177090611149664256</t>
+          <t>554207268614606848</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>柚米社区</t>
+          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -5829,23 +6120,23 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>113</v>
+        <v>630</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -5858,21 +6149,24 @@
         </is>
       </c>
       <c r="L98" s="9" t="n">
-        <v>48</v>
+        <v>193</v>
       </c>
       <c r="M98" s="9" t="n">
-        <v>65</v>
+        <v>160</v>
+      </c>
+      <c r="N98" s="9" t="n">
+        <v>277</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>723758596467601408</t>
+          <t>1177090611149664256</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>全天-居民区-颐和府邸投放点A</t>
+          <t>柚米社区</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -5889,16 +6183,16 @@
         <v>20</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -5911,21 +6205,24 @@
         </is>
       </c>
       <c r="L99" s="9" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="M99" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="N99" s="9" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>1008726508792258560</t>
+          <t>723758596467601408</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-南砖新村</t>
+          <t>全天-居民区-颐和府邸投放点A</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -5939,19 +6236,19 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -5969,16 +6266,19 @@
       <c r="M100" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="N100" s="9" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>857062808558088192</t>
+          <t>1008726508792258560</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>23早高峰-全天-居民区-金浦御龙湾D区</t>
+          <t>25-早峰-居民区-南砖新村</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5995,16 +6295,16 @@
         <v>25</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -6017,21 +6317,24 @@
         </is>
       </c>
       <c r="L101" s="9" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="M101" s="9" t="n">
-        <v>76</v>
+        <v>25</v>
+      </c>
+      <c r="N101" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>690088208255492096</t>
+          <t>857062808558088192</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>迈化路长营村15号小区投放点</t>
+          <t>23早高峰-全天-居民区-金浦御龙湾D区</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -6045,19 +6348,19 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>93</v>
+        <v>178</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -6070,21 +6373,24 @@
         </is>
       </c>
       <c r="L102" s="9" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M102" s="9" t="n">
-        <v>50</v>
+        <v>76</v>
+      </c>
+      <c r="N102" s="9" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>892408647821217792</t>
+          <t>690088208255492096</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-融创玉兰公馆</t>
+          <t>迈化路长营村15号小区投放点</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -6098,46 +6404,49 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I103" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L103" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="M103" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L103" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="M103" s="9" t="n">
-        <v>25</v>
+      <c r="N103" s="9" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>1084472481506824192</t>
+          <t>892408647821217792</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>栖霞区宜春街40号</t>
+          <t>25-早峰-居民区-融创玉兰公馆</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -6147,23 +6456,23 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -6176,21 +6485,24 @@
         </is>
       </c>
       <c r="L104" s="9" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="M104" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="N104" s="9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>836164410974330880</t>
+          <t>1084472481506824192</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>全天-居民区-愉景湾北门</t>
+          <t>栖霞区宜春街40号</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -6200,23 +6512,23 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -6229,21 +6541,24 @@
         </is>
       </c>
       <c r="L105" s="9" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="M105" s="9" t="n">
-        <v>45</v>
+        <v>25</v>
+      </c>
+      <c r="N105" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>854565226235502592</t>
+          <t>836164410974330880</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>北苑西路枫桥雅筑投放点渗透</t>
+          <t>全天-居民区-愉景湾北门</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -6257,46 +6572,49 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L106" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="M106" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="N106" s="9" t="n">
         <v>25</v>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L106" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="M106" s="9" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>754151029387345920</t>
+          <t>854565226235502592</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>工作日-早峰-居民区-颐和家园</t>
+          <t>北苑西路枫桥雅筑投放点渗透</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -6310,19 +6628,19 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -6338,44 +6656,47 @@
         <v>25</v>
       </c>
       <c r="M107" s="9" t="n">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="N107" s="9" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>0a8393e2l1lq483xeda38ekbcqzbyd8h</t>
+          <t>754151029387345920</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>凤滁路高芯科谷-中科创新广场投放点F</t>
+          <t>工作日-早峰-居民区-颐和家园</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -6388,21 +6709,24 @@
         </is>
       </c>
       <c r="L108" s="9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M108" s="9" t="n">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="N108" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>1110455282713198592</t>
+          <t>0a8393e2l1lq483xeda38ekbcqzbyd8h</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-万汇城-渗透</t>
+          <t>凤滁路高芯科谷-中科创新广场投放点F</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -6412,23 +6736,23 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -6441,10 +6765,13 @@
         </is>
       </c>
       <c r="L109" s="9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M109" s="9" t="n">
         <v>17</v>
+      </c>
+      <c r="N109" s="9" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -10377,7 +10704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10393,6 +10720,7 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10468,6 +10796,11 @@
           <t>08-04(二)</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>08-05(三)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -10494,25 +10827,25 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -10521,33 +10854,36 @@
       <c r="M3" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="N3" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
+          <t>893749163098365952</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>胜太西路47号汇金新天地广场站点</t>
+          <t>玉堂巷2-1号小里新寓站点A</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>2</v>
@@ -10556,60 +10892,63 @@
         <v>2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L4" s="9" t="n">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="M4" s="9" t="n">
         <v>24</v>
       </c>
+      <c r="N4" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
+          <t>893298745100976128</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>吉印大道融信·铂岸中心站点</t>
+          <t>江宁区科建路6-9号</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -10618,25 +10957,28 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L5" s="9" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>36</v>
+        <v>24</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
+          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
+          <t>胜太西路47号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -10653,16 +10995,16 @@
         <v>11</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -10675,21 +11017,24 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="N6" s="9" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
+          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>胜太西路45号汇金新天地广场站点</t>
+          <t>吉印大道融信·铂岸中心站点</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10699,23 +11044,23 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -10728,21 +11073,24 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
+          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>严南路金辉禹洲金陵铭著站点A</t>
+          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -10752,23 +11100,23 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -10781,21 +11129,24 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>33</v>
+        <v>23</v>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
+          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
+          <t>胜太西路45号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -10805,23 +11156,23 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -10834,21 +11185,24 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>48</v>
+        <v>22</v>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
+          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>平泰街太平花苑站点</t>
+          <t>严南路金辉禹洲金陵铭著站点A</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -10858,23 +11212,23 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -10887,21 +11241,24 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>12</v>
+        <v>33</v>
+      </c>
+      <c r="N10" s="9" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
+          <t>0a83e2bbl1lsd7prmyvenp48mu89cxm6</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>胜太西路天琪雅居站点</t>
+          <t>东大九龙湖校区地铁站2号口中粮·彩云居站点</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -10911,23 +11268,23 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -10940,21 +11297,24 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>11</v>
+        <v>48</v>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
+          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>胜太西路太平花苑北苑站点C</t>
+          <t>平泰街太平花苑站点</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -10971,43 +11331,46 @@
         <v>11</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="n">
+      <c r="M12" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M12" s="9" t="n">
-        <v>11</v>
+      <c r="N12" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1l4y8jhxjgrp6t9eecq3anb</t>
+          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>胜太路77-4号胜泰新寓站点</t>
+          <t>胜太西路天琪雅居站点</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11024,16 +11387,16 @@
         <v>11</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -11046,26 +11409,29 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>32</v>
+        <v>11</v>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1158030570667700224</t>
+          <t>0a896d7bl1l4vzexr6xbfpx9euc368fc</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>美龄宫</t>
+          <t>胜太西路太平花苑北苑站点C</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -11074,19 +11440,19 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1203</v>
+        <v>34</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -11099,47 +11465,50 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>668</v>
+        <v>12</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>535</v>
+        <v>11</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1158030572869709824</t>
+          <t>0a8399c6l1l4y8jhxjgrp6t9eecq3anb</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>东沟停车场</t>
+          <t>胜太路77-4号胜泰新寓站点</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>刘永振</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>893</v>
+        <v>76</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -11152,21 +11521,24 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>243</v>
+        <v>22</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>650</v>
+        <v>32</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1158030569614929920</t>
+          <t>1158030570667700224</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>海底世界站台</t>
+          <t>美龄宫</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -11180,19 +11552,19 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>410</v>
+        <v>1819</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -11205,21 +11577,24 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>209</v>
+        <v>668</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>201</v>
+        <v>535</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>616</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1158030573943451648</t>
+          <t>1158030572869709824</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>中山陵7号门</t>
+          <t>东沟停车场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11233,19 +11608,19 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>453</v>
+        <v>1557</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -11258,21 +11633,24 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>134</v>
+        <v>243</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>319</v>
+        <v>650</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1158025287508230144</t>
+          <t>1158030569614929920</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>3号门</t>
+          <t>海底世界站台</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11286,19 +11664,19 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>165</v>
+        <v>608</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -11311,21 +11689,24 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>44</v>
+        <v>209</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>121</v>
+        <v>201</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1158030563076009984</t>
+          <t>1158030573943451648</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺公园1</t>
+          <t>中山陵7号门</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11339,19 +11720,19 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>55</v>
+        <v>742</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -11364,21 +11745,24 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>22</v>
+        <v>319</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <v>289</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1158030568570548224</t>
+          <t>1158025287508230144</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>海底世界</t>
+          <t>3号门</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11395,16 +11779,16 @@
         <v>10</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>131</v>
+        <v>278</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -11417,21 +11801,24 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>85</v>
+        <v>121</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1158030571808550912</t>
+          <t>1158030563076009984</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>1号门</t>
+          <t>灵谷寺公园1</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11448,16 +11835,16 @@
         <v>10</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -11470,21 +11857,24 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="N21" s="9" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1158025279480332288</t>
+          <t>1158030568570548224</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2号门</t>
+          <t>海底世界</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11494,23 +11884,23 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>44</v>
+        <v>276</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -11523,127 +11913,136 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>22</v>
+        <v>85</v>
+      </c>
+      <c r="N22" s="9" t="n">
+        <v>145</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a83f070l1l3nefxhf3epn6wjp3gniq2</t>
+          <t>1158030571808550912</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>高新-地铁-交院地铁站2号口b</t>
+          <t>1号门</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>47</v>
-      </c>
       <c r="M23" s="9" t="n">
-        <v>51</v>
+        <v>23</v>
+      </c>
+      <c r="N23" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>0a83975dl1l7x9tn88g4jtig37jrdaaw</t>
+          <t>1158025279480332288</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>知行路江宁高新区人才公寓站点P</t>
+          <t>2号门</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘永振</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>11</v>
-      </c>
       <c r="M24" s="9" t="n">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="N24" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
+          <t>0a83f070l1l3nefxhf3epn6wjp3gniq2</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>高新-小区-瑾家珑熹台（南2门）-工作日-早高峰-12</t>
+          <t>高新-地铁-交院地铁站2号口b</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11653,23 +12052,23 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -11682,21 +12081,24 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>34</v>
+        <v>51</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a898873l1l2z5yttrk27pq8kwxsxux8</t>
+          <t>0a83975dl1l7x9tn88g4jtig37jrdaaw</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>高新-小区-瑾家珑熹台(南1门)-工作日-早高峰-12</t>
+          <t>知行路江宁高新区人才公寓站点P</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11706,23 +12108,23 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -11735,47 +12137,50 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="N26" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
+          <t>0a83a414l1lnkizbvg92gvnctvmcsxy4</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点H</t>
+          <t>高新-小区-瑾家珑熹台（南2门）-工作日-早高峰-12</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -11788,47 +12193,50 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>13</v>
+        <v>34</v>
+      </c>
+      <c r="N27" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>0a836758l1lnzcr39623ggbxyhbddncg</t>
+          <t>0a898873l1l2z5yttrk27pq8kwxsxux8</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点G</t>
+          <t>高新-小区-瑾家珑熹台(南1门)-工作日-早高峰-12</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>熊彦军</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -11841,21 +12249,24 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M28" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="N28" s="9" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>0a837fa4l1l27tpydpm8gjqn4qaqm6ef</t>
+          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>高新-商圈-中粮药膳鸡-全周-午晚高峰-30</t>
+          <t>天元东路辅路南京义乌小商品城站点H</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -11865,23 +12276,23 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -11894,21 +12305,24 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="N29" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>897042860272709632</t>
+          <t>0a836758l1lnzcr39623ggbxyhbddncg</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>高新-商圈-中粮悦天地西北门B-全周-午晚高峰-50</t>
+          <t>天元东路辅路南京义乌小商品城站点G</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -11925,16 +12339,16 @@
         <v>11</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -11947,21 +12361,24 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>45</v>
+        <v>23</v>
+      </c>
+      <c r="N30" s="9" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
+          <t>0a837fa4l1l27tpydpm8gjqn4qaqm6ef</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>竹山路地铁1号口</t>
+          <t>高新-商圈-中粮药膳鸡-全周-午晚高峰-30</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11971,23 +12388,23 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -12000,21 +12417,24 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>12</v>
+        <v>23</v>
+      </c>
+      <c r="N31" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
+          <t>897042860272709632</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>高新-写字楼-海丰小视科技中心-工作日-晚高峰-12</t>
+          <t>高新-商圈-中粮悦天地西北门B-全周-午晚高峰-50</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12031,16 +12451,16 @@
         <v>11</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -12053,21 +12473,24 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="M32" s="9" t="n">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>0a8320ecl1lvbzz3tyzcnk28dt6w9vz4</t>
+          <t>0a83ff7al1l5vr9epvjjipgzjyy7aq3j</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>逸夫医院门口左手</t>
+          <t>竹山路地铁1号口</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12077,23 +12500,23 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -12106,21 +12529,24 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M33" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="N33" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>0a83975dl1lsfxyiczcx2rt37eb2pmpx</t>
+          <t>0a83266cl1l9quuduphtrxkuwc3y3g7g</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>高新-商圈-中粮好想来-全周-午晚高峰-30</t>
+          <t>高新-写字楼-海丰小视科技中心-工作日-晚高峰-12</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12137,16 +12563,16 @@
         <v>11</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -12159,21 +12585,24 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>57</v>
+        <v>46</v>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>889855305298198528</t>
+          <t>0a83975dl1lsfxyiczcx2rt37eb2pmpx</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>科建路16号武夷绿洲站点3</t>
+          <t>高新-商圈-中粮好想来-全周-午晚高峰-30</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12183,50 +12612,53 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L35" s="9" t="n">
-        <v>12</v>
-      </c>
       <c r="M35" s="9" t="n">
-        <v>12</v>
+        <v>57</v>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1l2ef8wtmsfysajshhixta6</t>
+          <t>889855305298198528</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>鹏山路9号1幢金邻生活广场站点C</t>
+          <t>科建路16号武夷绿洲站点3</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -12236,23 +12668,23 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -12265,21 +12697,24 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M36" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="N36" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>0a83e9a8l1l5gi7n8g39kdamy6h6xzfc</t>
+          <t>0a83a414l1l2ef8wtmsfysajshhixta6</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路城市之光大厦站点</t>
+          <t>鹏山路9号1幢金邻生活广场站点C</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -12296,16 +12731,16 @@
         <v>11</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -12318,21 +12753,24 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>889833971314581504</t>
+          <t>0a83e9a8l1l5gi7n8g39kdamy6h6xzfc</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>江宁区天景山锦绣苑</t>
+          <t>天元东路辅路城市之光大厦站点</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12342,23 +12780,23 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -12376,16 +12814,19 @@
       <c r="M38" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="N38" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
+          <t>889833971314581504</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>鹏山路东方·龙湖湾站点Z2</t>
+          <t>江宁区天景山锦绣苑</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12402,16 +12843,16 @@
         <v>11</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -12424,21 +12865,24 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="N39" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>889836462803582976</t>
+          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点A</t>
+          <t>鹏山路东方·龙湖湾站点Z2</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12455,16 +12899,16 @@
         <v>11</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -12477,21 +12921,24 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="N40" s="9" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a833b7al1ln8b77uvihj3abdufjp6w4</t>
+          <t>889836462803582976</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>龙眠大道保利·樾广场站点O</t>
+          <t>天元东路辅路南京义乌小商品城站点A</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -12501,23 +12948,23 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -12530,21 +12977,24 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>61</v>
+        <v>13</v>
+      </c>
+      <c r="N41" s="9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>0a89810cl1lrxjz8hhcesusmyvs7jmw6</t>
+          <t>0a833b7al1ln8b77uvihj3abdufjp6w4</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>湖山路429号天景山公寓站点A</t>
+          <t>龙眠大道保利·樾广场站点O</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -12554,23 +13004,23 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -12583,47 +13033,50 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M42" s="9" t="n">
-        <v>12</v>
+        <v>61</v>
+      </c>
+      <c r="N42" s="9" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>889466722646794240</t>
+          <t>0a89810cl1lrxjz8hhcesusmyvs7jmw6</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>胜太东路江宁供销商厦站点</t>
+          <t>湖山路429号天景山公寓站点A</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>熊彦军</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -12636,21 +13089,24 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M43" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="N43" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>893750907107000320</t>
+          <t>889466722646794240</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>新医路27-2号小里新寓站点</t>
+          <t>胜太东路江宁供销商厦站点</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12660,23 +13116,23 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -12689,21 +13145,24 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="M44" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M44" s="9" t="n">
-        <v>24</v>
+      <c r="N44" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>893749163098365952</t>
+          <t>893750907107000320</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>玉堂巷2-1号小里新寓站点A</t>
+          <t>新医路27-2号小里新寓站点</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -12713,23 +13172,23 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -12742,11 +13201,14 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M45" s="9" t="n">
         <v>24</v>
       </c>
+      <c r="N45" s="9" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -12773,16 +13235,16 @@
         <v>12</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -12800,6 +13262,9 @@
       <c r="M46" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="N46" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -12826,16 +13291,16 @@
         <v>11</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -12853,6 +13318,9 @@
       <c r="M47" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="N47" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -12879,16 +13347,16 @@
         <v>11</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -12905,6 +13373,9 @@
       </c>
       <c r="M48" s="9" t="n">
         <v>11</v>
+      </c>
+      <c r="N48" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -14571,13 +15042,13 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -14600,13 +15071,13 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -14615,7 +15086,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>93.3%</t>
         </is>
       </c>
     </row>
@@ -14629,22 +15100,22 @@
         <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -14658,22 +15129,22 @@
         <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>93.3%</t>
         </is>
       </c>
     </row>
@@ -14687,22 +15158,22 @@
         <v>15</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.4%</t>
         </is>
       </c>
     </row>
@@ -14716,22 +15187,22 @@
         <v>10</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>96.7%</t>
         </is>
       </c>
     </row>
@@ -14745,13 +15216,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -14774,22 +15245,22 @@
         <v>14</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>69.0%</t>
         </is>
       </c>
     </row>
@@ -14803,13 +15274,13 @@
         <v>14</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -14818,7 +15289,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>88.1%</t>
         </is>
       </c>
     </row>
@@ -14832,22 +15303,22 @@
         <v>8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
     </row>
@@ -15285,13 +15756,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -15314,13 +15785,13 @@
         <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -15343,13 +15814,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -15372,13 +15843,13 @@
         <v>16</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -15387,7 +15858,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.9%</t>
         </is>
       </c>
     </row>
@@ -15401,22 +15872,22 @@
         <v>7</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>90.5%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -553,12 +553,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>79.0%</t>
         </is>
       </c>
     </row>
@@ -603,12 +603,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>98.4%</t>
         </is>
       </c>
     </row>
@@ -641,14 +641,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20260801 ~ 20260805</t>
+          <t>数据范围: 20260801 ~ 20260806</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 3天, 周末: 2天</t>
+          <t>工作日: 4天, 周末: 2天</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -701,6 +701,7 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,16 +782,21 @@
           <t>08-05(三)</t>
         </is>
       </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>08-06(四)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lj8cs3vsnr7r56rr3rgrgj</t>
+          <t>1153706318256898048</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>新浦路投放点B</t>
+          <t>浦口大道投放点渗透</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -800,27 +806,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -832,26 +838,29 @@
         <v>0</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>1098069901166710784</t>
+          <t>0a89826bl1l59cpgauqj57mi6t47n2cn</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-工业大学地铁站2号口渗透</t>
+          <t>软件大道润和创智中心投放点</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -860,140 +869,146 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N4" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>3</v>
+      <c r="O4" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>1153706318256898048</t>
+          <t>1174621727109263360</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>浦口大道投放点渗透</t>
+          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>16</v>
+      <c r="M5" s="9" t="n">
+        <v>40</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0a89826bl1l59cpgauqj57mi6t47n2cn</t>
+          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>软件大道润和创智中心投放点</t>
+          <t>中和路阿里中心·南京投放点A</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -1003,186 +1018,198 @@
         <v>15</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1174621727109263360</t>
+          <t>597639530744799232</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道延龄巷龙台国际大厦</t>
+          <t>南京市建邺区沙洲街道中胜地铁站5号口明基医院</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>20</v>
+        <v>6</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>0a83bbf3l1lepixh2snucnwxz7fn5cv6</t>
+          <t>0a83a497l1lj8cs3vsnr7r56rr3rgrgj</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>中和路阿里中心·南京投放点A</t>
+          <t>新浦路投放点B</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>15</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>597639530744799232</t>
+          <t>1206467184454987776</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道中胜地铁站5号口明基医院</t>
+          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1206467184454987776</t>
+          <t>1098069901166710784</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
+          <t>25-全天-地铁站-工业大学地铁站2号口渗透</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1192,333 +1219,351 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="9" t="n">
-        <v>42</v>
+      <c r="M10" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a83e334l1l38kski9q2syd6gczb42g8</t>
+          <t>732955785461030912</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>云密路汇智城(建设中)投放点</t>
+          <t>25-早峰-居民区-天润城5街区</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="n">
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="O11" s="7" t="n">
         <v>0</v>
-      </c>
-      <c r="M11" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="N11" s="9" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a83eb4fl1lz4hvkvkpdqc8mwis9httv</t>
+          <t>1077190082872029184</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>仙林中心(地铁站)投放点A</t>
+          <t>南京市建邺区沙洲街道嘉陵江东街地铁站</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H12" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="M12" s="7" t="n">
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="M12" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="N12" s="9" t="n">
-        <v>49</v>
+        <v>15</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
+          <t>0a83e334l1l38kski9q2syd6gczb42g8</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
+          <t>云密路汇智城(建设中)投放点</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>34</v>
+        <v>24</v>
+      </c>
+      <c r="O13" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1leh9rgc924wv39dv6m7mvs</t>
+          <t>0a83eb4fl1lz4hvkvkpdqc8mwis9httv</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>梦都大街东地铁站4B口江苏中烟工业有限责任公司南京卷烟投放点A</t>
+          <t>仙林中心(地铁站)投放点A</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="n">
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="M14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="N14" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="O14" s="9" t="n">
         <v>25</v>
-      </c>
-      <c r="N14" s="9" t="n">
-        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1077190082872029184</t>
+          <t>0a836587l1l52jyfb689jaxmnqbkj53d</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道嘉陵江东街地铁站</t>
+          <t>徐庄·苏宁总部地铁站7号口江苏软件园投放点A</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>15</v>
+        <v>34</v>
+      </c>
+      <c r="O15" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1174597131085402112</t>
+          <t>0a836146l1leh9rgc924wv39dv6m7mvs</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-地铁站-云南路地铁站渗透</t>
+          <t>梦都大街东地铁站4B口江苏中烟工业有限责任公司南京卷烟投放点A</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1535,46 +1580,49 @@
         <v>15</v>
       </c>
       <c r="F16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="n">
-        <v>17</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1076695373435187200</t>
+          <t>1174597131085402112</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区吴侯街地铁站</t>
+          <t>25-早峰-地铁站-云南路地铁站渗透</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1584,53 +1632,56 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="M17" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="N17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="9" t="n">
-        <v>47</v>
+      <c r="O17" s="9" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1153706290333523968</t>
+          <t>1076695373435187200</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>鼓楼区集庆门大街268号</t>
+          <t>南京市建邺区吴侯街地铁站</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1640,58 +1691,61 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="M18" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="N18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="M18" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>0a83b42bl1lurmqhqrwviu2qvdiirgcs</t>
+          <t>1153706290333523968</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>安德门大街楚翘城投放点G</t>
+          <t>鼓楼区集庆门大街268号</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1703,107 +1757,113 @@
         <v>15</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="N19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>12</v>
+      <c r="O19" s="9" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0a838c9fl1l6eu5z5992t8pxsi4euarb</t>
+          <t>690088208255492096</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>凤信路云密城投放点A</t>
+          <t>迈化路长营村15号小区投放点</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="O20" s="7" t="n">
         <v>0</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M20" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1174535930061524992</t>
+          <t>0a838c9fl1l6eu5z5992t8pxsi4euarb</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
+          <t>凤信路云密城投放点A</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1812,19 +1872,19 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1837,29 +1897,32 @@
         </is>
       </c>
       <c r="L21" s="8" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>854196782092722176</t>
+          <t>1174535930061524992</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-居民区-好的渗透</t>
+          <t>南京市秦淮区五老村街道太平南路长安国际中心(太平南路)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1868,19 +1931,19 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1893,50 +1956,53 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lduskfcd7fg98zc4m8acq2</t>
+          <t>854196782092722176</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>望江路正荣润锦城投放点C</t>
+          <t>工作日-全天-居民区-好的渗透</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1949,50 +2015,53 @@
         </is>
       </c>
       <c r="L23" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="M23" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="M23" s="8" t="n">
-        <v>20</v>
-      </c>
       <c r="N23" s="8" t="n">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>0a83384dl1lbqqk7xa7gxkbhz9gpmyzs</t>
+          <t>0a836587l1lduskfcd7fg98zc4m8acq2</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>西春路48号云密城投放点</t>
+          <t>望江路正荣润锦城投放点C</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2001,33 +2070,36 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L24" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>754365148238000128</t>
+          <t>0a83b42bl1lurmqhqrwviu2qvdiirgcs</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>玄武区四牌楼63号</t>
+          <t>安德门大街楚翘城投放点G</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -2036,19 +2108,19 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2057,54 +2129,57 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="n">
-        <v>37</v>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a83eb4fl1lyh6gadse7cuxyngppbre5</t>
+          <t>0a83384dl1lbqqk7xa7gxkbhz9gpmyzs</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>中胜地铁站2C口投放点</t>
+          <t>西春路48号云密城投放点</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2113,54 +2188,57 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L26" s="8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>754151861948555264</t>
+          <t>754365148238000128</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>23早高峰-全天-居民区-金浦御龙湾F区</t>
+          <t>玄武区四牌楼63号</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2169,54 +2247,57 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>853114235179171840</t>
+          <t>0a83eb4fl1lyh6gadse7cuxyngppbre5</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>全天-居民区-和燕花苑</t>
+          <t>中胜地铁站2C口投放点</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2225,17 +2306,20 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>10</v>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" s="9" t="n">
+        <v>29</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>24</v>
+        <v>7</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2263,16 +2347,16 @@
         <v>25</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2281,7 +2365,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L29" s="8" t="n">
@@ -2293,16 +2377,19 @@
       <c r="N29" s="9" t="n">
         <v>45</v>
       </c>
+      <c r="O29" s="8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>0a83612el1lx8dxfbxif2vsjehjqtwrj</t>
+          <t>732956005347999744</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>江山路投放点H</t>
+          <t>25-早峰-居民区-天润城十街区</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2312,23 +2399,23 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2337,54 +2424,57 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L30" s="8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>126</v>
+        <v>40</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>732956005347999744</t>
+          <t>1098070146307002368</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城十街区</t>
+          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2393,33 +2483,36 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="n">
-        <v>21</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>94</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>54</v>
-      </c>
-      <c r="N31" s="9" t="n">
-        <v>40</v>
+        <v>64</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>732955785461030912</t>
+          <t>f25bafa6cea44ac49303d053fcda9045</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城5街区</t>
+          <t>南京市建邺区沙洲街道中胜地铁站2A口</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2428,54 +2521,57 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="M32" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="M32" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="N32" s="9" t="n">
-        <v>72</v>
+      <c r="N32" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>1098070146307002368</t>
+          <t>0a8331f1l1lfxks8nftfew7gr7y37gvu</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>南京市栖霞区西岗街道经天路(地铁站)</t>
+          <t>西城路建邺科技创新产业园投放点A</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -2484,19 +2580,19 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>203</v>
+        <v>45</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2505,54 +2601,57 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>45</v>
+        <v>8</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>1176842717252255744</t>
+          <t>754151861948555264</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>三元巷6号三元公寓投放点渗透</t>
+          <t>23早高峰-全天-居民区-金浦御龙湾F区</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2561,54 +2660,57 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="N34" s="9" t="n">
-        <v>59</v>
+        <v>19</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
+          <t>853114235179171840</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>淮海路远洋国际中心投放点A</t>
+          <t>全天-居民区-和燕花苑</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2617,33 +2719,36 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="N35" s="9" t="n">
-        <v>29</v>
+        <v>10</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
+          <t>0a83612el1lx8dxfbxif2vsjehjqtwrj</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
+          <t>江山路投放点H</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -2652,19 +2757,19 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I36" s="3" t="n">
-        <v>99</v>
+        <v>357</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2673,54 +2778,57 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L36" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>8</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>96</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>61</v>
+        <v>126</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>f25bafa6cea44ac49303d053fcda9045</t>
+          <t>0a835aeel1lazxwqtfa664yxtxendmyu</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道中胜地铁站2A口</t>
+          <t>汇智路南海生物科技园投放点</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F37" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I37" s="3" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2729,89 +2837,95 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="N37" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="O37" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>0a8331f1l1lfxks8nftfew7gr7y37gvu</t>
+          <t>0a8398f6l1lw2mup86pcczvtx5uv56gv</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>西城路建邺科技创新产业园投放点A</t>
+          <t>宁双路软件谷垠坤·南京大数据产业基地投放点</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F38" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I38" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="M38" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="M38" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>8</v>
+      <c r="N38" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>724131086902996992</t>
+          <t>1176842717252255744</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>迈皋桥公交场站渗透</t>
+          <t>三元巷6号三元公寓投放点渗透</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -2820,75 +2934,78 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="M39" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="M39" s="9" t="n">
-        <v>80</v>
-      </c>
       <c r="N39" s="9" t="n">
-        <v>100</v>
+        <v>59</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>1110455282713198592</t>
+          <t>0a83ab2el1lxps7t4mcjvd48y5ryp479</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-万汇城-渗透</t>
+          <t>淮海路远洋国际中心投放点A</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I40" s="3" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2897,33 +3014,36 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="M40" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="N40" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="O40" s="9" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lfmy2n3ksr3ftxi64ycwsh</t>
+          <t>854249531796738048</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>钟阜路建宁路55号院投放点</t>
+          <t>25-全天-地铁站-金马路地铁站</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2932,19 +3052,19 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>146</v>
+        <v>282</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2953,54 +3073,57 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>43</v>
+        <v>90</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
+          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>九家圩路世茂外滩新城投放点A</t>
+          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>108</v>
+        <v>196</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3009,54 +3132,57 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="M42" s="9" t="n">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>15</v>
+        <v>61</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>1178909948933013504</t>
+          <t>d0f80f128e074902a9109772ebc0edc6</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-商圈-香格里拉渗透</t>
+          <t>南京市建邺区沙洲街道中胜地铁站1A</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>于继坤</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3065,33 +3191,36 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>56</v>
+        <v>25</v>
+      </c>
+      <c r="O43" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>724131086902996992</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>迈皋桥公交场站渗透</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -3100,19 +3229,19 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>800</v>
+        <v>270</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3121,33 +3250,36 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L44" s="9" t="n">
-        <v>151</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="M44" s="9" t="n">
-        <v>339</v>
+        <v>80</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>310</v>
+        <v>100</v>
+      </c>
+      <c r="O44" s="9" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>e5189cd954054116aa19db28790cc606</t>
+          <t>1110455282713198592</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-高新地铁站-30</t>
+          <t>25-全天-地铁站-万汇城-渗透</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3156,19 +3288,19 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>371</v>
+        <v>66</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3177,54 +3309,57 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>152</v>
-      </c>
-      <c r="N45" s="9" t="n">
-        <v>141</v>
+        <v>17</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="O45" s="9" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>554207268778184704</t>
+          <t>0a836587l1lfmy2n3ksr3ftxi64ycwsh</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路3号口</t>
+          <t>钟阜路建宁路55号院投放点</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>453</v>
+        <v>197</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3237,50 +3372,53 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>162</v>
+        <v>64</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>143</v>
+        <v>39</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>148</v>
+        <v>43</v>
+      </c>
+      <c r="O46" s="9" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>594063e60b264e419feea65370752c3f</t>
+          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
+          <t>九家圩路世茂外滩新城投放点A</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>424</v>
+        <v>142</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3293,29 +3431,32 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>177</v>
+        <v>15</v>
+      </c>
+      <c r="O47" s="9" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>1178909948933013504</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>25-早峰-商圈-香格里拉渗透</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>于继坤</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -3324,19 +3465,19 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>668</v>
+        <v>162</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3349,24 +3490,27 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>213</v>
+        <v>32</v>
       </c>
       <c r="M48" s="9" t="n">
-        <v>196</v>
+        <v>41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>259</v>
+        <v>56</v>
+      </c>
+      <c r="O48" s="9" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3380,19 +3524,19 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>551</v>
+        <v>924</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3405,24 +3549,27 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>212</v>
+        <v>339</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>178</v>
+        <v>310</v>
+      </c>
+      <c r="O49" s="9" t="n">
+        <v>124</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1l77t6e64cbw8rqk9kqakwh</t>
+          <t>e5189cd954054116aa19db28790cc606</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>江山路明发滨江新城三期投放点A</t>
+          <t>25-晚峰-地铁站-高新地铁站-30</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3432,23 +3579,23 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
         <v>30</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>291</v>
+        <v>512</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3461,24 +3608,27 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M50" s="9" t="n">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="N50" s="9" t="n">
-        <v>113</v>
+        <v>141</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>141</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>732955501476995072</t>
+          <t>554207268778184704</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-威尼斯三街区</t>
+          <t>25-晚峰-地铁站-柳州东路3号口</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3488,23 +3638,23 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>320</v>
+        <v>628</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3517,24 +3667,27 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="N51" s="9" t="n">
-        <v>100</v>
+        <v>148</v>
+      </c>
+      <c r="O51" s="9" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>626976116946362368</t>
+          <t>594063e60b264e419feea65370752c3f</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-润泰花园东30</t>
+          <t>25-晚峰-地铁站-天润城地铁站3号口</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3544,23 +3697,23 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
         <v>30</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>198</v>
+        <v>543</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3573,24 +3726,27 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="M52" s="9" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="N52" s="9" t="n">
-        <v>76</v>
+        <v>177</v>
+      </c>
+      <c r="O52" s="9" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>777073646895747072</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>25-全天-商场-1914街区</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3600,23 +3756,23 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>150</v>
+        <v>840</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -3629,24 +3785,27 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>50</v>
+        <v>213</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="N53" s="9" t="n">
-        <v>50</v>
+        <v>259</v>
+      </c>
+      <c r="O53" s="9" t="n">
+        <v>172</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>732955983377653760</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城1-4街区</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -3656,23 +3815,23 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>236</v>
+        <v>750</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -3685,24 +3844,27 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="M54" s="9" t="n">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="N54" s="9" t="n">
-        <v>72</v>
+        <v>178</v>
+      </c>
+      <c r="O54" s="9" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>732955258519240704</t>
+          <t>0a836146l1l77t6e64cbw8rqk9kqakwh</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路1号口</t>
+          <t>江山路明发滨江新城三期投放点A</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3712,23 +3874,23 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>575</v>
+        <v>391</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -3741,29 +3903,32 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>250</v>
+        <v>103</v>
       </c>
       <c r="N55" s="9" t="n">
-        <v>205</v>
+        <v>113</v>
+      </c>
+      <c r="O55" s="9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>0a838c9fl1l9eahd7x3xm2ecvtjwbbdv</t>
+          <t>732955501476995072</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>沙县小吃(南京第099店)凤翔新城投放点</t>
+          <t>25-早峰-居民区-威尼斯三街区</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -3775,16 +3940,16 @@
         <v>20</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>324</v>
+        <v>409</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -3797,50 +3962,53 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="N56" s="9" t="n">
-        <v>93</v>
+        <v>100</v>
+      </c>
+      <c r="O56" s="9" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>0a835aeel1lazxwqtfa664yxtxendmyu</t>
+          <t>626976116946362368</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>汇智路南海生物科技园投放点</t>
+          <t>25-早峰-居民区-润泰花园东30</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>87</v>
+        <v>276</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -3853,50 +4021,53 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="N57" s="9" t="n">
-        <v>47</v>
+        <v>76</v>
+      </c>
+      <c r="O57" s="9" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>0a8398f6l1lw2mup86pcczvtx5uv56gv</t>
+          <t>777073646895747072</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>宁双路软件谷垠坤·南京大数据产业基地投放点</t>
+          <t>25-全天-商场-1914街区</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>86</v>
+        <v>199</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -3909,50 +4080,53 @@
         </is>
       </c>
       <c r="L58" s="9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M58" s="9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="N58" s="9" t="n">
-        <v>23</v>
+        <v>50</v>
+      </c>
+      <c r="O58" s="9" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>584636981105418240</t>
+          <t>732955983377653760</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-羊山公园2号口</t>
+          <t>25-早峰-居民区-天润城1-4街区</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>383</v>
+        <v>315</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -3965,50 +4139,53 @@
         </is>
       </c>
       <c r="L59" s="9" t="n">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="N59" s="9" t="n">
-        <v>122</v>
+        <v>72</v>
+      </c>
+      <c r="O59" s="9" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
+          <t>732955258519240704</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁口-仙林中心站1号口</t>
+          <t>25-晚峰-地铁站-柳州东路1号口</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4021,50 +4198,53 @@
         </is>
       </c>
       <c r="L60" s="9" t="n">
-        <v>231</v>
+        <v>120</v>
       </c>
       <c r="M60" s="9" t="n">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="N60" s="9" t="n">
-        <v>262</v>
+        <v>205</v>
+      </c>
+      <c r="O60" s="9" t="n">
+        <v>143</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>684268350256898048</t>
+          <t>0a838c9fl1l9eahd7x3xm2ecvtjwbbdv</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-学则路</t>
+          <t>沙县小吃(南京第099店)凤翔新城投放点</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>135</v>
+        <v>471</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4077,24 +4257,27 @@
         </is>
       </c>
       <c r="L61" s="9" t="n">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="N61" s="9" t="n">
-        <v>45</v>
+        <v>93</v>
+      </c>
+      <c r="O61" s="9" t="n">
+        <v>147</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>1023193174134530048</t>
+          <t>584636981105418240</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>仙林大道投放点N</t>
+          <t>25-全天-地铁-羊山公园2号口</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -4104,23 +4287,23 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>183</v>
+        <v>488</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4133,24 +4316,27 @@
         </is>
       </c>
       <c r="L62" s="9" t="n">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="M62" s="9" t="n">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="N62" s="9" t="n">
-        <v>84</v>
+        <v>122</v>
+      </c>
+      <c r="O62" s="9" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>998560699433394176</t>
+          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>广志路南京万达茂投放点D</t>
+          <t>25-全天-地铁口-仙林中心站1号口</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4160,23 +4346,23 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>162</v>
+        <v>958</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4189,24 +4375,27 @@
         </is>
       </c>
       <c r="L63" s="9" t="n">
-        <v>25</v>
+        <v>231</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>64</v>
+        <v>224</v>
       </c>
       <c r="N63" s="9" t="n">
-        <v>73</v>
+        <v>262</v>
+      </c>
+      <c r="O63" s="9" t="n">
+        <v>241</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>778851422965239808</t>
+          <t>684268350256898048</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-仙林新村</t>
+          <t>25-全天-地铁-学则路</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -4216,23 +4405,23 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4248,21 +4437,24 @@
         <v>25</v>
       </c>
       <c r="M64" s="9" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="N64" s="9" t="n">
-        <v>50</v>
+        <v>45</v>
+      </c>
+      <c r="O64" s="9" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>1023193174134530048</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>仙林大道投放点N</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -4272,23 +4464,23 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>150</v>
+        <v>253</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4301,24 +4493,27 @@
         </is>
       </c>
       <c r="L65" s="9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M65" s="9" t="n">
         <v>50</v>
       </c>
       <c r="N65" s="9" t="n">
-        <v>50</v>
+        <v>84</v>
+      </c>
+      <c r="O65" s="9" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>1123869911569338368</t>
+          <t>998560699433394176</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>学衡路南京师范大学仙林校区投放点B</t>
+          <t>广志路南京万达茂投放点D</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -4335,16 +4530,16 @@
         <v>25</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>375</v>
+        <v>187</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4357,50 +4552,53 @@
         </is>
       </c>
       <c r="L66" s="9" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="M66" s="9" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="N66" s="9" t="n">
-        <v>125</v>
+        <v>73</v>
+      </c>
+      <c r="O66" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
+          <t>778851422965239808</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>中山东路228号新世纪广场A幢投放点</t>
+          <t>25-早峰-居民区-仙林新村</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>489</v>
+        <v>150</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -4413,50 +4611,53 @@
         </is>
       </c>
       <c r="L67" s="9" t="n">
-        <v>174</v>
+        <v>25</v>
       </c>
       <c r="M67" s="9" t="n">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="N67" s="9" t="n">
-        <v>191</v>
+        <v>50</v>
+      </c>
+      <c r="O67" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>1153706291117858816</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>385</v>
+        <v>200</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -4469,50 +4670,53 @@
         </is>
       </c>
       <c r="L68" s="9" t="n">
-        <v>144</v>
+        <v>50</v>
       </c>
       <c r="M68" s="9" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="N68" s="9" t="n">
-        <v>71</v>
+        <v>50</v>
+      </c>
+      <c r="O68" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
+          <t>1123869911569338368</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
+          <t>学衡路南京师范大学仙林校区投放点B</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>340</v>
+        <v>425</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -4525,24 +4729,27 @@
         </is>
       </c>
       <c r="L69" s="9" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M69" s="9" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="N69" s="9" t="n">
-        <v>81</v>
+        <v>125</v>
+      </c>
+      <c r="O69" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>1174622373773963264</t>
+          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道常府街地铁站</t>
+          <t>中山东路228号新世纪广场A幢投放点</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -4559,16 +4766,16 @@
         <v>20</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>574</v>
+        <v>654</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -4581,24 +4788,27 @@
         </is>
       </c>
       <c r="L70" s="9" t="n">
-        <v>318</v>
+        <v>174</v>
       </c>
       <c r="M70" s="9" t="n">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="N70" s="9" t="n">
+        <v>191</v>
+      </c>
+      <c r="O70" s="9" t="n">
         <v>165</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>1174627346911133696</t>
+          <t>1153706291117858816</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道户部街长发银座</t>
+          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4615,16 +4825,16 @@
         <v>20</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>140</v>
+        <v>538</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -4637,24 +4847,27 @@
         </is>
       </c>
       <c r="L71" s="9" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="M71" s="9" t="n">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="N71" s="9" t="n">
-        <v>60</v>
+        <v>71</v>
+      </c>
+      <c r="O71" s="9" t="n">
+        <v>153</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
+          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>石门坎地铁站3号口光华科技产业园投放点</t>
+          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -4668,19 +4881,19 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>220</v>
+        <v>403</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -4693,24 +4906,27 @@
         </is>
       </c>
       <c r="L72" s="9" t="n">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="M72" s="9" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="N72" s="9" t="n">
-        <v>61</v>
+        <v>81</v>
+      </c>
+      <c r="O72" s="9" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>5331e3a58a50481dbc8e7273561f4e25</t>
+          <t>1174622373773963264</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-地铁站-夫子庙2号口-10</t>
+          <t>南京市秦淮区洪武路街道常府街地铁站</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -4720,23 +4936,23 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>75</v>
+        <v>729</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -4749,24 +4965,27 @@
         </is>
       </c>
       <c r="L73" s="9" t="n">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="M73" s="9" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="N73" s="9" t="n">
-        <v>25</v>
+        <v>165</v>
+      </c>
+      <c r="O73" s="9" t="n">
+        <v>155</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>874549501386596352</t>
+          <t>1174627346911133696</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
+          <t>南京市秦淮区洪武路街道户部街长发银座</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -4776,53 +4995,56 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="F74" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L74" s="9" t="n">
-        <v>85</v>
-      </c>
       <c r="M74" s="9" t="n">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="N74" s="9" t="n">
-        <v>76</v>
+        <v>60</v>
+      </c>
+      <c r="O74" s="9" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>f72b5a964e164de7930e4077acb795b0</t>
+          <t>0a8974e0l1lzvjdnkezcvres7fh2jkrk</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道中华路宜必思酒店(南京夫子庙店)</t>
+          <t>石门坎地铁站3号口光华科技产业园投放点</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -4832,23 +5054,23 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>116</v>
+        <v>291</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -4861,24 +5083,27 @@
         </is>
       </c>
       <c r="L75" s="9" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M75" s="9" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N75" s="9" t="n">
-        <v>46</v>
+        <v>61</v>
+      </c>
+      <c r="O75" s="9" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lhbuznwmz926qn65svufex</t>
+          <t>5331e3a58a50481dbc8e7273561f4e25</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>中山南路280号张府园小区投放点A</t>
+          <t>工作日-全天-地铁站-夫子庙2号口-10</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -4888,23 +5113,23 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -4917,24 +5142,27 @@
         </is>
       </c>
       <c r="L76" s="9" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="M76" s="9" t="n">
         <v>25</v>
       </c>
       <c r="N76" s="9" t="n">
-        <v>42</v>
+        <v>25</v>
+      </c>
+      <c r="O76" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>732951617602912256</t>
+          <t>874549501386596352</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
+          <t>南京市秦淮区秦虹街道龙蟠汇投放点</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -4944,23 +5172,23 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>518</v>
+        <v>307</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -4973,50 +5201,53 @@
         </is>
       </c>
       <c r="L77" s="9" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M77" s="9" t="n">
-        <v>198</v>
+        <v>89</v>
       </c>
       <c r="N77" s="9" t="n">
-        <v>232</v>
+        <v>76</v>
+      </c>
+      <c r="O77" s="9" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>732956028185985024</t>
+          <t>f72b5a964e164de7930e4077acb795b0</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>下马坊地铁站</t>
+          <t>南京市秦淮区洪武路街道中华路宜必思酒店(南京夫子庙店)</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5029,29 +5260,32 @@
         </is>
       </c>
       <c r="L78" s="9" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M78" s="9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="N78" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="O78" s="9" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>854249531796738048</t>
+          <t>0a83a497l1lhbuznwmz926qn65svufex</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-金马路地铁站</t>
+          <t>中山南路280号张府园小区投放点A</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -5060,19 +5294,19 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>258</v>
+        <v>126</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5085,50 +5319,53 @@
         </is>
       </c>
       <c r="L79" s="9" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="M79" s="9" t="n">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="N79" s="9" t="n">
-        <v>90</v>
+        <v>42</v>
+      </c>
+      <c r="O79" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>816505037427507200</t>
+          <t>732951617602912256</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>玄武区童卫路28-2号</t>
+          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>337</v>
+        <v>576</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5141,24 +5378,27 @@
         </is>
       </c>
       <c r="L80" s="9" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M80" s="9" t="n">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="N80" s="9" t="n">
-        <v>98</v>
+        <v>232</v>
+      </c>
+      <c r="O80" s="9" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lbvs3sx44tiwdb7kvc7kap</t>
+          <t>732956028185985024</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>苏园路江苏软件园二期投放点A</t>
+          <t>下马坊地铁站</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -5172,19 +5412,19 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -5197,24 +5437,27 @@
         </is>
       </c>
       <c r="L81" s="9" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="M81" s="9" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="N81" s="9" t="n">
-        <v>40</v>
+        <v>45</v>
+      </c>
+      <c r="O81" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>857508296047517696</t>
+          <t>816505037427507200</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2b</t>
+          <t>玄武区童卫路28-2号</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -5228,19 +5471,19 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>169</v>
+        <v>433</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -5253,24 +5496,27 @@
         </is>
       </c>
       <c r="L82" s="9" t="n">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="M82" s="9" t="n">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="N82" s="9" t="n">
-        <v>64</v>
+        <v>98</v>
+      </c>
+      <c r="O82" s="9" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>0a838699l1lzri8zeup3f4zan2nxpmck</t>
+          <t>0a836587l1lbvs3sx44tiwdb7kvc7kap</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>童卫路南理工科技创新园投放点</t>
+          <t>苏园路江苏软件园二期投放点A</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -5280,23 +5526,23 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5309,24 +5555,27 @@
         </is>
       </c>
       <c r="L83" s="9" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M83" s="9" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="N83" s="9" t="n">
-        <v>72</v>
+        <v>40</v>
+      </c>
+      <c r="O83" s="9" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>788321551519383552</t>
+          <t>857508296047517696</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>玄武区鹤鸣路37号</t>
+          <t>钟灵街2b</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -5336,23 +5585,23 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>90</v>
+        <v>192</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -5365,24 +5614,27 @@
         </is>
       </c>
       <c r="L84" s="9" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M84" s="9" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="N84" s="9" t="n">
-        <v>40</v>
+        <v>64</v>
+      </c>
+      <c r="O84" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
+          <t>0a838699l1lzri8zeup3f4zan2nxpmck</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2A</t>
+          <t>童卫路南理工科技创新园投放点</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -5392,23 +5644,23 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>96</v>
+        <v>301</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -5421,24 +5673,27 @@
         </is>
       </c>
       <c r="L85" s="9" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="M85" s="9" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="N85" s="9" t="n">
-        <v>36</v>
+        <v>72</v>
+      </c>
+      <c r="O85" s="9" t="n">
+        <v>111</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>0a833ecdl1lcqyspwc7ejjhwh8vz5pfp</t>
+          <t>788321551519383552</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>石狮路辅路INS Mall·浪里投放点B</t>
+          <t>玄武区鹤鸣路37号</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -5455,16 +5710,16 @@
         <v>20</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -5477,29 +5732,32 @@
         </is>
       </c>
       <c r="L86" s="9" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="M86" s="9" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="N86" s="9" t="n">
         <v>40</v>
       </c>
+      <c r="O86" s="9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>948393128847777792</t>
+          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>30-工作日-全天-地铁-明故宫2渗透</t>
+          <t>钟灵街2A</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -5508,19 +5766,19 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>404</v>
+        <v>106</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -5533,29 +5791,32 @@
         </is>
       </c>
       <c r="L87" s="9" t="n">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="M87" s="9" t="n">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="N87" s="9" t="n">
-        <v>132</v>
+        <v>36</v>
+      </c>
+      <c r="O87" s="9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
+          <t>0a833ecdl1lcqyspwc7ejjhwh8vz5pfp</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>大行宫6号口渗透</t>
+          <t>石狮路辅路INS Mall·浪里投放点B</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>胡锐</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -5567,16 +5828,16 @@
         <v>20</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>435</v>
+        <v>143</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -5589,24 +5850,27 @@
         </is>
       </c>
       <c r="L88" s="9" t="n">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="M88" s="9" t="n">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="N88" s="9" t="n">
-        <v>183</v>
+        <v>40</v>
+      </c>
+      <c r="O88" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>816513511474413568</t>
+          <t>948393128847777792</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>熊猫</t>
+          <t>30-工作日-全天-地铁-明故宫2渗透</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -5616,23 +5880,23 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>358</v>
+        <v>516</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -5645,24 +5909,27 @@
         </is>
       </c>
       <c r="L89" s="9" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="M89" s="9" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="N89" s="9" t="n">
-        <v>114</v>
+        <v>132</v>
+      </c>
+      <c r="O89" s="9" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>大行宫6号口渗透</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -5679,16 +5946,16 @@
         <v>20</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>484</v>
+        <v>601</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -5701,24 +5968,27 @@
         </is>
       </c>
       <c r="L90" s="9" t="n">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="M90" s="9" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="N90" s="9" t="n">
-        <v>169</v>
+        <v>183</v>
+      </c>
+      <c r="O90" s="9" t="n">
+        <v>166</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>1176722757207629824</t>
+          <t>816513511474413568</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>规划建设展览馆渗透</t>
+          <t>熊猫</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -5728,23 +5998,23 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>224</v>
+        <v>493</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -5757,24 +6027,27 @@
         </is>
       </c>
       <c r="L91" s="9" t="n">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="M91" s="9" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="N91" s="9" t="n">
-        <v>49</v>
+        <v>114</v>
+      </c>
+      <c r="O91" s="9" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>732955102642126848</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>玄武区丹凤街69号</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -5784,23 +6057,23 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰点位</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>66</v>
+        <v>597</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -5813,24 +6086,27 @@
         </is>
       </c>
       <c r="L92" s="9" t="n">
-        <v>26</v>
+        <v>167</v>
       </c>
       <c r="M92" s="9" t="n">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="N92" s="9" t="n">
-        <v>20</v>
+        <v>169</v>
+      </c>
+      <c r="O92" s="9" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>732954989023625216</t>
+          <t>1176722757207629824</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-地铁站-鸡鸣寺地铁站渗透</t>
+          <t>规划建设展览馆渗透</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -5840,23 +6116,23 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>393</v>
+        <v>277</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -5869,50 +6145,53 @@
         </is>
       </c>
       <c r="L93" s="9" t="n">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="M93" s="9" t="n">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="N93" s="9" t="n">
-        <v>30</v>
+        <v>49</v>
+      </c>
+      <c r="O93" s="9" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
+          <t>732955102642126848</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>集贤路鼓楼创新广场投放点B</t>
+          <t>玄武区丹凤街69号</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -5925,50 +6204,53 @@
         </is>
       </c>
       <c r="L94" s="9" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="M94" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N94" s="9" t="n">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="O94" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>1206516292750213120</t>
+          <t>732954989023625216</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>中山北路宏图大厦渗透</t>
+          <t>工作日-全天-地铁站-鸡鸣寺地铁站渗透</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>胡锐</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>49</v>
+        <v>507</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -5981,24 +6263,27 @@
         </is>
       </c>
       <c r="L95" s="9" t="n">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>17</v>
+        <v>187</v>
       </c>
       <c r="N95" s="9" t="n">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="O95" s="9" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
+          <t>0a83612el1lvgjvs22amzxvqduth45bx</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>鼓楼区童家山2-3号楼</t>
+          <t>集贤路鼓楼创新广场投放点B</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -6008,23 +6293,23 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -6037,24 +6322,27 @@
         </is>
       </c>
       <c r="L96" s="9" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="M96" s="9" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N96" s="9" t="n">
-        <v>17</v>
+        <v>38</v>
+      </c>
+      <c r="O96" s="9" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>d0f80f128e074902a9109772ebc0edc6</t>
+          <t>1206516292750213120</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区沙洲街道中胜地铁站1A</t>
+          <t>中山北路宏图大厦渗透</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -6064,23 +6352,23 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -6093,50 +6381,53 @@
         </is>
       </c>
       <c r="L97" s="9" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="M97" s="9" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N97" s="9" t="n">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="O97" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>554207268614606848</t>
+          <t>0a83a7f2l1lsy25k3x5uysbbw4wnt2zg</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
+          <t>鼓楼区童家山2-3号楼</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>晚峰点位</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>630</v>
+        <v>113</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -6149,24 +6440,27 @@
         </is>
       </c>
       <c r="L98" s="9" t="n">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="M98" s="9" t="n">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="N98" s="9" t="n">
-        <v>277</v>
+        <v>17</v>
+      </c>
+      <c r="O98" s="9" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>1177090611149664256</t>
+          <t>554207268614606848</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>柚米社区</t>
+          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -6176,23 +6470,23 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>早峰点位</t>
+          <t>晚峰点位</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>138</v>
+        <v>801</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -6205,24 +6499,27 @@
         </is>
       </c>
       <c r="L99" s="9" t="n">
-        <v>48</v>
+        <v>193</v>
       </c>
       <c r="M99" s="9" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="N99" s="9" t="n">
-        <v>25</v>
+        <v>277</v>
+      </c>
+      <c r="O99" s="9" t="n">
+        <v>171</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>723758596467601408</t>
+          <t>1177090611149664256</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>全天-居民区-颐和府邸投放点A</t>
+          <t>柚米社区</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -6239,16 +6536,16 @@
         <v>20</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -6261,24 +6558,27 @@
         </is>
       </c>
       <c r="L100" s="9" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="M100" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="N100" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="N100" s="9" t="n">
-        <v>70</v>
+      <c r="O100" s="9" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>1008726508792258560</t>
+          <t>723758596467601408</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-南砖新村</t>
+          <t>全天-居民区-颐和府邸投放点A</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -6292,19 +6592,19 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -6323,18 +6623,21 @@
         <v>25</v>
       </c>
       <c r="N101" s="9" t="n">
-        <v>50</v>
+        <v>70</v>
+      </c>
+      <c r="O101" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>857062808558088192</t>
+          <t>1008726508792258560</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>23早高峰-全天-居民区-金浦御龙湾D区</t>
+          <t>25-早峰-居民区-南砖新村</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -6351,16 +6654,16 @@
         <v>25</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -6373,24 +6676,27 @@
         </is>
       </c>
       <c r="L102" s="9" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="M102" s="9" t="n">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="N102" s="9" t="n">
-        <v>65</v>
+        <v>50</v>
+      </c>
+      <c r="O102" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>690088208255492096</t>
+          <t>857062808558088192</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>迈化路长营村15号小区投放点</t>
+          <t>23早高峰-全天-居民区-金浦御龙湾D区</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -6404,19 +6710,19 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>160</v>
+        <v>251</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -6429,13 +6735,16 @@
         </is>
       </c>
       <c r="L103" s="9" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M103" s="9" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="N103" s="9" t="n">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="O103" s="9" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="104">
@@ -6463,16 +6772,16 @@
         <v>25</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -6493,6 +6802,9 @@
       <c r="N104" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="O104" s="9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -6519,16 +6831,16 @@
         <v>25</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -6549,6 +6861,9 @@
       <c r="N105" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="O105" s="9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -6575,16 +6890,16 @@
         <v>20</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -6605,6 +6920,9 @@
       <c r="N106" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="O106" s="9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -6631,16 +6949,16 @@
         <v>25</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -6661,6 +6979,9 @@
       <c r="N107" s="9" t="n">
         <v>43</v>
       </c>
+      <c r="O107" s="9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -6687,16 +7008,16 @@
         <v>20</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -6717,6 +7038,9 @@
       <c r="N108" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="O108" s="9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
@@ -6743,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -6772,6 +7096,9 @@
       </c>
       <c r="N109" s="9" t="n">
         <v>18</v>
+      </c>
+      <c r="O109" s="9" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -10704,7 +11031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10721,6 +11048,7 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10801,6 +11129,11 @@
           <t>08-05(三)</t>
         </is>
       </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>08-06(四)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -10827,25 +11160,25 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -10857,6 +11190,9 @@
       <c r="N3" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="O3" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -10883,25 +11219,25 @@
         <v>11</v>
       </c>
       <c r="F4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="H4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L4" s="9" t="n">
@@ -10913,6 +11249,9 @@
       <c r="N4" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="O4" s="9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -10939,16 +11278,16 @@
         <v>20</v>
       </c>
       <c r="F5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -10957,7 +11296,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L5" s="9" t="n">
@@ -10969,6 +11308,9 @@
       <c r="N5" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="O5" s="9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -10995,16 +11337,16 @@
         <v>11</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -11025,6 +11367,9 @@
       <c r="N6" s="9" t="n">
         <v>34</v>
       </c>
+      <c r="O6" s="9" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -11051,16 +11396,16 @@
         <v>11</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -11081,6 +11426,9 @@
       <c r="N7" s="9" t="n">
         <v>26</v>
       </c>
+      <c r="O7" s="9" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -11107,16 +11455,16 @@
         <v>11</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -11137,6 +11485,9 @@
       <c r="N8" s="9" t="n">
         <v>36</v>
       </c>
+      <c r="O8" s="9" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -11163,16 +11514,16 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -11193,6 +11544,9 @@
       <c r="N9" s="9" t="n">
         <v>22</v>
       </c>
+      <c r="O9" s="9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -11219,16 +11573,16 @@
         <v>11</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -11249,6 +11603,9 @@
       <c r="N10" s="9" t="n">
         <v>44</v>
       </c>
+      <c r="O10" s="9" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -11275,16 +11632,16 @@
         <v>11</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -11305,6 +11662,9 @@
       <c r="N11" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="O11" s="9" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -11331,16 +11691,16 @@
         <v>11</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -11361,6 +11721,9 @@
       <c r="N12" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="O12" s="9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -11387,16 +11750,16 @@
         <v>11</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -11417,6 +11780,9 @@
       <c r="N13" s="9" t="n">
         <v>23</v>
       </c>
+      <c r="O13" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -11443,16 +11809,16 @@
         <v>11</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -11473,6 +11839,9 @@
       <c r="N14" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="O14" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -11499,16 +11868,16 @@
         <v>11</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -11529,6 +11898,9 @@
       <c r="N15" s="9" t="n">
         <v>22</v>
       </c>
+      <c r="O15" s="9" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -11555,16 +11927,16 @@
         <v>60</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1819</v>
+        <v>2325</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -11585,6 +11957,9 @@
       <c r="N16" s="9" t="n">
         <v>616</v>
       </c>
+      <c r="O16" s="9" t="n">
+        <v>506</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -11611,16 +11986,16 @@
         <v>30</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1557</v>
+        <v>1934</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -11641,6 +12016,9 @@
       <c r="N17" s="9" t="n">
         <v>664</v>
       </c>
+      <c r="O17" s="9" t="n">
+        <v>377</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -11667,16 +12045,16 @@
         <v>20</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>608</v>
+        <v>841</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -11697,6 +12075,9 @@
       <c r="N18" s="9" t="n">
         <v>198</v>
       </c>
+      <c r="O18" s="9" t="n">
+        <v>233</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -11723,16 +12104,16 @@
         <v>20</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>742</v>
+        <v>1019</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -11753,6 +12134,9 @@
       <c r="N19" s="9" t="n">
         <v>289</v>
       </c>
+      <c r="O19" s="9" t="n">
+        <v>277</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -11779,16 +12163,16 @@
         <v>10</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>278</v>
+        <v>402</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -11809,6 +12193,9 @@
       <c r="N20" s="9" t="n">
         <v>113</v>
       </c>
+      <c r="O20" s="9" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -11835,16 +12222,16 @@
         <v>10</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>121</v>
+        <v>231</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -11865,6 +12252,9 @@
       <c r="N21" s="9" t="n">
         <v>66</v>
       </c>
+      <c r="O21" s="9" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -11891,16 +12281,16 @@
         <v>10</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>276</v>
+        <v>365</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -11921,6 +12311,9 @@
       <c r="N22" s="9" t="n">
         <v>145</v>
       </c>
+      <c r="O22" s="9" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -11947,16 +12340,16 @@
         <v>10</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -11977,6 +12370,9 @@
       <c r="N23" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="O23" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -12003,16 +12399,16 @@
         <v>10</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -12033,6 +12429,9 @@
       <c r="N24" s="9" t="n">
         <v>23</v>
       </c>
+      <c r="O24" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -12059,16 +12458,16 @@
         <v>11</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -12089,6 +12488,9 @@
       <c r="N25" s="9" t="n">
         <v>58</v>
       </c>
+      <c r="O25" s="9" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -12115,16 +12517,16 @@
         <v>11</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -12145,6 +12547,9 @@
       <c r="N26" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="O26" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -12171,16 +12576,16 @@
         <v>11</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -12201,6 +12606,9 @@
       <c r="N27" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="O27" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -12227,16 +12635,16 @@
         <v>11</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -12257,6 +12665,9 @@
       <c r="N28" s="9" t="n">
         <v>23</v>
       </c>
+      <c r="O28" s="9" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -12283,16 +12694,16 @@
         <v>11</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -12313,6 +12724,9 @@
       <c r="N29" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="O29" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -12339,16 +12753,16 @@
         <v>11</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -12369,6 +12783,9 @@
       <c r="N30" s="9" t="n">
         <v>36</v>
       </c>
+      <c r="O30" s="9" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -12395,16 +12812,16 @@
         <v>11</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -12425,6 +12842,9 @@
       <c r="N31" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="O31" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -12451,16 +12871,16 @@
         <v>11</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -12481,6 +12901,9 @@
       <c r="N32" s="9" t="n">
         <v>44</v>
       </c>
+      <c r="O32" s="9" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -12507,16 +12930,16 @@
         <v>11</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -12537,6 +12960,9 @@
       <c r="N33" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="O33" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -12563,16 +12989,16 @@
         <v>11</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -12593,6 +13019,9 @@
       <c r="N34" s="9" t="n">
         <v>63</v>
       </c>
+      <c r="O34" s="9" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -12619,16 +13048,16 @@
         <v>11</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -12649,6 +13078,9 @@
       <c r="N35" s="9" t="n">
         <v>45</v>
       </c>
+      <c r="O35" s="9" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -12675,16 +13107,16 @@
         <v>11</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -12705,6 +13137,9 @@
       <c r="N36" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="O36" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -12731,16 +13166,16 @@
         <v>11</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -12761,6 +13196,9 @@
       <c r="N37" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="O37" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -12787,16 +13225,16 @@
         <v>11</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -12817,6 +13255,9 @@
       <c r="N38" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="O38" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -12843,16 +13284,16 @@
         <v>11</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -12873,6 +13314,9 @@
       <c r="N39" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="O39" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -12899,16 +13343,16 @@
         <v>11</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -12929,6 +13373,9 @@
       <c r="N40" s="9" t="n">
         <v>33</v>
       </c>
+      <c r="O40" s="9" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -12955,16 +13402,16 @@
         <v>11</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -12985,6 +13432,9 @@
       <c r="N41" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="O41" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -13011,16 +13461,16 @@
         <v>15</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -13041,6 +13491,9 @@
       <c r="N42" s="9" t="n">
         <v>61</v>
       </c>
+      <c r="O42" s="9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -13067,16 +13520,16 @@
         <v>11</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -13097,6 +13550,9 @@
       <c r="N43" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="O43" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -13123,16 +13579,16 @@
         <v>11</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -13153,6 +13609,9 @@
       <c r="N44" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="O44" s="9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -13179,16 +13638,16 @@
         <v>11</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -13209,6 +13668,9 @@
       <c r="N45" s="9" t="n">
         <v>32</v>
       </c>
+      <c r="O45" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -13235,16 +13697,16 @@
         <v>12</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -13265,6 +13727,9 @@
       <c r="N46" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="O46" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -13291,16 +13756,16 @@
         <v>11</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -13321,6 +13786,9 @@
       <c r="N47" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="O47" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -13347,16 +13815,16 @@
         <v>11</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -13375,6 +13843,9 @@
         <v>11</v>
       </c>
       <c r="N48" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="O48" s="9" t="n">
         <v>12</v>
       </c>
     </row>
@@ -15042,13 +15513,13 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -15071,22 +15542,22 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -15100,22 +15571,22 @@
         <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -15129,22 +15600,22 @@
         <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>92.5%</t>
         </is>
       </c>
     </row>
@@ -15158,22 +15629,22 @@
         <v>15</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -15187,22 +15658,22 @@
         <v>10</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>95.0%</t>
         </is>
       </c>
     </row>
@@ -15216,13 +15687,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -15245,22 +15716,22 @@
         <v>14</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -15274,22 +15745,22 @@
         <v>14</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>89.3%</t>
         </is>
       </c>
     </row>
@@ -15303,22 +15774,22 @@
         <v>8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
     </row>
@@ -15756,13 +16227,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -15785,13 +16256,13 @@
         <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -15814,13 +16285,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -15843,13 +16314,13 @@
         <v>16</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -15858,7 +16329,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.4%</t>
         </is>
       </c>
     </row>
@@ -15872,22 +16343,22 @@
         <v>7</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>92.9%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -566,12 +566,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
@@ -828,47 +828,47 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>796589147581059072</t>
+          <t>1146360435397558272</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>南京邮电大学渗透</t>
+          <t>红山学院-学生公寓9号楼</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>季晨曦</t>
+          <t>桂超</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -890,11 +890,11 @@
       <c r="P3" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8" t="n">
-        <v>0</v>
+      <c r="Q3" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R3" s="9" t="n">
+        <v>100</v>
       </c>
       <c r="S3" s="8" t="n">
         <v>0</v>
@@ -903,26 +903,26 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>1146360435397558272</t>
+          <t>1206516292750213120</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>红山学院-学生公寓9号楼</t>
+          <t>中山北路宏图大厦渗透</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>桂超</t>
+          <t>季晨曦</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>6</v>
@@ -934,7 +934,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="n">
-        <v>0</v>
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>21</v>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
@@ -965,11 +965,11 @@
       <c r="P4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="9" t="n">
-        <v>25</v>
+      <c r="Q4" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="R4" s="9" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="S4" s="8" t="n">
         <v>0</v>
@@ -978,17 +978,17 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>1206516292750213120</t>
+          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>中山北路宏图大厦渗透</t>
+          <t>九家圩路世茂外滩新城投放点A</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>季晨曦</t>
+          <t>袁博</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1009,7 +1009,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -1023,11 +1023,11 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>20☂</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>21</v>
+          <t>54☂</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
@@ -1040,69 +1040,71 @@
       <c r="P5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="Q5" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="R5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="S5" s="8" t="n">
-        <v>0</v>
+      <c r="S5" s="9" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1206516292750213120</t>
+          <t>0a832885l1lmfyyu2hdqnciwuq2965xt</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>内环北线南京工业大学国家大学科技园投放点C</t>
+          <t>中华路夫子庙秦淮风光带投放点B</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>季晨曦</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>20☂</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="n">
-        <v>21</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
@@ -1112,77 +1114,73 @@
       <c r="O6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="8" t="n">
-        <v>0</v>
+      <c r="P6" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="Q6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="S6" s="8" t="n">
+      <c r="R6" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="S6" s="9" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1l53j82u2t2b5ribpqy4yg8</t>
+          <t>1172004123334877184</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>九家圩路世茂外滩新城投放点A</t>
+          <t>25-全天-景区-先锋书店渗透</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>袁博</t>
+          <t>季晨曦</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>54☂</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="n">
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" s="8" t="n">
         <v>0</v>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
       </c>
       <c r="O7" s="8" t="n">
         <v>0</v>
@@ -1190,60 +1188,60 @@
       <c r="P7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="R7" s="8" t="n">
+      <c r="Q7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="9" t="n">
-        <v>33</v>
+      <c r="R7" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S7" s="10" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>0a832885l1lmfyyu2hdqnciwuq2965xt</t>
+          <t>1150293617358008320</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>中华路夫子庙秦淮风光带投放点B</t>
+          <t>白马-食堂</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>桂超</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰+夜间</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -1251,10 +1249,8 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="M8" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
@@ -1264,38 +1260,38 @@
       <c r="O8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="10" t="n">
-        <v>16</v>
+      <c r="P8" s="9" t="n">
+        <v>60</v>
       </c>
       <c r="Q8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="9" t="n">
-        <v>41</v>
+      <c r="R8" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="S8" s="10" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>1150293617358008320</t>
+          <t>684029950445703168</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>白马-食堂</t>
+          <t>江山路投放点</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>桂超</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -1311,7 +1307,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1328,53 +1324,53 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>18☂</t>
+        </is>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="P9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="n">
+      <c r="Q9" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q9" s="8" t="n">
+      <c r="S9" s="8" t="n">
         <v>0</v>
-      </c>
-      <c r="R9" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="S9" s="10" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>684029950445703168</t>
+          <t>0a83a497l1lcd7nmuf65dsa5z6sdj5vv</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>江山路投放点</t>
+          <t>江东中路108-13号南京万达广场投放点A</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>6</v>
@@ -1383,10 +1379,10 @@
         <v>3</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1395,7 +1391,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -1403,22 +1399,22 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="M10" s="9" t="n">
-        <v>50</v>
+      <c r="M10" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>18☂</t>
-        </is>
-      </c>
-      <c r="O10" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="P10" s="8" t="n">
-        <v>0</v>
+          <t>30☂</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>30</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>0</v>
@@ -1430,12 +1426,12 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lcd7nmuf65dsa5z6sdj5vv</t>
+          <t>1028995958944616448</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>江东中路108-13号南京万达广场投放点A</t>
+          <t>南京市建邺区莫愁湖街道云锦路地铁站1号口</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1445,7 +1441,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
@@ -1461,7 +1457,7 @@
         <v>3</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1471,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>24☂</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1483,20 +1479,20 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>30☂</t>
+          <t>53☂</t>
         </is>
       </c>
       <c r="O11" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="P11" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="R11" s="8" t="n">
-        <v>0</v>
+      <c r="R11" s="9" t="n">
+        <v>30</v>
       </c>
       <c r="S11" s="8" t="n">
         <v>0</v>
@@ -1505,22 +1501,22 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1028995958944616448</t>
+          <t>0a837567l1l4y9kacpmee6a7hsrxt7v5</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>南京市建邺区莫愁湖街道云锦路地铁站1号口</t>
+          <t>中央路222号金茂览秀城投放点</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>季晨曦</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
@@ -1550,7 +1546,7 @@
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>24☂</t>
+          <t>30☂</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1558,114 +1554,110 @@
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>53☂</t>
-        </is>
-      </c>
-      <c r="O12" s="9" t="n">
-        <v>31</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="P12" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="S12" s="8" t="n">
-        <v>0</v>
+      <c r="S12" s="9" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a837567l1l4y9kacpmee6a7hsrxt7v5</t>
+          <t>1174627346911133696</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>中央路222号金茂览秀城投放点</t>
+          <t>南京市秦淮区洪武路街道户部街长发银座</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>季晨曦</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>10</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>30☂</t>
-        </is>
       </c>
       <c r="M13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="O13" s="8" t="n">
+      <c r="N13" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="P13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="9" t="n">
-        <v>47</v>
+      <c r="Q13" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="R13" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="S13" s="9" t="n">
-        <v>61</v>
+        <v>22</v>
+      </c>
+      <c r="S13" s="10" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1174627346911133696</t>
+          <t>939721465176301568</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道户部街长发银座</t>
+          <t>25-全天-居民区-旭日上城5区</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1674,7 +1666,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>8</v>
@@ -1683,10 +1675,10 @@
         <v>5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1695,48 +1687,48 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="L14" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M14" s="8" t="n">
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="10" t="n">
-        <v>10</v>
+      <c r="M14" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>21</v>
       </c>
       <c r="P14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="R14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9" t="n">
         <v>22</v>
-      </c>
-      <c r="S14" s="10" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>939721465176301568</t>
+          <t>754367403259662336</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-旭日上城5区</t>
+          <t>玄武区珠江路79号</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1745,7 +1737,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>8</v>
@@ -1754,10 +1746,10 @@
         <v>5</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1766,43 +1758,43 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="n">
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="N15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="N15" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="O15" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="P15" s="8" t="n">
+      <c r="O15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="10" t="n">
-        <v>1</v>
+      <c r="P15" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>16</v>
       </c>
       <c r="R15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>754367403259662336</t>
+          <t>1176722757207629824</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>玄武区珠江路79号</t>
+          <t>规划建设展览馆渗透</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1812,11 +1804,11 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>夜间</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>8</v>
@@ -1828,7 +1820,7 @@
         <v>5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1840,116 +1832,120 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="L16" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="N16" s="8" t="n">
+      <c r="L16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="8" t="n">
+      <c r="M16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="9" t="n">
-        <v>26</v>
+      <c r="N16" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="R16" s="8" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>25</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1176722757207629824</t>
+          <t>939771822760374272</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>规划建设展览馆渗透</t>
+          <t>建邺区莫愁湖街道江南名府</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>许永青</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>夜间</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>25☂</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="O17" s="9" t="n">
-        <v>49</v>
       </c>
       <c r="P17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R17" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="S17" s="9" t="n">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>939771822760374272</t>
+          <t>1174597131085402112</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>建邺区莫愁湖街道江南名府</t>
+          <t>25-早峰-地铁站-云南路地铁站渗透</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>许永青</t>
+          <t>季晨曦</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1958,7 +1954,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>6</v>
@@ -1967,10 +1963,10 @@
         <v>4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1979,7 +1975,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -1987,53 +1983,53 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="M18" s="10" t="n">
-        <v>6</v>
+      <c r="M18" s="9" t="n">
+        <v>34</v>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>25☂</t>
-        </is>
-      </c>
-      <c r="O18" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="P18" s="8" t="n">
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="R18" s="8" t="n">
+      <c r="P18" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="R18" s="10" t="n">
+        <v>14</v>
+      </c>
       <c r="S18" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1174597131085402112</t>
+          <t>0a83a497l1lqdjntf3q76pvpqwudjgfs</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-地铁站-云南路地铁站渗透</t>
+          <t>石狮路辅路绿地云都会投放点A</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>季晨曦</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>6</v>
@@ -2045,7 +2041,7 @@
         <v>2</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -2063,43 +2059,43 @@
         </is>
       </c>
       <c r="M19" s="9" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>20☂</t>
-        </is>
-      </c>
-      <c r="O19" s="8" t="n">
+          <t>21☂</t>
+        </is>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q19" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="R19" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q19" s="8" t="n">
+      <c r="S19" s="8" t="n">
         <v>0</v>
-      </c>
-      <c r="R19" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="S19" s="10" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1lqdjntf3q76pvpqwudjgfs</t>
+          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>石狮路辅路绿地云都会投放点A</t>
+          <t>钟灵街2A</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2108,7 +2104,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>6</v>
@@ -2117,10 +2113,10 @@
         <v>4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2129,47 +2125,47 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>44☂</t>
         </is>
       </c>
       <c r="M20" s="9" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>21☂</t>
-        </is>
-      </c>
-      <c r="O20" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="P20" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q20" s="10" t="n">
-        <v>13</v>
+          <t>6☂</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>47</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="8" t="n">
-        <v>0</v>
+      <c r="S20" s="9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
+          <t>878937641051193344</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2A</t>
+          <t>工作日-全天-居民区-双拜巷</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2179,7 +2175,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
@@ -2195,7 +2191,7 @@
         <v>3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2209,47 +2205,47 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>44☂</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="n">
-        <v>25</v>
+          <t>15☂</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>6☂</t>
+          <t>5☂</t>
         </is>
       </c>
       <c r="O21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="10" t="n">
-        <v>14</v>
+      <c r="P21" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="R21" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="R21" s="9" t="n">
+        <v>19</v>
       </c>
       <c r="S21" s="9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>878937641051193344</t>
+          <t>601342234557509632</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-居民区-双拜巷</t>
+          <t>25-全天-居民区-学生公寓-南苑-80</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>桂超</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2258,7 +2254,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>6</v>
@@ -2267,10 +2263,10 @@
         <v>4</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>85</v>
+        <v>822</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2279,20 +2275,20 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>15☂</t>
-        </is>
-      </c>
-      <c r="M22" s="10" t="n">
-        <v>12</v>
+          <t>180☂</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="n">
+        <v>123</v>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>5☂</t>
+          <t>0☂</t>
         </is>
       </c>
       <c r="O22" s="8" t="n">
@@ -2302,24 +2298,24 @@
         <v>0</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R22" s="9" t="n">
-        <v>19</v>
+        <v>272</v>
       </c>
       <c r="S22" s="9" t="n">
-        <v>19</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>601342234557509632</t>
+          <t>1150622201246429184</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-学生公寓-南苑-80</t>
+          <t>南师大-博士生公寓</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2345,7 +2341,7 @@
         <v>4</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>822</v>
+        <v>146</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2359,47 +2355,47 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>180☂</t>
-        </is>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>123</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>0</v>
+          <t>21☂</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="n">
+        <v>22</v>
       </c>
       <c r="P23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R23" s="9" t="n">
-        <v>272</v>
+        <v>42</v>
       </c>
       <c r="S23" s="9" t="n">
-        <v>222</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>1150622201246429184</t>
+          <t>1174593029863960576</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>南师大-博士生公寓</t>
+          <t>25-全天-高校-师范大学渗透</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>桂超</t>
+          <t>季晨曦</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2408,7 +2404,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>6</v>
@@ -2420,7 +2416,7 @@
         <v>4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2434,47 +2430,47 @@
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="n">
+          <t>33☂</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>26☂</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="n">
         <v>0</v>
-      </c>
-      <c r="N24" s="7" t="inlineStr">
-        <is>
-          <t>21☂</t>
-        </is>
-      </c>
-      <c r="O24" s="9" t="n">
-        <v>22</v>
       </c>
       <c r="P24" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R24" s="9" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="S24" s="9" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1174593029863960576</t>
+          <t>0a83a743l1l543cya5xwy3fctzevinw2</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>25-全天-高校-师范大学渗透</t>
+          <t>长白街万厦商务楼投放点</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>季晨曦</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -2483,7 +2479,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>6</v>
@@ -2495,7 +2491,7 @@
         <v>4</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2509,47 +2505,47 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>33☂</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>26</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>26☂</t>
-        </is>
-      </c>
-      <c r="O25" s="8" t="n">
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="R25" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="P25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="R25" s="9" t="n">
-        <v>25</v>
-      </c>
       <c r="S25" s="9" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a83a743l1l543cya5xwy3fctzevinw2</t>
+          <t>1206515660536758272</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>长白街万厦商务楼投放点</t>
+          <t>南京邮电大学渗透</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>季晨曦</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2558,7 +2554,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>6</v>
@@ -2570,7 +2566,7 @@
         <v>4</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2587,39 +2583,39 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>31☂</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="P26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>20☂</t>
-        </is>
-      </c>
-      <c r="O26" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="P26" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q26" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R26" s="8" t="n">
+      <c r="Q26" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="R26" s="9" t="n">
+        <v>49</v>
+      </c>
       <c r="S26" s="9" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>1101025006370287616</t>
+          <t>0a83cb70l1l8mh5bczz58u3svwm3k2si</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>南昌路68号新金贸花园投放点</t>
+          <t>内环北线南京工业大学国家大学科技园投放点C</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2629,7 +2625,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -2645,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2659,22 +2655,22 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>40☂</t>
+          <t>64☂</t>
         </is>
       </c>
       <c r="M27" s="9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>32☂</t>
-        </is>
-      </c>
-      <c r="O27" s="8" t="n">
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="P27" s="8" t="n">
         <v>0</v>
-      </c>
-      <c r="P27" s="9" t="n">
-        <v>32</v>
       </c>
       <c r="Q27" s="8" t="n">
         <v>0</v>
@@ -2683,7 +2679,7 @@
         <v>28</v>
       </c>
       <c r="S27" s="9" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
@@ -10556,87 +10552,87 @@
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>0a838c9fl1l9eahd7x3xm2ecvtjwbbdv</t>
+          <t>1221340620200710144</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>沙县小吃(南京第099店)凤翔新城投放点</t>
+          <t>南昌路68号新金贸花园投放点</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>季晨曦</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>17☂</t>
+        </is>
+      </c>
+      <c r="M133" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="N133" s="7" t="inlineStr">
+        <is>
+          <t>32☂</t>
+        </is>
+      </c>
+      <c r="O133" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="P133" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q133" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F133" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G133" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H133" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I133" s="3" t="n">
-        <v>920</v>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K133" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L133" s="7" t="inlineStr">
-        <is>
-          <t>48☂</t>
-        </is>
-      </c>
-      <c r="M133" s="9" t="n">
-        <v>133</v>
-      </c>
-      <c r="N133" s="7" t="inlineStr">
-        <is>
-          <t>75☂</t>
-        </is>
-      </c>
-      <c r="O133" s="9" t="n">
-        <v>157</v>
-      </c>
-      <c r="P133" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="Q133" s="9" t="n">
-        <v>134</v>
-      </c>
       <c r="R133" s="9" t="n">
-        <v>184</v>
+        <v>26</v>
       </c>
       <c r="S133" s="9" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>0a835aeel1lazxwqtfa664yxtxendmyu</t>
+          <t>0a838c9fl1l9eahd7x3xm2ecvtjwbbdv</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>汇智路南海生物科技园投放点</t>
+          <t>沙县小吃(南京第099店)凤翔新城投放点</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -10646,7 +10642,7 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
@@ -10662,7 +10658,7 @@
         <v>6</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>348</v>
+        <v>920</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -10676,52 +10672,52 @@
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
-          <t>33☂</t>
+          <t>48☂</t>
         </is>
       </c>
       <c r="M134" s="9" t="n">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="N134" s="7" t="inlineStr">
         <is>
-          <t>25☂</t>
+          <t>75☂</t>
         </is>
       </c>
       <c r="O134" s="9" t="n">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="P134" s="9" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="Q134" s="9" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="R134" s="9" t="n">
-        <v>60</v>
+        <v>184</v>
       </c>
       <c r="S134" s="9" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>732955501476995072</t>
+          <t>0a835aeel1lazxwqtfa664yxtxendmyu</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-威尼斯三街区</t>
+          <t>汇智路南海生物科技园投放点</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E135" s="3" t="n">
@@ -10737,7 +10733,7 @@
         <v>6</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>775</v>
+        <v>348</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
@@ -10751,42 +10747,42 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>75☂</t>
+          <t>33☂</t>
         </is>
       </c>
       <c r="M135" s="9" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="N135" s="7" t="inlineStr">
         <is>
-          <t>100☂</t>
+          <t>25☂</t>
         </is>
       </c>
       <c r="O135" s="9" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="P135" s="9" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="Q135" s="9" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="R135" s="9" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="S135" s="9" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>639135555017715712</t>
+          <t>732955501476995072</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>浦口区天华北路1号</t>
+          <t>25-早峰-居民区-威尼斯三街区</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -10812,7 +10808,7 @@
         <v>6</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>476</v>
+        <v>775</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -10830,38 +10826,38 @@
         </is>
       </c>
       <c r="M136" s="9" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="N136" s="7" t="inlineStr">
         <is>
-          <t>70☂</t>
+          <t>100☂</t>
         </is>
       </c>
       <c r="O136" s="9" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="P136" s="9" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="R136" s="9" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="S136" s="9" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>765176977161322496</t>
+          <t>639135555017715712</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-明发三期金斯利</t>
+          <t>浦口区天华北路1号</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -10887,7 +10883,7 @@
         <v>6</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>343</v>
+        <v>476</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
@@ -10901,42 +10897,42 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>50☂</t>
+          <t>75☂</t>
         </is>
       </c>
       <c r="M137" s="9" t="n">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="N137" s="7" t="inlineStr">
         <is>
-          <t>50☂</t>
+          <t>70☂</t>
         </is>
       </c>
       <c r="O137" s="9" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P137" s="9" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="Q137" s="9" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="R137" s="9" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="S137" s="9" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>732956005347999744</t>
+          <t>765176977161322496</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城十街区</t>
+          <t>25-早峰-居民区-明发三期金斯利</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -10962,7 +10958,7 @@
         <v>6</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -10976,42 +10972,42 @@
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
-          <t>40☂</t>
+          <t>50☂</t>
         </is>
       </c>
       <c r="M138" s="9" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N138" s="7" t="inlineStr">
         <is>
-          <t>60☂</t>
+          <t>50☂</t>
         </is>
       </c>
       <c r="O138" s="9" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P138" s="9" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="Q138" s="9" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="R138" s="9" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="S138" s="9" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>752739851247206400</t>
+          <t>732956005347999744</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-明发三期北区</t>
+          <t>25-早峰-居民区-天润城十街区</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -11037,7 +11033,7 @@
         <v>6</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>330</v>
+        <v>377</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -11051,42 +11047,42 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>25☂</t>
+          <t>40☂</t>
         </is>
       </c>
       <c r="M139" s="9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N139" s="7" t="inlineStr">
         <is>
-          <t>50☂</t>
+          <t>60☂</t>
         </is>
       </c>
       <c r="O139" s="9" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="P139" s="9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q139" s="9" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="R139" s="9" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="S139" s="9" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>626976116946362368</t>
+          <t>752739851247206400</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-润泰花园东30</t>
+          <t>25-早峰-居民区-明发三期北区</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -11112,7 +11108,7 @@
         <v>6</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>681</v>
+        <v>330</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -11126,42 +11122,42 @@
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
-          <t>80☂</t>
+          <t>25☂</t>
         </is>
       </c>
       <c r="M140" s="9" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N140" s="7" t="inlineStr">
         <is>
-          <t>70☂</t>
+          <t>50☂</t>
         </is>
       </c>
       <c r="O140" s="9" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="P140" s="9" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="Q140" s="9" t="n">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="R140" s="9" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="S140" s="9" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>0a836146l1l77t6e64cbw8rqk9kqakwh</t>
+          <t>626976116946362368</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>江山路明发滨江新城三期投放点A</t>
+          <t>25-早峰-居民区-润泰花园东30</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -11171,7 +11167,7 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E141" s="3" t="n">
@@ -11187,7 +11183,7 @@
         <v>6</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -11201,42 +11197,42 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>100☂</t>
+          <t>80☂</t>
         </is>
       </c>
       <c r="M141" s="9" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N141" s="7" t="inlineStr">
         <is>
-          <t>100☂</t>
+          <t>70☂</t>
         </is>
       </c>
       <c r="O141" s="9" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="P141" s="9" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="Q141" s="9" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="R141" s="9" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="S141" s="9" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>844072914782052352</t>
+          <t>0a836146l1l77t6e64cbw8rqk9kqakwh</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-威尼斯十二街区</t>
+          <t>江山路明发滨江新城三期投放点A</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -11246,7 +11242,7 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E142" s="3" t="n">
@@ -11262,7 +11258,7 @@
         <v>6</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>245</v>
+        <v>675</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
@@ -11276,42 +11272,42 @@
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
-          <t>25☂</t>
+          <t>100☂</t>
         </is>
       </c>
       <c r="M142" s="9" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="N142" s="7" t="inlineStr">
         <is>
-          <t>28☂</t>
+          <t>100☂</t>
         </is>
       </c>
       <c r="O142" s="9" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="P142" s="9" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="R142" s="9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>e5189cd954054116aa19db28790cc606</t>
+          <t>844072914782052352</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-高新地铁站-30</t>
+          <t>25-早峰-居民区-威尼斯十二街区</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -11337,7 +11333,7 @@
         <v>6</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>876</v>
+        <v>245</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -11351,42 +11347,42 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>25☂</t>
         </is>
       </c>
       <c r="M143" s="9" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="N143" s="7" t="inlineStr">
         <is>
-          <t>162☂</t>
+          <t>28☂</t>
         </is>
       </c>
       <c r="O143" s="9" t="n">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="P143" s="9" t="n">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="Q143" s="9" t="n">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="R143" s="9" t="n">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>124</v>
+        <v>28</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>590398960471314432</t>
+          <t>e5189cd954054116aa19db28790cc606</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城1-4街区东</t>
+          <t>25-晚峰-地铁站-高新地铁站-30</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -11412,7 +11408,7 @@
         <v>6</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>255</v>
+        <v>876</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -11426,42 +11422,42 @@
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
-          <t>29☂</t>
+          <t>0☂</t>
         </is>
       </c>
       <c r="M144" s="9" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="N144" s="7" t="inlineStr">
         <is>
-          <t>29☂</t>
+          <t>162☂</t>
         </is>
       </c>
       <c r="O144" s="9" t="n">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="P144" s="9" t="n">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="Q144" s="9" t="n">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="R144" s="9" t="n">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="S144" s="9" t="n">
-        <v>29</v>
+        <v>124</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>826474668008353792</t>
+          <t>590398960471314432</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-蓝海雅苑</t>
+          <t>25-早峰-居民区-天润城1-4街区东</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -11471,7 +11467,7 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E145" s="3" t="n">
@@ -11487,7 +11483,7 @@
         <v>6</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>495</v>
+        <v>255</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -11501,42 +11497,42 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>50☂</t>
+          <t>29☂</t>
         </is>
       </c>
       <c r="M145" s="9" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="N145" s="7" t="inlineStr">
         <is>
-          <t>62☂</t>
+          <t>29☂</t>
         </is>
       </c>
       <c r="O145" s="9" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="P145" s="9" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="Q145" s="9" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="R145" s="9" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="S145" s="9" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>1206467184454987776</t>
+          <t>826474668008353792</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
+          <t>25-全天-居民区-蓝海雅苑</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -11562,7 +11558,7 @@
         <v>6</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>599</v>
+        <v>495</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -11576,7 +11572,7 @@
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
-          <t>61☂</t>
+          <t>50☂</t>
         </is>
       </c>
       <c r="M146" s="9" t="n">
@@ -11584,34 +11580,34 @@
       </c>
       <c r="N146" s="7" t="inlineStr">
         <is>
-          <t>113☂</t>
+          <t>62☂</t>
         </is>
       </c>
       <c r="O146" s="9" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P146" s="9" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="Q146" s="9" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="R146" s="9" t="n">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="S146" s="9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>732955983377653760</t>
+          <t>1206467184454987776</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-天润城1-4街区</t>
+          <t>25-全天-地铁站-临江地铁 1号口-渗透</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -11637,7 +11633,7 @@
         <v>6</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>706</v>
+        <v>599</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -11651,68 +11647,68 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>100☂</t>
+          <t>61☂</t>
         </is>
       </c>
       <c r="M147" s="9" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N147" s="7" t="inlineStr">
         <is>
-          <t>80☂</t>
+          <t>113☂</t>
         </is>
       </c>
       <c r="O147" s="9" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="P147" s="9" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="Q147" s="9" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="R147" s="9" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="S147" s="9" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>1130000746265899008</t>
+          <t>732955983377653760</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>城北万象汇</t>
+          <t>25-早峰-居民区-天润城1-4街区</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰+夜间</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>275</v>
+        <v>706</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -11724,68 +11720,70 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L148" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="M148" s="7" t="inlineStr">
-        <is>
-          <t>25☂</t>
-        </is>
-      </c>
-      <c r="N148" s="9" t="n">
+      <c r="L148" s="7" t="inlineStr">
+        <is>
+          <t>100☂</t>
+        </is>
+      </c>
+      <c r="M148" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="N148" s="7" t="inlineStr">
+        <is>
+          <t>80☂</t>
+        </is>
+      </c>
+      <c r="O148" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="P148" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q148" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="O148" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="P148" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q148" s="9" t="n">
-        <v>25</v>
-      </c>
       <c r="R148" s="9" t="n">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="S148" s="9" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>816505037427507200</t>
+          <t>1130000746265899008</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>玄武区童卫路28-2号</t>
+          <t>城北万象汇</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>午峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E149" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>915</v>
+        <v>275</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
@@ -11798,44 +11796,46 @@
         </is>
       </c>
       <c r="L149" s="9" t="n">
-        <v>154</v>
-      </c>
-      <c r="M149" s="9" t="n">
-        <v>106</v>
+        <v>25</v>
+      </c>
+      <c r="M149" s="7" t="inlineStr">
+        <is>
+          <t>25☂</t>
+        </is>
       </c>
       <c r="N149" s="9" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="O149" s="9" t="n">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="P149" s="9" t="n">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="Q149" s="9" t="n">
-        <v>171</v>
+        <v>25</v>
       </c>
       <c r="R149" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="S149" s="9" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>732954989023625216</t>
+          <t>816505037427507200</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>工作日-全天-地铁站-鸡鸣寺地铁站渗透</t>
+          <t>玄武区童卫路28-2号</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -11856,7 +11856,7 @@
         <v>8</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>377</v>
+        <v>915</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
@@ -11869,44 +11869,44 @@
         </is>
       </c>
       <c r="L150" s="9" t="n">
-        <v>29</v>
+        <v>154</v>
       </c>
       <c r="M150" s="9" t="n">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="N150" s="9" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="O150" s="9" t="n">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="P150" s="9" t="n">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="Q150" s="9" t="n">
-        <v>25</v>
+        <v>171</v>
       </c>
       <c r="R150" s="9" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="S150" s="9" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>1150779775536443392</t>
+          <t>732954989023625216</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>南师大-笃学路</t>
+          <t>工作日-全天-地铁站-鸡鸣寺地铁站渗透</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>桂超</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F151" s="3" t="n">
         <v>8</v>
@@ -11927,7 +11927,7 @@
         <v>8</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>1785</v>
+        <v>377</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -11940,44 +11940,44 @@
         </is>
       </c>
       <c r="L151" s="9" t="n">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="M151" s="9" t="n">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="N151" s="9" t="n">
-        <v>208</v>
+        <v>85</v>
       </c>
       <c r="O151" s="9" t="n">
-        <v>154</v>
+        <v>30</v>
       </c>
       <c r="P151" s="9" t="n">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="Q151" s="9" t="n">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="R151" s="9" t="n">
-        <v>330</v>
+        <v>34</v>
       </c>
       <c r="S151" s="9" t="n">
-        <v>366</v>
+        <v>58</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>833203355565592576</t>
+          <t>1150779775536443392</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-保利朗诗蔚蓝</t>
+          <t>南师大-笃学路</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>桂超</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F152" s="3" t="n">
         <v>8</v>
@@ -11998,7 +11998,7 @@
         <v>8</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>284</v>
+        <v>1785</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -12011,44 +12011,44 @@
         </is>
       </c>
       <c r="L152" s="9" t="n">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="M152" s="9" t="n">
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="N152" s="9" t="n">
-        <v>28</v>
+        <v>208</v>
       </c>
       <c r="O152" s="9" t="n">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="P152" s="9" t="n">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="Q152" s="9" t="n">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="R152" s="9" t="n">
-        <v>46</v>
+        <v>330</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>45</v>
+        <v>366</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>939772361158500352</t>
+          <t>833203355565592576</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>25-全天-景区-先锋书店渗透</t>
+          <t>25-全天-居民区-保利朗诗蔚蓝</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>季晨曦</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -12069,7 +12069,7 @@
         <v>8</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>360</v>
+        <v>284</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -12082,28 +12082,28 @@
         </is>
       </c>
       <c r="L153" s="9" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="M153" s="9" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N153" s="9" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="O153" s="9" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="P153" s="9" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q153" s="9" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="R153" s="9" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="S153" s="9" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="154">
@@ -13043,12 +13043,12 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1206516292750213120</t>
+          <t>1221340620200710144</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>中山北路宏图大厦渗透</t>
+          <t>南昌路68号新金贸花园投放点</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>内环北线南京工业大学国家大学科技园投放点C</t>
+          <t>中山北路宏图大厦渗透</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -13785,7 +13785,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>939772361158500352</t>
+          <t>1172004123334877184</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -13816,7 +13816,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -13828,11 +13828,11 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="L30" s="8" t="n">
+      <c r="L30" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="M30" s="8" t="n">
         <v>0</v>
-      </c>
-      <c r="M30" s="9" t="n">
-        <v>58</v>
       </c>
     </row>
     <row r="31">
@@ -14156,12 +14156,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>1101025006370287616</t>
+          <t>1206515660536758272</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>南昌路68号新金贸花园投放点</t>
+          <t>南京邮电大学渗透</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
@@ -14187,7 +14187,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M37" s="8" t="n">
         <v>0</v>
@@ -14209,12 +14209,12 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>796589147581059072</t>
+          <t>0a83cb70l1l8mh5bczz58u3svwm3k2si</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>南京邮电大学渗透</t>
+          <t>内环北线南京工业大学国家大学科技园投放点C</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -14240,7 +14240,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39">
@@ -25662,19 +25662,19 @@
         <v>64</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
